--- a/research/traditional_assets/database/data/malaysia/malaysia_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_heathcare_information_and_technology.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="klse_mgrc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.017</v>
+        <v>0.12</v>
       </c>
       <c r="G2">
-        <v>-0.3722433460076046</v>
+        <v>0.3150406504065041</v>
       </c>
       <c r="H2">
-        <v>-0.3722433460076046</v>
+        <v>0.3150406504065041</v>
       </c>
       <c r="I2">
-        <v>-0.2916349809885932</v>
+        <v>0.2886178861788618</v>
       </c>
       <c r="J2">
-        <v>-0.2916349809885932</v>
+        <v>0.2886178861788618</v>
       </c>
       <c r="K2">
-        <v>-0.77</v>
+        <v>1.68</v>
       </c>
       <c r="L2">
-        <v>-0.2927756653992395</v>
+        <v>0.3414634146341463</v>
       </c>
       <c r="M2">
-        <v>0.4968</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.01435838150289017</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.6451948051948052</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.4968</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.01435838150289017</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.6451948051948052</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>5.13</v>
+        <v>1.69</v>
       </c>
       <c r="V2">
-        <v>0.1482658959537572</v>
+        <v>0.07444933920704846</v>
       </c>
       <c r="W2">
-        <v>-0.3392070484581498</v>
+        <v>0.2336578581363004</v>
       </c>
       <c r="X2">
-        <v>0.06900101408139761</v>
+        <v>0.1417590532949718</v>
       </c>
       <c r="Y2">
-        <v>-0.4082080625395474</v>
+        <v>0.09189880484132859</v>
       </c>
       <c r="Z2">
-        <v>3.012600229095074</v>
+        <v>2.021364009860312</v>
       </c>
       <c r="AA2">
-        <v>-0.8785796105383734</v>
+        <v>0.5834018077239111</v>
       </c>
       <c r="AB2">
-        <v>0.06859814253265403</v>
+        <v>0.1404864668532663</v>
       </c>
       <c r="AC2">
-        <v>-0.9471777530710275</v>
+        <v>0.4429153408706449</v>
       </c>
       <c r="AD2">
-        <v>0.374</v>
+        <v>0.33</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.374</v>
+        <v>0.33</v>
       </c>
       <c r="AG2">
-        <v>-4.756</v>
+        <v>-1.36</v>
       </c>
       <c r="AH2">
-        <v>0.01069365814605135</v>
+        <v>0.01432913590968302</v>
       </c>
       <c r="AI2">
-        <v>0.04944473823373876</v>
+        <v>0.03707865168539326</v>
       </c>
       <c r="AJ2">
-        <v>-0.1593620158155743</v>
+        <v>-0.06373008434864104</v>
       </c>
       <c r="AK2">
-        <v>-1.953985209531635</v>
+        <v>-0.188626907073509</v>
       </c>
       <c r="AL2">
-        <v>0.029</v>
+        <v>0.022</v>
       </c>
       <c r="AM2">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="AN2">
-        <v>-0.5780525502318392</v>
+        <v>0.2049689440993789</v>
       </c>
       <c r="AO2">
-        <v>-26.44827586206896</v>
+        <v>64.54545454545455</v>
       </c>
       <c r="AP2">
-        <v>7.350850077279753</v>
+        <v>-0.8447204968944098</v>
       </c>
       <c r="AQ2">
-        <v>-69.72727272727271</v>
+        <v>64.54545454545455</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +718,8827 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.017</v>
+        <v>0.12</v>
       </c>
       <c r="G3">
-        <v>-0.3722433460076046</v>
+        <v>0.3150406504065041</v>
       </c>
       <c r="H3">
-        <v>-0.3722433460076046</v>
+        <v>0.3150406504065041</v>
       </c>
       <c r="I3">
-        <v>-0.2916349809885932</v>
+        <v>0.2886178861788618</v>
       </c>
       <c r="J3">
-        <v>-0.2916349809885932</v>
+        <v>0.2886178861788618</v>
       </c>
       <c r="K3">
-        <v>-0.77</v>
+        <v>1.68</v>
       </c>
       <c r="L3">
-        <v>-0.2927756653992395</v>
+        <v>0.3414634146341463</v>
       </c>
       <c r="M3">
-        <v>0.4968</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01435838150289017</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.6451948051948052</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.4968</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01435838150289017</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.6451948051948052</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>1.69</v>
+      </c>
+      <c r="V3">
+        <v>0.07444933920704846</v>
+      </c>
+      <c r="W3">
+        <v>0.2336578581363004</v>
+      </c>
+      <c r="X3">
+        <v>0.1417590532949718</v>
+      </c>
+      <c r="Y3">
+        <v>0.09189880484132859</v>
+      </c>
+      <c r="Z3">
+        <v>2.021364009860312</v>
+      </c>
+      <c r="AA3">
+        <v>0.5834018077239111</v>
+      </c>
+      <c r="AB3">
+        <v>0.1404864668532663</v>
+      </c>
+      <c r="AC3">
+        <v>0.4429153408706449</v>
+      </c>
+      <c r="AD3">
+        <v>0.33</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.33</v>
+      </c>
+      <c r="AG3">
+        <v>-1.36</v>
+      </c>
+      <c r="AH3">
+        <v>0.01432913590968302</v>
+      </c>
+      <c r="AI3">
+        <v>0.03707865168539326</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.06373008434864104</v>
+      </c>
+      <c r="AK3">
+        <v>-0.188626907073509</v>
+      </c>
+      <c r="AL3">
+        <v>0.022</v>
+      </c>
+      <c r="AM3">
+        <v>0.022</v>
+      </c>
+      <c r="AN3">
+        <v>0.2049689440993789</v>
+      </c>
+      <c r="AO3">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="AP3">
+        <v>-0.8447204968944098</v>
+      </c>
+      <c r="AQ3">
+        <v>64.54545454545455</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Malaysian Genomics Resource Centre Berhad (KLSE:MGRC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KLSE:MGRC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Heathcare Information and Technology</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.014329135909683</v>
+      </c>
+      <c r="F2">
+        <v>0.24</v>
+      </c>
+      <c r="G2">
+        <v>22.7</v>
+      </c>
+      <c r="H2">
+        <v>18.6059392310946</v>
+      </c>
+      <c r="I2">
+        <v>21.34</v>
+      </c>
+      <c r="J2">
+        <v>22.4431392310946</v>
+      </c>
+      <c r="K2">
+        <v>0.33</v>
+      </c>
+      <c r="L2">
+        <v>5.5272</v>
+      </c>
+      <c r="M2">
+        <v>0.140486466853266</v>
+      </c>
+      <c r="N2">
+        <v>0.135488309968786</v>
+      </c>
+      <c r="O2">
+        <v>0.0529479449541284</v>
+      </c>
+      <c r="P2">
+        <v>0.0418</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.141759053294972</v>
+      </c>
+      <c r="T2">
+        <v>0.165074092064192</v>
+      </c>
+      <c r="U2">
+        <v>1.28966524512076</v>
+      </c>
+      <c r="V2">
+        <v>1.58170945325039</v>
+      </c>
+      <c r="W2">
+        <v>4.671114093606496</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>22.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.07983393650755573</v>
+      </c>
+      <c r="AC2">
+        <v>0.06966834862385321</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.61</v>
+      </c>
+      <c r="AH2">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="AI2">
+        <v>0.7490000000000006</v>
+      </c>
+      <c r="AJ2">
+        <v>0.33</v>
+      </c>
+      <c r="AK2">
+        <v>0.33</v>
+      </c>
+      <c r="AL2">
+        <v>0.022</v>
+      </c>
+      <c r="AM2">
+        <v>0.33</v>
+      </c>
+      <c r="AN2">
+        <v>1.69</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1406339452130583</v>
+      </c>
+      <c r="C2">
+        <v>22.9990949006112</v>
+      </c>
+      <c r="D2">
+        <v>21.3090949006112</v>
+      </c>
+      <c r="E2">
+        <v>-0.33</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.69</v>
+      </c>
+      <c r="H2">
+        <v>22.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L2">
+        <v>1.42</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.42</v>
+      </c>
+      <c r="O2">
+        <v>0.3408</v>
+      </c>
+      <c r="P2">
+        <v>1.0792</v>
+      </c>
+      <c r="Q2">
+        <v>1.2692</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1406339452130583</v>
+      </c>
+      <c r="T2">
+        <v>1.275572139718057</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.140348863744547</v>
+      </c>
+      <c r="C3">
+        <v>22.8286166242909</v>
+      </c>
+      <c r="D3">
+        <v>21.3689166242909</v>
+      </c>
+      <c r="E3">
+        <v>-0.09970000000000004</v>
+      </c>
+      <c r="F3">
+        <v>0.2303</v>
+      </c>
+      <c r="G3">
+        <v>1.69</v>
+      </c>
+      <c r="H3">
+        <v>22.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.61</v>
+      </c>
+      <c r="K3">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L3">
+        <v>1.42</v>
+      </c>
+      <c r="M3">
+        <v>0.01052471</v>
+      </c>
+      <c r="N3">
+        <v>1.40947529</v>
+      </c>
+      <c r="O3">
+        <v>0.3382740695999999</v>
+      </c>
+      <c r="P3">
+        <v>1.0712012204</v>
+      </c>
+      <c r="Q3">
+        <v>1.2612012204</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1414157007520677</v>
+      </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.28536441068963</v>
       </c>
       <c r="U3">
-        <v>5.13</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.1482658959537572</v>
+        <v>0.24</v>
       </c>
       <c r="W3">
-        <v>-0.3392070484581498</v>
-      </c>
-      <c r="X3">
-        <v>0.06900101408139761</v>
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.4082080625395474</v>
+        <v>134.9205821348046</v>
       </c>
       <c r="Z3">
-        <v>3.012600229095074</v>
-      </c>
-      <c r="AA3">
-        <v>-0.8785796105383734</v>
-      </c>
-      <c r="AB3">
-        <v>0.06859814253265403</v>
-      </c>
-      <c r="AC3">
-        <v>-0.9471777530710275</v>
-      </c>
-      <c r="AD3">
-        <v>0.374</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.374</v>
-      </c>
-      <c r="AG3">
-        <v>-4.756</v>
-      </c>
-      <c r="AH3">
-        <v>0.01069365814605135</v>
-      </c>
-      <c r="AI3">
-        <v>0.04944473823373876</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.1593620158155743</v>
-      </c>
-      <c r="AK3">
-        <v>-1.953985209531635</v>
-      </c>
-      <c r="AL3">
-        <v>0.029</v>
-      </c>
-      <c r="AM3">
-        <v>0.011</v>
-      </c>
-      <c r="AN3">
-        <v>-0.5780525502318392</v>
-      </c>
-      <c r="AO3">
-        <v>-26.44827586206896</v>
-      </c>
-      <c r="AP3">
-        <v>7.350850077279753</v>
-      </c>
-      <c r="AQ3">
-        <v>-69.72727272727271</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1400637822760356</v>
+      </c>
+      <c r="C4">
+        <v>22.65847517253813</v>
+      </c>
+      <c r="D4">
+        <v>21.42907517253813</v>
+      </c>
+      <c r="E4">
+        <v>0.1305999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.4606</v>
+      </c>
+      <c r="G4">
+        <v>1.69</v>
+      </c>
+      <c r="H4">
+        <v>22.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.61</v>
+      </c>
+      <c r="K4">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L4">
+        <v>1.42</v>
+      </c>
+      <c r="M4">
+        <v>0.02104942</v>
+      </c>
+      <c r="N4">
+        <v>1.39895058</v>
+      </c>
+      <c r="O4">
+        <v>0.3357481392</v>
+      </c>
+      <c r="P4">
+        <v>1.0632024408</v>
+      </c>
+      <c r="Q4">
+        <v>1.2532024408</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1422134104857506</v>
+      </c>
+      <c r="T4">
+        <v>1.295356523925928</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>67.46029106740234</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1397787008075243</v>
+      </c>
+      <c r="C5">
+        <v>22.48867339810623</v>
+      </c>
+      <c r="D5">
+        <v>21.48957339810622</v>
+      </c>
+      <c r="E5">
+        <v>0.3608999999999998</v>
+      </c>
+      <c r="F5">
+        <v>0.6908999999999998</v>
+      </c>
+      <c r="G5">
+        <v>1.69</v>
+      </c>
+      <c r="H5">
+        <v>22.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.61</v>
+      </c>
+      <c r="K5">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L5">
+        <v>1.42</v>
+      </c>
+      <c r="M5">
+        <v>0.03157413</v>
+      </c>
+      <c r="N5">
+        <v>1.38842587</v>
+      </c>
+      <c r="O5">
+        <v>0.3332222088</v>
+      </c>
+      <c r="P5">
+        <v>1.0552036612</v>
+      </c>
+      <c r="Q5">
+        <v>1.2452036612</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1430275678428086</v>
+      </c>
+      <c r="T5">
+        <v>1.305554660115553</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>44.97352737826822</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.139493619339013</v>
+      </c>
+      <c r="C6">
+        <v>22.31921418605515</v>
+      </c>
+      <c r="D6">
+        <v>21.55041418605514</v>
+      </c>
+      <c r="E6">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.9211999999999999</v>
+      </c>
+      <c r="G6">
+        <v>1.69</v>
+      </c>
+      <c r="H6">
+        <v>22.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.61</v>
+      </c>
+      <c r="K6">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L6">
+        <v>1.42</v>
+      </c>
+      <c r="M6">
+        <v>0.04209884</v>
+      </c>
+      <c r="N6">
+        <v>1.37790116</v>
+      </c>
+      <c r="O6">
+        <v>0.3306962784</v>
+      </c>
+      <c r="P6">
+        <v>1.0472048816</v>
+      </c>
+      <c r="Q6">
+        <v>1.2372048816</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1438586868114718</v>
+      </c>
+      <c r="T6">
+        <v>1.315965257475795</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>33.73014553370117</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1392085378705016</v>
+      </c>
+      <c r="C7">
+        <v>22.15010045421007</v>
+      </c>
+      <c r="D7">
+        <v>21.61160045421007</v>
+      </c>
+      <c r="E7">
+        <v>0.8214999999999999</v>
+      </c>
+      <c r="F7">
+        <v>1.1515</v>
+      </c>
+      <c r="G7">
+        <v>1.69</v>
+      </c>
+      <c r="H7">
+        <v>22.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.61</v>
+      </c>
+      <c r="K7">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L7">
+        <v>1.42</v>
+      </c>
+      <c r="M7">
+        <v>0.05262355000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.36737645</v>
+      </c>
+      <c r="O7">
+        <v>0.3281703479999999</v>
+      </c>
+      <c r="P7">
+        <v>1.039206102</v>
+      </c>
+      <c r="Q7">
+        <v>1.229206102</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1447073030215807</v>
+      </c>
+      <c r="T7">
+        <v>1.326595025306779</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>26.98411642696093</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1389234564019903</v>
+      </c>
+      <c r="C8">
+        <v>21.98133515362786</v>
+      </c>
+      <c r="D8">
+        <v>21.67313515362785</v>
+      </c>
+      <c r="E8">
+        <v>1.0518</v>
+      </c>
+      <c r="F8">
+        <v>1.3818</v>
+      </c>
+      <c r="G8">
+        <v>1.69</v>
+      </c>
+      <c r="H8">
+        <v>22.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.61</v>
+      </c>
+      <c r="K8">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L8">
+        <v>1.42</v>
+      </c>
+      <c r="M8">
+        <v>0.06314826</v>
+      </c>
+      <c r="N8">
+        <v>1.35685174</v>
+      </c>
+      <c r="O8">
+        <v>0.3256444176</v>
+      </c>
+      <c r="P8">
+        <v>1.0312073224</v>
+      </c>
+      <c r="Q8">
+        <v>1.2212073224</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1455739748957344</v>
+      </c>
+      <c r="T8">
+        <v>1.337450958410762</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>22.48676368913411</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1386383749334789</v>
+      </c>
+      <c r="C9">
+        <v>21.81292126907152</v>
+      </c>
+      <c r="D9">
+        <v>21.73502126907152</v>
+      </c>
+      <c r="E9">
+        <v>1.2821</v>
+      </c>
+      <c r="F9">
+        <v>1.6121</v>
+      </c>
+      <c r="G9">
+        <v>1.69</v>
+      </c>
+      <c r="H9">
+        <v>22.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.61</v>
+      </c>
+      <c r="K9">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L9">
+        <v>1.42</v>
+      </c>
+      <c r="M9">
+        <v>0.07367297000000002</v>
+      </c>
+      <c r="N9">
+        <v>1.34632703</v>
+      </c>
+      <c r="O9">
+        <v>0.3231184872</v>
+      </c>
+      <c r="P9">
+        <v>1.0232085428</v>
+      </c>
+      <c r="Q9">
+        <v>1.2132085428</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1464592848747086</v>
+      </c>
+      <c r="T9">
+        <v>1.348540352441713</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>19.27436887640066</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1383532934649676</v>
+      </c>
+      <c r="C10">
+        <v>21.64486181949281</v>
+      </c>
+      <c r="D10">
+        <v>21.79726181949281</v>
+      </c>
+      <c r="E10">
+        <v>1.5124</v>
+      </c>
+      <c r="F10">
+        <v>1.8424</v>
+      </c>
+      <c r="G10">
+        <v>1.69</v>
+      </c>
+      <c r="H10">
+        <v>22.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.61</v>
+      </c>
+      <c r="K10">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L10">
+        <v>1.42</v>
+      </c>
+      <c r="M10">
+        <v>0.08419768</v>
+      </c>
+      <c r="N10">
+        <v>1.33580232</v>
+      </c>
+      <c r="O10">
+        <v>0.3205925568</v>
+      </c>
+      <c r="P10">
+        <v>1.0152097632</v>
+      </c>
+      <c r="Q10">
+        <v>1.2052097632</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1473638407227909</v>
+      </c>
+      <c r="T10">
+        <v>1.359870820255946</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>16.86507276685058</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1380682119964563</v>
+      </c>
+      <c r="C11">
+        <v>21.47715985852316</v>
+      </c>
+      <c r="D11">
+        <v>21.85985985852316</v>
+      </c>
+      <c r="E11">
+        <v>1.7427</v>
+      </c>
+      <c r="F11">
+        <v>2.0727</v>
+      </c>
+      <c r="G11">
+        <v>1.69</v>
+      </c>
+      <c r="H11">
+        <v>22.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.61</v>
+      </c>
+      <c r="K11">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L11">
+        <v>1.42</v>
+      </c>
+      <c r="M11">
+        <v>0.09472239</v>
+      </c>
+      <c r="N11">
+        <v>1.32527761</v>
+      </c>
+      <c r="O11">
+        <v>0.3180666263999999</v>
+      </c>
+      <c r="P11">
+        <v>1.0072109836</v>
+      </c>
+      <c r="Q11">
+        <v>1.1972109836</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1482882769191827</v>
+      </c>
+      <c r="T11">
+        <v>1.37145030934082</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>14.99117579275607</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1377831305279449</v>
+      </c>
+      <c r="C12">
+        <v>21.30981847497306</v>
+      </c>
+      <c r="D12">
+        <v>21.92281847497306</v>
+      </c>
+      <c r="E12">
+        <v>1.973</v>
+      </c>
+      <c r="F12">
+        <v>2.303</v>
+      </c>
+      <c r="G12">
+        <v>1.69</v>
+      </c>
+      <c r="H12">
+        <v>22.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.61</v>
+      </c>
+      <c r="K12">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L12">
+        <v>1.42</v>
+      </c>
+      <c r="M12">
+        <v>0.1052471</v>
+      </c>
+      <c r="N12">
+        <v>1.3147529</v>
+      </c>
+      <c r="O12">
+        <v>0.315540696</v>
+      </c>
+      <c r="P12">
+        <v>0.999212204</v>
+      </c>
+      <c r="Q12">
+        <v>1.189212204</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.149233256142161</v>
+      </c>
+      <c r="T12">
+        <v>1.383287120405359</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>13.49205821348047</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1376318090594336</v>
+      </c>
+      <c r="C13">
+        <v>21.11308452134125</v>
+      </c>
+      <c r="D13">
+        <v>21.95638452134125</v>
+      </c>
+      <c r="E13">
+        <v>2.2033</v>
+      </c>
+      <c r="F13">
+        <v>2.5333</v>
+      </c>
+      <c r="G13">
+        <v>1.69</v>
+      </c>
+      <c r="H13">
+        <v>22.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.61</v>
+      </c>
+      <c r="K13">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L13">
+        <v>1.42</v>
+      </c>
+      <c r="M13">
+        <v>0.11982509</v>
+      </c>
+      <c r="N13">
+        <v>1.30017491</v>
+      </c>
+      <c r="O13">
+        <v>0.3120419784</v>
+      </c>
+      <c r="P13">
+        <v>0.9881329316</v>
+      </c>
+      <c r="Q13">
+        <v>1.1781329316</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1501994708532962</v>
+      </c>
+      <c r="T13">
+        <v>1.395389927224157</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.035948</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>11.85060657997419</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1373588875909222</v>
+      </c>
+      <c r="C14">
+        <v>20.94358440304889</v>
+      </c>
+      <c r="D14">
+        <v>22.01718440304889</v>
+      </c>
+      <c r="E14">
+        <v>2.433599999999999</v>
+      </c>
+      <c r="F14">
+        <v>2.763599999999999</v>
+      </c>
+      <c r="G14">
+        <v>1.69</v>
+      </c>
+      <c r="H14">
+        <v>22.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.61</v>
+      </c>
+      <c r="K14">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L14">
+        <v>1.42</v>
+      </c>
+      <c r="M14">
+        <v>0.13071828</v>
+      </c>
+      <c r="N14">
+        <v>1.28928172</v>
+      </c>
+      <c r="O14">
+        <v>0.3094276128</v>
+      </c>
+      <c r="P14">
+        <v>0.9798541072</v>
+      </c>
+      <c r="Q14">
+        <v>1.1698541072</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1511876449896844</v>
+      </c>
+      <c r="T14">
+        <v>1.407767797834292</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.035948</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>10.86305603164301</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1374614061224109</v>
+      </c>
+      <c r="C15">
+        <v>20.69040646626259</v>
+      </c>
+      <c r="D15">
+        <v>21.99430646626259</v>
+      </c>
+      <c r="E15">
+        <v>2.6639</v>
+      </c>
+      <c r="F15">
+        <v>2.9939</v>
+      </c>
+      <c r="G15">
+        <v>1.69</v>
+      </c>
+      <c r="H15">
+        <v>22.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.61</v>
+      </c>
+      <c r="K15">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L15">
+        <v>1.42</v>
+      </c>
+      <c r="M15">
+        <v>0.15298829</v>
+      </c>
+      <c r="N15">
+        <v>1.26701171</v>
+      </c>
+      <c r="O15">
+        <v>0.3040828104</v>
+      </c>
+      <c r="P15">
+        <v>0.9629288996000001</v>
+      </c>
+      <c r="Q15">
+        <v>1.1529288996</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1521985357728861</v>
+      </c>
+      <c r="T15">
+        <v>1.420430217194084</v>
+      </c>
+      <c r="U15">
+        <v>0.0511</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.038836</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>9.28175613963657</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1372173646538996</v>
+      </c>
+      <c r="C16">
+        <v>20.51464483830487</v>
+      </c>
+      <c r="D16">
+        <v>22.04884483830487</v>
+      </c>
+      <c r="E16">
+        <v>2.8942</v>
+      </c>
+      <c r="F16">
+        <v>3.2242</v>
+      </c>
+      <c r="G16">
+        <v>1.69</v>
+      </c>
+      <c r="H16">
+        <v>22.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.61</v>
+      </c>
+      <c r="K16">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L16">
+        <v>1.42</v>
+      </c>
+      <c r="M16">
+        <v>0.16475662</v>
+      </c>
+      <c r="N16">
+        <v>1.25524338</v>
+      </c>
+      <c r="O16">
+        <v>0.3012584112</v>
+      </c>
+      <c r="P16">
+        <v>0.9539849687999999</v>
+      </c>
+      <c r="Q16">
+        <v>1.1439849688</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1532329356440693</v>
+      </c>
+      <c r="T16">
+        <v>1.433387111422709</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.038836</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.618773558233958</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1369733231853882</v>
+      </c>
+      <c r="C17">
+        <v>20.33915435578609</v>
+      </c>
+      <c r="D17">
+        <v>22.10365435578608</v>
+      </c>
+      <c r="E17">
+        <v>3.124499999999999</v>
+      </c>
+      <c r="F17">
+        <v>3.454499999999999</v>
+      </c>
+      <c r="G17">
+        <v>1.69</v>
+      </c>
+      <c r="H17">
+        <v>22.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.61</v>
+      </c>
+      <c r="K17">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L17">
+        <v>1.42</v>
+      </c>
+      <c r="M17">
+        <v>0.17652495</v>
+      </c>
+      <c r="N17">
+        <v>1.24347505</v>
+      </c>
+      <c r="O17">
+        <v>0.298434012</v>
+      </c>
+      <c r="P17">
+        <v>0.9450410380000001</v>
+      </c>
+      <c r="Q17">
+        <v>1.135041038</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1542916743357509</v>
+      </c>
+      <c r="T17">
+        <v>1.446648873750831</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.038836</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.044188654351696</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1369603217168769</v>
+      </c>
+      <c r="C18">
+        <v>20.11178201495698</v>
+      </c>
+      <c r="D18">
+        <v>22.10658201495698</v>
+      </c>
+      <c r="E18">
+        <v>3.3548</v>
+      </c>
+      <c r="F18">
+        <v>3.6848</v>
+      </c>
+      <c r="G18">
+        <v>1.69</v>
+      </c>
+      <c r="H18">
+        <v>22.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.61</v>
+      </c>
+      <c r="K18">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L18">
+        <v>1.42</v>
+      </c>
+      <c r="M18">
+        <v>0.1952944</v>
+      </c>
+      <c r="N18">
+        <v>1.2247056</v>
+      </c>
+      <c r="O18">
+        <v>0.2939293439999999</v>
+      </c>
+      <c r="P18">
+        <v>0.9307762559999999</v>
+      </c>
+      <c r="Q18">
+        <v>1.120776256</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1553756210915201</v>
+      </c>
+      <c r="T18">
+        <v>1.460226392324861</v>
+      </c>
+      <c r="U18">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.04028</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.271073824953505</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1367307202483656</v>
+      </c>
+      <c r="C19">
+        <v>19.93331154997447</v>
+      </c>
+      <c r="D19">
+        <v>22.15841154997447</v>
+      </c>
+      <c r="E19">
+        <v>3.5851</v>
+      </c>
+      <c r="F19">
+        <v>3.9151</v>
+      </c>
+      <c r="G19">
+        <v>1.69</v>
+      </c>
+      <c r="H19">
+        <v>22.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.61</v>
+      </c>
+      <c r="K19">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L19">
+        <v>1.42</v>
+      </c>
+      <c r="M19">
+        <v>0.2075003</v>
+      </c>
+      <c r="N19">
+        <v>1.2124997</v>
+      </c>
+      <c r="O19">
+        <v>0.290999928</v>
+      </c>
+      <c r="P19">
+        <v>0.921499772</v>
+      </c>
+      <c r="Q19">
+        <v>1.111499772</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1564856870462236</v>
+      </c>
+      <c r="T19">
+        <v>1.474131080021157</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.04028</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>6.843363599956241</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1365011187798542</v>
+      </c>
+      <c r="C20">
+        <v>19.75508468788005</v>
+      </c>
+      <c r="D20">
+        <v>22.21048468788005</v>
+      </c>
+      <c r="E20">
+        <v>3.815399999999999</v>
+      </c>
+      <c r="F20">
+        <v>4.1454</v>
+      </c>
+      <c r="G20">
+        <v>1.69</v>
+      </c>
+      <c r="H20">
+        <v>22.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.61</v>
+      </c>
+      <c r="K20">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L20">
+        <v>1.42</v>
+      </c>
+      <c r="M20">
+        <v>0.2197062</v>
+      </c>
+      <c r="N20">
+        <v>1.2002938</v>
+      </c>
+      <c r="O20">
+        <v>0.2880705119999999</v>
+      </c>
+      <c r="P20">
+        <v>0.9122232879999999</v>
+      </c>
+      <c r="Q20">
+        <v>1.102223288</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.15762282778031</v>
+      </c>
+      <c r="T20">
+        <v>1.488374906441752</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.04028</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.463176733292005</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1365603173113429</v>
+      </c>
+      <c r="C21">
+        <v>19.51133518082714</v>
+      </c>
+      <c r="D21">
+        <v>22.19703518082714</v>
+      </c>
+      <c r="E21">
+        <v>4.045699999999999</v>
+      </c>
+      <c r="F21">
+        <v>4.375699999999999</v>
+      </c>
+      <c r="G21">
+        <v>1.69</v>
+      </c>
+      <c r="H21">
+        <v>22.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.61</v>
+      </c>
+      <c r="K21">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L21">
+        <v>1.42</v>
+      </c>
+      <c r="M21">
+        <v>0.2406634999999999</v>
+      </c>
+      <c r="N21">
+        <v>1.1793365</v>
+      </c>
+      <c r="O21">
+        <v>0.28304076</v>
+      </c>
+      <c r="P21">
+        <v>0.89629574</v>
+      </c>
+      <c r="Q21">
+        <v>1.08629574</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1587880460633863</v>
+      </c>
+      <c r="T21">
+        <v>1.50297043228014</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.0418</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.900354644555573</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1363459158428316</v>
+      </c>
+      <c r="C22">
+        <v>19.32982325050946</v>
+      </c>
+      <c r="D22">
+        <v>22.24582325050946</v>
+      </c>
+      <c r="E22">
+        <v>4.276</v>
+      </c>
+      <c r="F22">
+        <v>4.606</v>
+      </c>
+      <c r="G22">
+        <v>1.69</v>
+      </c>
+      <c r="H22">
+        <v>22.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.61</v>
+      </c>
+      <c r="K22">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L22">
+        <v>1.42</v>
+      </c>
+      <c r="M22">
+        <v>0.25333</v>
+      </c>
+      <c r="N22">
+        <v>1.16667</v>
+      </c>
+      <c r="O22">
+        <v>0.2800007999999999</v>
+      </c>
+      <c r="P22">
+        <v>0.8866691999999999</v>
+      </c>
+      <c r="Q22">
+        <v>1.0766692</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1599823948035394</v>
+      </c>
+      <c r="T22">
+        <v>1.517930846264487</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.0418</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.605336912327793</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1361315143743202</v>
+      </c>
+      <c r="C23">
+        <v>19.14852626051925</v>
+      </c>
+      <c r="D23">
+        <v>22.29482626051925</v>
+      </c>
+      <c r="E23">
+        <v>4.5063</v>
+      </c>
+      <c r="F23">
+        <v>4.8363</v>
+      </c>
+      <c r="G23">
+        <v>1.69</v>
+      </c>
+      <c r="H23">
+        <v>22.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.61</v>
+      </c>
+      <c r="K23">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L23">
+        <v>1.42</v>
+      </c>
+      <c r="M23">
+        <v>0.2659965</v>
+      </c>
+      <c r="N23">
+        <v>1.1540035</v>
+      </c>
+      <c r="O23">
+        <v>0.27696084</v>
+      </c>
+      <c r="P23">
+        <v>0.87704266</v>
+      </c>
+      <c r="Q23">
+        <v>1.06704266</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1612069802206585</v>
+      </c>
+      <c r="T23">
+        <v>1.533270004906667</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.0418</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.338416106978851</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1359171129058089</v>
+      </c>
+      <c r="C24">
+        <v>18.96744563440135</v>
+      </c>
+      <c r="D24">
+        <v>22.34404563440135</v>
+      </c>
+      <c r="E24">
+        <v>4.736599999999999</v>
+      </c>
+      <c r="F24">
+        <v>5.066599999999999</v>
+      </c>
+      <c r="G24">
+        <v>1.69</v>
+      </c>
+      <c r="H24">
+        <v>22.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.61</v>
+      </c>
+      <c r="K24">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L24">
+        <v>1.42</v>
+      </c>
+      <c r="M24">
+        <v>0.2786629999999999</v>
+      </c>
+      <c r="N24">
+        <v>1.141337</v>
+      </c>
+      <c r="O24">
+        <v>0.27392088</v>
+      </c>
+      <c r="P24">
+        <v>0.8674161200000001</v>
+      </c>
+      <c r="Q24">
+        <v>1.05741612</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1624629652638575</v>
+      </c>
+      <c r="T24">
+        <v>1.549002475308902</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.0418</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.095760829388905</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1357027114372975</v>
+      </c>
+      <c r="C25">
+        <v>18.78658280829922</v>
+      </c>
+      <c r="D25">
+        <v>22.39348280829921</v>
+      </c>
+      <c r="E25">
+        <v>4.9669</v>
+      </c>
+      <c r="F25">
+        <v>5.2969</v>
+      </c>
+      <c r="G25">
+        <v>1.69</v>
+      </c>
+      <c r="H25">
+        <v>22.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.61</v>
+      </c>
+      <c r="K25">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L25">
+        <v>1.42</v>
+      </c>
+      <c r="M25">
+        <v>0.2913295</v>
+      </c>
+      <c r="N25">
+        <v>1.1286705</v>
+      </c>
+      <c r="O25">
+        <v>0.27088092</v>
+      </c>
+      <c r="P25">
+        <v>0.8577895799999999</v>
+      </c>
+      <c r="Q25">
+        <v>1.04778958</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1637515732951916</v>
+      </c>
+      <c r="T25">
+        <v>1.565143581306</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.0418</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>4.874206010719821</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1354883099687862</v>
+      </c>
+      <c r="C26">
+        <v>18.60593923109462</v>
+      </c>
+      <c r="D26">
+        <v>22.44313923109461</v>
+      </c>
+      <c r="E26">
+        <v>5.197199999999999</v>
+      </c>
+      <c r="F26">
+        <v>5.527199999999999</v>
+      </c>
+      <c r="G26">
+        <v>1.69</v>
+      </c>
+      <c r="H26">
+        <v>22.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.61</v>
+      </c>
+      <c r="K26">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L26">
+        <v>1.42</v>
+      </c>
+      <c r="M26">
+        <v>0.3039959999999999</v>
+      </c>
+      <c r="N26">
+        <v>1.116004</v>
+      </c>
+      <c r="O26">
+        <v>0.26784096</v>
+      </c>
+      <c r="P26">
+        <v>0.84816304</v>
+      </c>
+      <c r="Q26">
+        <v>1.03816304</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1650740920641923</v>
+      </c>
+      <c r="T26">
+        <v>1.58170945325039</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.0418</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.671114093606496</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1359959085002748</v>
+      </c>
+      <c r="C27">
+        <v>18.25843157604536</v>
+      </c>
+      <c r="D27">
+        <v>22.32593157604536</v>
+      </c>
+      <c r="E27">
+        <v>5.427499999999999</v>
+      </c>
+      <c r="F27">
+        <v>5.757499999999999</v>
+      </c>
+      <c r="G27">
+        <v>1.69</v>
+      </c>
+      <c r="H27">
+        <v>22.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.61</v>
+      </c>
+      <c r="K27">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L27">
+        <v>1.42</v>
+      </c>
+      <c r="M27">
+        <v>0.338541</v>
+      </c>
+      <c r="N27">
+        <v>1.081459</v>
+      </c>
+      <c r="O27">
+        <v>0.25955016</v>
+      </c>
+      <c r="P27">
+        <v>0.82190884</v>
+      </c>
+      <c r="Q27">
+        <v>1.01190884</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1664318780003665</v>
+      </c>
+      <c r="T27">
+        <v>1.598717081779964</v>
+      </c>
+      <c r="U27">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.194469798340526</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1358103870317635</v>
+      </c>
+      <c r="C28">
+        <v>18.0708274124254</v>
+      </c>
+      <c r="D28">
+        <v>22.3686274124254</v>
+      </c>
+      <c r="E28">
+        <v>5.6578</v>
+      </c>
+      <c r="F28">
+        <v>5.9878</v>
+      </c>
+      <c r="G28">
+        <v>1.69</v>
+      </c>
+      <c r="H28">
+        <v>22.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.61</v>
+      </c>
+      <c r="K28">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L28">
+        <v>1.42</v>
+      </c>
+      <c r="M28">
+        <v>0.3520826400000001</v>
+      </c>
+      <c r="N28">
+        <v>1.06791736</v>
+      </c>
+      <c r="O28">
+        <v>0.2563001664</v>
+      </c>
+      <c r="P28">
+        <v>0.8116171935999998</v>
+      </c>
+      <c r="Q28">
+        <v>1.0016171936</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1678263608537345</v>
+      </c>
+      <c r="T28">
+        <v>1.616184375945473</v>
+      </c>
+      <c r="U28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.03314403686589</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1364867055632522</v>
+      </c>
+      <c r="C29">
+        <v>17.6856617410348</v>
+      </c>
+      <c r="D29">
+        <v>22.2137617410348</v>
+      </c>
+      <c r="E29">
+        <v>5.8881</v>
+      </c>
+      <c r="F29">
+        <v>6.2181</v>
+      </c>
+      <c r="G29">
+        <v>1.69</v>
+      </c>
+      <c r="H29">
+        <v>22.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.61</v>
+      </c>
+      <c r="K29">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L29">
+        <v>1.42</v>
+      </c>
+      <c r="M29">
+        <v>0.3917403</v>
+      </c>
+      <c r="N29">
+        <v>1.0282597</v>
+      </c>
+      <c r="O29">
+        <v>0.246782328</v>
+      </c>
+      <c r="P29">
+        <v>0.781477372</v>
+      </c>
+      <c r="Q29">
+        <v>0.9714773720000002</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1692590487167838</v>
+      </c>
+      <c r="T29">
+        <v>1.634130226115516</v>
+      </c>
+      <c r="U29">
+        <v>0.063</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.04788</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.624850443010331</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1378439840947408</v>
+      </c>
+      <c r="C30">
+        <v>17.15094888658147</v>
+      </c>
+      <c r="D30">
+        <v>21.90934888658147</v>
+      </c>
+      <c r="E30">
+        <v>6.1184</v>
+      </c>
+      <c r="F30">
+        <v>6.4484</v>
+      </c>
+      <c r="G30">
+        <v>1.69</v>
+      </c>
+      <c r="H30">
+        <v>22.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.61</v>
+      </c>
+      <c r="K30">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L30">
+        <v>1.42</v>
+      </c>
+      <c r="M30">
+        <v>0.45203284</v>
+      </c>
+      <c r="N30">
+        <v>0.9679671599999999</v>
+      </c>
+      <c r="O30">
+        <v>0.2323121184</v>
+      </c>
+      <c r="P30">
+        <v>0.7356550415999999</v>
+      </c>
+      <c r="Q30">
+        <v>0.9256550416000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1707315334649178</v>
+      </c>
+      <c r="T30">
+        <v>1.652574572123616</v>
+      </c>
+      <c r="U30">
+        <v>0.0701</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.053276</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.141364684919794</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1377443426262295</v>
+      </c>
+      <c r="C31">
+        <v>16.94271260077918</v>
+      </c>
+      <c r="D31">
+        <v>21.93141260077918</v>
+      </c>
+      <c r="E31">
+        <v>6.348699999999999</v>
+      </c>
+      <c r="F31">
+        <v>6.678699999999999</v>
+      </c>
+      <c r="G31">
+        <v>1.69</v>
+      </c>
+      <c r="H31">
+        <v>22.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.61</v>
+      </c>
+      <c r="K31">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L31">
+        <v>1.42</v>
+      </c>
+      <c r="M31">
+        <v>0.4681768699999999</v>
+      </c>
+      <c r="N31">
+        <v>0.95182313</v>
+      </c>
+      <c r="O31">
+        <v>0.2284375512</v>
+      </c>
+      <c r="P31">
+        <v>0.7233855788</v>
+      </c>
+      <c r="Q31">
+        <v>0.9133855788000002</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1722454966566613</v>
+      </c>
+      <c r="T31">
+        <v>1.671538477174197</v>
+      </c>
+      <c r="U31">
+        <v>0.0701</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.053276</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.033041764750147</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1425011011577181</v>
+      </c>
+      <c r="C32">
+        <v>15.70642102661364</v>
+      </c>
+      <c r="D32">
+        <v>20.92542102661363</v>
+      </c>
+      <c r="E32">
+        <v>6.578999999999999</v>
+      </c>
+      <c r="F32">
+        <v>6.908999999999999</v>
+      </c>
+      <c r="G32">
+        <v>1.69</v>
+      </c>
+      <c r="H32">
+        <v>22.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.61</v>
+      </c>
+      <c r="K32">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L32">
+        <v>1.42</v>
+      </c>
+      <c r="M32">
+        <v>0.6314826</v>
+      </c>
+      <c r="N32">
+        <v>0.7885173999999999</v>
+      </c>
+      <c r="O32">
+        <v>0.189244176</v>
+      </c>
+      <c r="P32">
+        <v>0.5992732239999999</v>
+      </c>
+      <c r="Q32">
+        <v>0.7892732240000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1738027159395973</v>
+      </c>
+      <c r="T32">
+        <v>1.691044208083366</v>
+      </c>
+      <c r="U32">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.24</v>
+      </c>
+      <c r="W32">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.248676368913411</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1425633396892068</v>
+      </c>
+      <c r="C33">
+        <v>15.46356970088164</v>
+      </c>
+      <c r="D33">
+        <v>20.91286970088164</v>
+      </c>
+      <c r="E33">
+        <v>6.809299999999999</v>
+      </c>
+      <c r="F33">
+        <v>7.1393</v>
+      </c>
+      <c r="G33">
+        <v>1.69</v>
+      </c>
+      <c r="H33">
+        <v>22.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.61</v>
+      </c>
+      <c r="K33">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L33">
+        <v>1.42</v>
+      </c>
+      <c r="M33">
+        <v>0.65253202</v>
+      </c>
+      <c r="N33">
+        <v>0.7674679799999999</v>
+      </c>
+      <c r="O33">
+        <v>0.1841923152</v>
+      </c>
+      <c r="P33">
+        <v>0.5832756647999999</v>
+      </c>
+      <c r="Q33">
+        <v>0.7732756648000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1754050720133432</v>
+      </c>
+      <c r="T33">
+        <v>1.71111532249715</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.24</v>
+      </c>
+      <c r="W33">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.176138421529108</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1426255782206954</v>
+      </c>
+      <c r="C34">
+        <v>15.22073342300386</v>
+      </c>
+      <c r="D34">
+        <v>20.90033342300385</v>
+      </c>
+      <c r="E34">
+        <v>7.039599999999999</v>
+      </c>
+      <c r="F34">
+        <v>7.369599999999999</v>
+      </c>
+      <c r="G34">
+        <v>1.69</v>
+      </c>
+      <c r="H34">
+        <v>22.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.61</v>
+      </c>
+      <c r="K34">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L34">
+        <v>1.42</v>
+      </c>
+      <c r="M34">
+        <v>0.67358144</v>
+      </c>
+      <c r="N34">
+        <v>0.74641856</v>
+      </c>
+      <c r="O34">
+        <v>0.1791404544</v>
+      </c>
+      <c r="P34">
+        <v>0.5672781056</v>
+      </c>
+      <c r="Q34">
+        <v>0.7572781056000002</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1770545562069051</v>
+      </c>
+      <c r="T34">
+        <v>1.731776763805456</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.24</v>
+      </c>
+      <c r="W34">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.108134095856323</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1426878167521841</v>
+      </c>
+      <c r="C35">
+        <v>14.97791216593504</v>
+      </c>
+      <c r="D35">
+        <v>20.88781216593504</v>
+      </c>
+      <c r="E35">
+        <v>7.2699</v>
+      </c>
+      <c r="F35">
+        <v>7.5999</v>
+      </c>
+      <c r="G35">
+        <v>1.69</v>
+      </c>
+      <c r="H35">
+        <v>22.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.61</v>
+      </c>
+      <c r="K35">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L35">
+        <v>1.42</v>
+      </c>
+      <c r="M35">
+        <v>0.6946308600000001</v>
+      </c>
+      <c r="N35">
+        <v>0.7253691399999999</v>
+      </c>
+      <c r="O35">
+        <v>0.1740885936</v>
+      </c>
+      <c r="P35">
+        <v>0.5512805463999999</v>
+      </c>
+      <c r="Q35">
+        <v>0.7412805464000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1787532787346031</v>
+      </c>
+      <c r="T35">
+        <v>1.753054964555801</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.24</v>
+      </c>
+      <c r="W35">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.044251244466737</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1482022952836728</v>
+      </c>
+      <c r="C36">
+        <v>13.69475133280399</v>
+      </c>
+      <c r="D36">
+        <v>19.83495133280399</v>
+      </c>
+      <c r="E36">
+        <v>7.5002</v>
+      </c>
+      <c r="F36">
+        <v>7.8302</v>
+      </c>
+      <c r="G36">
+        <v>1.69</v>
+      </c>
+      <c r="H36">
+        <v>22.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.61</v>
+      </c>
+      <c r="K36">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L36">
+        <v>1.42</v>
+      </c>
+      <c r="M36">
+        <v>0.8808975</v>
+      </c>
+      <c r="N36">
+        <v>0.5391024999999999</v>
+      </c>
+      <c r="O36">
+        <v>0.1293846</v>
+      </c>
+      <c r="P36">
+        <v>0.4097179</v>
+      </c>
+      <c r="Q36">
+        <v>0.5997179000000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1805034777025345</v>
+      </c>
+      <c r="T36">
+        <v>1.774977959268278</v>
+      </c>
+      <c r="U36">
+        <v>0.1125</v>
+      </c>
+      <c r="V36">
+        <v>0.24</v>
+      </c>
+      <c r="W36">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>1.611992314656359</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1484248938151614</v>
+      </c>
+      <c r="C37">
+        <v>13.42417552604905</v>
+      </c>
+      <c r="D37">
+        <v>19.79467552604905</v>
+      </c>
+      <c r="E37">
+        <v>7.730499999999999</v>
+      </c>
+      <c r="F37">
+        <v>8.060499999999999</v>
+      </c>
+      <c r="G37">
+        <v>1.69</v>
+      </c>
+      <c r="H37">
+        <v>22.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.61</v>
+      </c>
+      <c r="K37">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L37">
+        <v>1.42</v>
+      </c>
+      <c r="M37">
+        <v>0.9068062499999999</v>
+      </c>
+      <c r="N37">
+        <v>0.51319375</v>
+      </c>
+      <c r="O37">
+        <v>0.1231665</v>
+      </c>
+      <c r="P37">
+        <v>0.39002725</v>
+      </c>
+      <c r="Q37">
+        <v>0.5800272500000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1823075289464022</v>
+      </c>
+      <c r="T37">
+        <v>1.797575507664215</v>
+      </c>
+      <c r="U37">
+        <v>0.1125</v>
+      </c>
+      <c r="V37">
+        <v>0.24</v>
+      </c>
+      <c r="W37">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.565935391380463</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1486474923466501</v>
+      </c>
+      <c r="C38">
+        <v>13.15376295170381</v>
+      </c>
+      <c r="D38">
+        <v>19.75456295170381</v>
+      </c>
+      <c r="E38">
+        <v>7.960799999999999</v>
+      </c>
+      <c r="F38">
+        <v>8.290799999999999</v>
+      </c>
+      <c r="G38">
+        <v>1.69</v>
+      </c>
+      <c r="H38">
+        <v>22.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.61</v>
+      </c>
+      <c r="K38">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L38">
+        <v>1.42</v>
+      </c>
+      <c r="M38">
+        <v>0.932715</v>
+      </c>
+      <c r="N38">
+        <v>0.487285</v>
+      </c>
+      <c r="O38">
+        <v>0.1169484</v>
+      </c>
+      <c r="P38">
+        <v>0.3703366</v>
+      </c>
+      <c r="Q38">
+        <v>0.5603366000000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1841679567916408</v>
+      </c>
+      <c r="T38">
+        <v>1.820879229447526</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0.24</v>
+      </c>
+      <c r="W38">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.522437186064339</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1765568108501635</v>
+      </c>
+      <c r="C39">
+        <v>8.921218809187407</v>
+      </c>
+      <c r="D39">
+        <v>15.7523188091874</v>
+      </c>
+      <c r="E39">
+        <v>8.191099999999999</v>
+      </c>
+      <c r="F39">
+        <v>8.521099999999999</v>
+      </c>
+      <c r="G39">
+        <v>1.69</v>
+      </c>
+      <c r="H39">
+        <v>22.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.61</v>
+      </c>
+      <c r="K39">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L39">
+        <v>1.42</v>
+      </c>
+      <c r="M39">
+        <v>1.67524826</v>
+      </c>
+      <c r="N39">
+        <v>-0.2552482599999999</v>
+      </c>
+      <c r="O39">
+        <v>-0.06125958239999997</v>
+      </c>
+      <c r="P39">
+        <v>-0.1939886775999999</v>
+      </c>
+      <c r="Q39">
+        <v>-0.003988677599999768</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1882744449185855</v>
+      </c>
+      <c r="T39">
+        <v>1.872317105450998</v>
+      </c>
+      <c r="U39">
+        <v>0.1966</v>
+      </c>
+      <c r="V39">
+        <v>0.203432534829196</v>
+      </c>
+      <c r="W39">
+        <v>0.1566051636525801</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.8476355617883167</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1781348108501635</v>
+      </c>
+      <c r="C40">
+        <v>8.512520037701444</v>
+      </c>
+      <c r="D40">
+        <v>15.57392003770144</v>
+      </c>
+      <c r="E40">
+        <v>8.421399999999998</v>
+      </c>
+      <c r="F40">
+        <v>8.751399999999999</v>
+      </c>
+      <c r="G40">
+        <v>1.69</v>
+      </c>
+      <c r="H40">
+        <v>22.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.61</v>
+      </c>
+      <c r="K40">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L40">
+        <v>1.42</v>
+      </c>
+      <c r="M40">
+        <v>1.72052524</v>
+      </c>
+      <c r="N40">
+        <v>-0.3005252399999998</v>
+      </c>
+      <c r="O40">
+        <v>-0.07212605759999995</v>
+      </c>
+      <c r="P40">
+        <v>-0.2283991823999998</v>
+      </c>
+      <c r="Q40">
+        <v>-0.03839918239999968</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1906853230624337</v>
+      </c>
+      <c r="T40">
+        <v>1.902515768442143</v>
+      </c>
+      <c r="U40">
+        <v>0.1966</v>
+      </c>
+      <c r="V40">
+        <v>0.1980790470705329</v>
+      </c>
+      <c r="W40">
+        <v>0.1576576593459332</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.8253293627938874</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1797128108501635</v>
+      </c>
+      <c r="C41">
+        <v>8.107816832831556</v>
+      </c>
+      <c r="D41">
+        <v>15.39951683283156</v>
+      </c>
+      <c r="E41">
+        <v>8.6517</v>
+      </c>
+      <c r="F41">
+        <v>8.9817</v>
+      </c>
+      <c r="G41">
+        <v>1.69</v>
+      </c>
+      <c r="H41">
+        <v>22.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.61</v>
+      </c>
+      <c r="K41">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L41">
+        <v>1.42</v>
+      </c>
+      <c r="M41">
+        <v>1.76580222</v>
+      </c>
+      <c r="N41">
+        <v>-0.3458022199999999</v>
+      </c>
+      <c r="O41">
+        <v>-0.08299253279999998</v>
+      </c>
+      <c r="P41">
+        <v>-0.2628096872</v>
+      </c>
+      <c r="Q41">
+        <v>-0.07280968719999981</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.193175246391326</v>
+      </c>
+      <c r="T41">
+        <v>1.933704551531359</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0.1930000971456475</v>
+      </c>
+      <c r="W41">
+        <v>0.1586561809011657</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8041670714401978</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1887874561847136</v>
+      </c>
+      <c r="C42">
+        <v>6.945804560778083</v>
+      </c>
+      <c r="D42">
+        <v>14.46780456077808</v>
+      </c>
+      <c r="E42">
+        <v>8.882</v>
+      </c>
+      <c r="F42">
+        <v>9.212</v>
+      </c>
+      <c r="G42">
+        <v>1.69</v>
+      </c>
+      <c r="H42">
+        <v>22.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.61</v>
+      </c>
+      <c r="K42">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L42">
+        <v>1.42</v>
+      </c>
+      <c r="M42">
+        <v>1.9695256</v>
+      </c>
+      <c r="N42">
+        <v>-0.5495255999999999</v>
+      </c>
+      <c r="O42">
+        <v>-0.131886144</v>
+      </c>
+      <c r="P42">
+        <v>-0.417639456</v>
+      </c>
+      <c r="Q42">
+        <v>-0.2276394559999998</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1967759093887649</v>
+      </c>
+      <c r="T42">
+        <v>1.978806461257408</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1730365931775652</v>
+      </c>
+      <c r="W42">
+        <v>0.1768047763786365</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.7209858049065216</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1905374561847136</v>
+      </c>
+      <c r="C43">
+        <v>6.548646234442755</v>
+      </c>
+      <c r="D43">
+        <v>14.30094623444275</v>
+      </c>
+      <c r="E43">
+        <v>9.112299999999999</v>
+      </c>
+      <c r="F43">
+        <v>9.442299999999999</v>
+      </c>
+      <c r="G43">
+        <v>1.69</v>
+      </c>
+      <c r="H43">
+        <v>22.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.61</v>
+      </c>
+      <c r="K43">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L43">
+        <v>1.42</v>
+      </c>
+      <c r="M43">
+        <v>2.01876374</v>
+      </c>
+      <c r="N43">
+        <v>-0.5987637399999999</v>
+      </c>
+      <c r="O43">
+        <v>-0.1437032976</v>
+      </c>
+      <c r="P43">
+        <v>-0.4550604423999999</v>
+      </c>
+      <c r="Q43">
+        <v>-0.2650604423999997</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1994534671750152</v>
+      </c>
+      <c r="T43">
+        <v>2.012345553821093</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1688161884659173</v>
+      </c>
+      <c r="W43">
+        <v>0.1777070989059869</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.7034007852746553</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1922874561847136</v>
+      </c>
+      <c r="C44">
+        <v>6.155292806284056</v>
+      </c>
+      <c r="D44">
+        <v>14.13789280628406</v>
+      </c>
+      <c r="E44">
+        <v>9.342599999999999</v>
+      </c>
+      <c r="F44">
+        <v>9.672599999999999</v>
+      </c>
+      <c r="G44">
+        <v>1.69</v>
+      </c>
+      <c r="H44">
+        <v>22.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.61</v>
+      </c>
+      <c r="K44">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L44">
+        <v>1.42</v>
+      </c>
+      <c r="M44">
+        <v>2.06800188</v>
+      </c>
+      <c r="N44">
+        <v>-0.6480018799999998</v>
+      </c>
+      <c r="O44">
+        <v>-0.1555204511999999</v>
+      </c>
+      <c r="P44">
+        <v>-0.4924814287999999</v>
+      </c>
+      <c r="Q44">
+        <v>-0.3024814287999997</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2022233545401017</v>
+      </c>
+      <c r="T44">
+        <v>2.047041166818008</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.164796755407205</v>
+      </c>
+      <c r="W44">
+        <v>0.1785664536939396</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.6866531475300206</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1940374561847136</v>
+      </c>
+      <c r="C45">
+        <v>5.76561559785082</v>
+      </c>
+      <c r="D45">
+        <v>13.97851559785082</v>
+      </c>
+      <c r="E45">
+        <v>9.572899999999999</v>
+      </c>
+      <c r="F45">
+        <v>9.902899999999999</v>
+      </c>
+      <c r="G45">
+        <v>1.69</v>
+      </c>
+      <c r="H45">
+        <v>22.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.61</v>
+      </c>
+      <c r="K45">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L45">
+        <v>1.42</v>
+      </c>
+      <c r="M45">
+        <v>2.11724002</v>
+      </c>
+      <c r="N45">
+        <v>-0.6972400199999997</v>
+      </c>
+      <c r="O45">
+        <v>-0.1673376047999999</v>
+      </c>
+      <c r="P45">
+        <v>-0.5299024151999998</v>
+      </c>
+      <c r="Q45">
+        <v>-0.3399024151999996</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.205090430935542</v>
+      </c>
+      <c r="T45">
+        <v>2.08295416974464</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1609642727233165</v>
+      </c>
+      <c r="W45">
+        <v>0.1793858384917549</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.6706844696804853</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1957874561847136</v>
+      </c>
+      <c r="C46">
+        <v>5.379491668406059</v>
+      </c>
+      <c r="D46">
+        <v>13.82269166840606</v>
+      </c>
+      <c r="E46">
+        <v>9.803199999999999</v>
+      </c>
+      <c r="F46">
+        <v>10.1332</v>
+      </c>
+      <c r="G46">
+        <v>1.69</v>
+      </c>
+      <c r="H46">
+        <v>22.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.61</v>
+      </c>
+      <c r="K46">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L46">
+        <v>1.42</v>
+      </c>
+      <c r="M46">
+        <v>2.16647816</v>
+      </c>
+      <c r="N46">
+        <v>-0.7464781599999997</v>
+      </c>
+      <c r="O46">
+        <v>-0.1791547583999999</v>
+      </c>
+      <c r="P46">
+        <v>-0.5673234015999997</v>
+      </c>
+      <c r="Q46">
+        <v>-0.3773234015999996</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2080599029165338</v>
+      </c>
+      <c r="T46">
+        <v>2.120149779918651</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1573059937977866</v>
+      </c>
+      <c r="W46">
+        <v>0.1801679785260332</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6554416408241106</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1975374561847136</v>
+      </c>
+      <c r="C47">
+        <v>4.996803498650067</v>
+      </c>
+      <c r="D47">
+        <v>13.67030349865007</v>
+      </c>
+      <c r="E47">
+        <v>10.0335</v>
+      </c>
+      <c r="F47">
+        <v>10.3635</v>
+      </c>
+      <c r="G47">
+        <v>1.69</v>
+      </c>
+      <c r="H47">
+        <v>22.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.61</v>
+      </c>
+      <c r="K47">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L47">
+        <v>1.42</v>
+      </c>
+      <c r="M47">
+        <v>2.2157163</v>
+      </c>
+      <c r="N47">
+        <v>-0.7957162999999996</v>
+      </c>
+      <c r="O47">
+        <v>-0.1909719119999999</v>
+      </c>
+      <c r="P47">
+        <v>-0.6047443879999996</v>
+      </c>
+      <c r="Q47">
+        <v>-0.4147443879999995</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2111373556968345</v>
+      </c>
+      <c r="T47">
+        <v>2.158697957735354</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1538103050467246</v>
+      </c>
+      <c r="W47">
+        <v>0.1809153567810103</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6408762710280194</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1992874561847136</v>
+      </c>
+      <c r="C48">
+        <v>4.617438695136057</v>
+      </c>
+      <c r="D48">
+        <v>13.52123869513606</v>
+      </c>
+      <c r="E48">
+        <v>10.2638</v>
+      </c>
+      <c r="F48">
+        <v>10.5938</v>
+      </c>
+      <c r="G48">
+        <v>1.69</v>
+      </c>
+      <c r="H48">
+        <v>22.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.61</v>
+      </c>
+      <c r="K48">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L48">
+        <v>1.42</v>
+      </c>
+      <c r="M48">
+        <v>2.26495444</v>
+      </c>
+      <c r="N48">
+        <v>-0.84495444</v>
+      </c>
+      <c r="O48">
+        <v>-0.2027890656</v>
+      </c>
+      <c r="P48">
+        <v>-0.6421653744</v>
+      </c>
+      <c r="Q48">
+        <v>-0.4521653743999998</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2143287882097388</v>
+      </c>
+      <c r="T48">
+        <v>2.198673845841564</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1504666027631002</v>
+      </c>
+      <c r="W48">
+        <v>0.1816302403292492</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.626944178179584</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2010374561847136</v>
+      </c>
+      <c r="C49">
+        <v>4.241289713816057</v>
+      </c>
+      <c r="D49">
+        <v>13.37538971381606</v>
+      </c>
+      <c r="E49">
+        <v>10.4941</v>
+      </c>
+      <c r="F49">
+        <v>10.8241</v>
+      </c>
+      <c r="G49">
+        <v>1.69</v>
+      </c>
+      <c r="H49">
+        <v>22.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.61</v>
+      </c>
+      <c r="K49">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L49">
+        <v>1.42</v>
+      </c>
+      <c r="M49">
+        <v>2.31419258</v>
+      </c>
+      <c r="N49">
+        <v>-0.8941925799999999</v>
+      </c>
+      <c r="O49">
+        <v>-0.2146062192</v>
+      </c>
+      <c r="P49">
+        <v>-0.6795863607999999</v>
+      </c>
+      <c r="Q49">
+        <v>-0.4895863607999997</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2176406521382245</v>
+      </c>
+      <c r="T49">
+        <v>2.240158258027254</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1472651856830342</v>
+      </c>
+      <c r="W49">
+        <v>0.1823147033009673</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6136049403459759</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2027874561847136</v>
+      </c>
+      <c r="C50">
+        <v>3.868253601287964</v>
+      </c>
+      <c r="D50">
+        <v>13.23265360128796</v>
+      </c>
+      <c r="E50">
+        <v>10.7244</v>
+      </c>
+      <c r="F50">
+        <v>11.0544</v>
+      </c>
+      <c r="G50">
+        <v>1.69</v>
+      </c>
+      <c r="H50">
+        <v>22.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.61</v>
+      </c>
+      <c r="K50">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L50">
+        <v>1.42</v>
+      </c>
+      <c r="M50">
+        <v>2.363430719999999</v>
+      </c>
+      <c r="N50">
+        <v>-0.9434307199999994</v>
+      </c>
+      <c r="O50">
+        <v>-0.2264233727999999</v>
+      </c>
+      <c r="P50">
+        <v>-0.7170073471999996</v>
+      </c>
+      <c r="Q50">
+        <v>-0.5270073471999994</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2210798954485749</v>
+      </c>
+      <c r="T50">
+        <v>2.283238224527778</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1441971609813044</v>
+      </c>
+      <c r="W50">
+        <v>0.1829706469821971</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6008215040887681</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2045374561847136</v>
+      </c>
+      <c r="C51">
+        <v>3.498231752435366</v>
+      </c>
+      <c r="D51">
+        <v>13.09293175243537</v>
+      </c>
+      <c r="E51">
+        <v>10.9547</v>
+      </c>
+      <c r="F51">
+        <v>11.2847</v>
+      </c>
+      <c r="G51">
+        <v>1.69</v>
+      </c>
+      <c r="H51">
+        <v>22.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.61</v>
+      </c>
+      <c r="K51">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L51">
+        <v>1.42</v>
+      </c>
+      <c r="M51">
+        <v>2.41266886</v>
+      </c>
+      <c r="N51">
+        <v>-0.9926688599999998</v>
+      </c>
+      <c r="O51">
+        <v>-0.2382405263999999</v>
+      </c>
+      <c r="P51">
+        <v>-0.7544283335999998</v>
+      </c>
+      <c r="Q51">
+        <v>-0.5644283335999997</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2246540110456058</v>
+      </c>
+      <c r="T51">
+        <v>2.328007601479303</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1412543617776043</v>
+      </c>
+      <c r="W51">
+        <v>0.1835998174519482</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5885598407400177</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2062874561847136</v>
+      </c>
+      <c r="C52">
+        <v>3.131129683261346</v>
+      </c>
+      <c r="D52">
+        <v>12.95612968326135</v>
+      </c>
+      <c r="E52">
+        <v>11.185</v>
+      </c>
+      <c r="F52">
+        <v>11.515</v>
+      </c>
+      <c r="G52">
+        <v>1.69</v>
+      </c>
+      <c r="H52">
+        <v>22.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.61</v>
+      </c>
+      <c r="K52">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L52">
+        <v>1.42</v>
+      </c>
+      <c r="M52">
+        <v>2.461907</v>
+      </c>
+      <c r="N52">
+        <v>-1.041907</v>
+      </c>
+      <c r="O52">
+        <v>-0.2500576799999999</v>
+      </c>
+      <c r="P52">
+        <v>-0.7918493199999999</v>
+      </c>
+      <c r="Q52">
+        <v>-0.6018493199999997</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2283710912665179</v>
+      </c>
+      <c r="T52">
+        <v>2.374567753508889</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1384292745420521</v>
+      </c>
+      <c r="W52">
+        <v>0.1842038211029093</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5767886439252174</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2080374561847136</v>
+      </c>
+      <c r="C53">
+        <v>2.766856817816237</v>
+      </c>
+      <c r="D53">
+        <v>12.82215681781624</v>
+      </c>
+      <c r="E53">
+        <v>11.4153</v>
+      </c>
+      <c r="F53">
+        <v>11.7453</v>
+      </c>
+      <c r="G53">
+        <v>1.69</v>
+      </c>
+      <c r="H53">
+        <v>22.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.61</v>
+      </c>
+      <c r="K53">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L53">
+        <v>1.42</v>
+      </c>
+      <c r="M53">
+        <v>2.51114514</v>
+      </c>
+      <c r="N53">
+        <v>-1.09114514</v>
+      </c>
+      <c r="O53">
+        <v>-0.2618748335999999</v>
+      </c>
+      <c r="P53">
+        <v>-0.8292703063999998</v>
+      </c>
+      <c r="Q53">
+        <v>-0.6392703063999996</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2322398890474673</v>
+      </c>
+      <c r="T53">
+        <v>2.42302831990703</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1357149750412276</v>
+      </c>
+      <c r="W53">
+        <v>0.1847841383361855</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5654790626717818</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2097874561847136</v>
+      </c>
+      <c r="C54">
+        <v>2.405326288209793</v>
+      </c>
+      <c r="D54">
+        <v>12.69092628820979</v>
+      </c>
+      <c r="E54">
+        <v>11.6456</v>
+      </c>
+      <c r="F54">
+        <v>11.9756</v>
+      </c>
+      <c r="G54">
+        <v>1.69</v>
+      </c>
+      <c r="H54">
+        <v>22.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.61</v>
+      </c>
+      <c r="K54">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L54">
+        <v>1.42</v>
+      </c>
+      <c r="M54">
+        <v>2.56038328</v>
+      </c>
+      <c r="N54">
+        <v>-1.14038328</v>
+      </c>
+      <c r="O54">
+        <v>-0.2736919872</v>
+      </c>
+      <c r="P54">
+        <v>-0.8666912928</v>
+      </c>
+      <c r="Q54">
+        <v>-0.6766912927999998</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2362698867359562</v>
+      </c>
+      <c r="T54">
+        <v>2.47350807657176</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1331050716750501</v>
+      </c>
+      <c r="W54">
+        <v>0.1853421356758743</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5546044653127089</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2115374561847136</v>
+      </c>
+      <c r="C55">
+        <v>2.046454746779785</v>
+      </c>
+      <c r="D55">
+        <v>12.56235474677979</v>
+      </c>
+      <c r="E55">
+        <v>11.8759</v>
+      </c>
+      <c r="F55">
+        <v>12.2059</v>
+      </c>
+      <c r="G55">
+        <v>1.69</v>
+      </c>
+      <c r="H55">
+        <v>22.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.61</v>
+      </c>
+      <c r="K55">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L55">
+        <v>1.42</v>
+      </c>
+      <c r="M55">
+        <v>2.60962142</v>
+      </c>
+      <c r="N55">
+        <v>-1.18962142</v>
+      </c>
+      <c r="O55">
+        <v>-0.2855091407999999</v>
+      </c>
+      <c r="P55">
+        <v>-0.9041122792</v>
+      </c>
+      <c r="Q55">
+        <v>-0.7141122791999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.240471373687785</v>
+      </c>
+      <c r="T55">
+        <v>2.52613590798818</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1305936552283511</v>
+      </c>
+      <c r="W55">
+        <v>0.1858790765121785</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5441402301181295</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2132874561847136</v>
+      </c>
+      <c r="C56">
+        <v>1.690162189563567</v>
+      </c>
+      <c r="D56">
+        <v>12.43636218956357</v>
+      </c>
+      <c r="E56">
+        <v>12.1062</v>
+      </c>
+      <c r="F56">
+        <v>12.4362</v>
+      </c>
+      <c r="G56">
+        <v>1.69</v>
+      </c>
+      <c r="H56">
+        <v>22.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.61</v>
+      </c>
+      <c r="K56">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L56">
+        <v>1.42</v>
+      </c>
+      <c r="M56">
+        <v>2.65885956</v>
+      </c>
+      <c r="N56">
+        <v>-1.23885956</v>
+      </c>
+      <c r="O56">
+        <v>-0.2973262944</v>
+      </c>
+      <c r="P56">
+        <v>-0.9415332655999999</v>
+      </c>
+      <c r="Q56">
+        <v>-0.7515332655999998</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2448555339853456</v>
+      </c>
+      <c r="T56">
+        <v>2.581051905987924</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.1281752542056038</v>
+      </c>
+      <c r="W56">
+        <v>0.1863961306508419</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.534063559190016</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2150374561847136</v>
+      </c>
+      <c r="C57">
+        <v>1.336371790287004</v>
+      </c>
+      <c r="D57">
+        <v>12.312871790287</v>
+      </c>
+      <c r="E57">
+        <v>12.3365</v>
+      </c>
+      <c r="F57">
+        <v>12.6665</v>
+      </c>
+      <c r="G57">
+        <v>1.69</v>
+      </c>
+      <c r="H57">
+        <v>22.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.61</v>
+      </c>
+      <c r="K57">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L57">
+        <v>1.42</v>
+      </c>
+      <c r="M57">
+        <v>2.7080977</v>
+      </c>
+      <c r="N57">
+        <v>-1.2880977</v>
+      </c>
+      <c r="O57">
+        <v>-0.3091434479999999</v>
+      </c>
+      <c r="P57">
+        <v>-0.9789542519999999</v>
+      </c>
+      <c r="Q57">
+        <v>-0.7889542519999997</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2494345458516866</v>
+      </c>
+      <c r="T57">
+        <v>2.638408615009878</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1258447950382292</v>
+      </c>
+      <c r="W57">
+        <v>0.1868943828208266</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5243533126592885</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2167874561847136</v>
+      </c>
+      <c r="C58">
+        <v>0.9850097441468506</v>
+      </c>
+      <c r="D58">
+        <v>12.19180974414685</v>
+      </c>
+      <c r="E58">
+        <v>12.5668</v>
+      </c>
+      <c r="F58">
+        <v>12.8968</v>
+      </c>
+      <c r="G58">
+        <v>1.69</v>
+      </c>
+      <c r="H58">
+        <v>22.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.61</v>
+      </c>
+      <c r="K58">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L58">
+        <v>1.42</v>
+      </c>
+      <c r="M58">
+        <v>2.75733584</v>
+      </c>
+      <c r="N58">
+        <v>-1.33733584</v>
+      </c>
+      <c r="O58">
+        <v>-0.3209606016</v>
+      </c>
+      <c r="P58">
+        <v>-1.0163752384</v>
+      </c>
+      <c r="Q58">
+        <v>-0.8263752384</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.254221694621043</v>
+      </c>
+      <c r="T58">
+        <v>2.698372447169192</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1235975665554037</v>
+      </c>
+      <c r="W58">
+        <v>0.1873748402704547</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5149898606475154</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2185374561847136</v>
+      </c>
+      <c r="C59">
+        <v>0.6360051207191635</v>
+      </c>
+      <c r="D59">
+        <v>12.07310512071916</v>
+      </c>
+      <c r="E59">
+        <v>12.7971</v>
+      </c>
+      <c r="F59">
+        <v>13.1271</v>
+      </c>
+      <c r="G59">
+        <v>1.69</v>
+      </c>
+      <c r="H59">
+        <v>22.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.61</v>
+      </c>
+      <c r="K59">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L59">
+        <v>1.42</v>
+      </c>
+      <c r="M59">
+        <v>2.80657398</v>
+      </c>
+      <c r="N59">
+        <v>-1.38657398</v>
+      </c>
+      <c r="O59">
+        <v>-0.3327777552</v>
+      </c>
+      <c r="P59">
+        <v>-1.0537962248</v>
+      </c>
+      <c r="Q59">
+        <v>-0.8637962248</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2592315014726953</v>
+      </c>
+      <c r="T59">
+        <v>2.761125294777779</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1214291881947826</v>
+      </c>
+      <c r="W59">
+        <v>0.1878384395639555</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5059549508115941</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2355253539631683</v>
+      </c>
+      <c r="C60">
+        <v>-0.6368482234609374</v>
+      </c>
+      <c r="D60">
+        <v>11.03055177653906</v>
+      </c>
+      <c r="E60">
+        <v>13.0274</v>
+      </c>
+      <c r="F60">
+        <v>13.3574</v>
+      </c>
+      <c r="G60">
+        <v>1.69</v>
+      </c>
+      <c r="H60">
+        <v>22.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.61</v>
+      </c>
+      <c r="K60">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L60">
+        <v>1.42</v>
+      </c>
+      <c r="M60">
+        <v>3.18974712</v>
+      </c>
+      <c r="N60">
+        <v>-1.76974712</v>
+      </c>
+      <c r="O60">
+        <v>-0.4247393087999999</v>
+      </c>
+      <c r="P60">
+        <v>-1.3450078112</v>
+      </c>
+      <c r="Q60">
+        <v>-1.1550078112</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2662367700278897</v>
+      </c>
+      <c r="T60">
+        <v>2.848873298467054</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.1068423254819021</v>
+      </c>
+      <c r="W60">
+        <v>0.2132860526749218</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4451763561745923</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2375253539631683</v>
+      </c>
+      <c r="C61">
+        <v>-0.9781612528158483</v>
+      </c>
+      <c r="D61">
+        <v>10.91953874718415</v>
+      </c>
+      <c r="E61">
+        <v>13.2577</v>
+      </c>
+      <c r="F61">
+        <v>13.5877</v>
+      </c>
+      <c r="G61">
+        <v>1.69</v>
+      </c>
+      <c r="H61">
+        <v>22.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.61</v>
+      </c>
+      <c r="K61">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L61">
+        <v>1.42</v>
+      </c>
+      <c r="M61">
+        <v>3.24474276</v>
+      </c>
+      <c r="N61">
+        <v>-1.82474276</v>
+      </c>
+      <c r="O61">
+        <v>-0.4379382623999999</v>
+      </c>
+      <c r="P61">
+        <v>-1.3868044976</v>
+      </c>
+      <c r="Q61">
+        <v>-1.1968044976</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2717840083212528</v>
+      </c>
+      <c r="T61">
+        <v>2.918358013063811</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.1050314386093275</v>
+      </c>
+      <c r="W61">
+        <v>0.2137184924600926</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4376309942055314</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2395253539631683</v>
+      </c>
+      <c r="C62">
+        <v>-1.317262044859167</v>
+      </c>
+      <c r="D62">
+        <v>10.81073795514083</v>
+      </c>
+      <c r="E62">
+        <v>13.488</v>
+      </c>
+      <c r="F62">
+        <v>13.818</v>
+      </c>
+      <c r="G62">
+        <v>1.69</v>
+      </c>
+      <c r="H62">
+        <v>22.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.61</v>
+      </c>
+      <c r="K62">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L62">
+        <v>1.42</v>
+      </c>
+      <c r="M62">
+        <v>3.2997384</v>
+      </c>
+      <c r="N62">
+        <v>-1.8797384</v>
+      </c>
+      <c r="O62">
+        <v>-0.451137216</v>
+      </c>
+      <c r="P62">
+        <v>-1.428601184</v>
+      </c>
+      <c r="Q62">
+        <v>-1.238601184</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2776086085292842</v>
+      </c>
+      <c r="T62">
+        <v>2.991316963390407</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.1032809146325054</v>
+      </c>
+      <c r="W62">
+        <v>0.2141365175857577</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.4303371443021059</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2415253539631683</v>
+      </c>
+      <c r="C63">
+        <v>-1.654216074498745</v>
+      </c>
+      <c r="D63">
+        <v>10.70408392550125</v>
+      </c>
+      <c r="E63">
+        <v>13.7183</v>
+      </c>
+      <c r="F63">
+        <v>14.0483</v>
+      </c>
+      <c r="G63">
+        <v>1.69</v>
+      </c>
+      <c r="H63">
+        <v>22.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.61</v>
+      </c>
+      <c r="K63">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L63">
+        <v>1.42</v>
+      </c>
+      <c r="M63">
+        <v>3.354734039999999</v>
+      </c>
+      <c r="N63">
+        <v>-1.934734039999999</v>
+      </c>
+      <c r="O63">
+        <v>-0.4643361695999998</v>
+      </c>
+      <c r="P63">
+        <v>-1.4703978704</v>
+      </c>
+      <c r="Q63">
+        <v>-1.280397870399999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2837319061838812</v>
+      </c>
+      <c r="T63">
+        <v>3.068017398349136</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.1015877848844316</v>
+      </c>
+      <c r="W63">
+        <v>0.2145408369695977</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4232824370184649</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2435253539631683</v>
+      </c>
+      <c r="C64">
+        <v>-1.989086258096297</v>
+      </c>
+      <c r="D64">
+        <v>10.5995137419037</v>
+      </c>
+      <c r="E64">
+        <v>13.9486</v>
+      </c>
+      <c r="F64">
+        <v>14.2786</v>
+      </c>
+      <c r="G64">
+        <v>1.69</v>
+      </c>
+      <c r="H64">
+        <v>22.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.61</v>
+      </c>
+      <c r="K64">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L64">
+        <v>1.42</v>
+      </c>
+      <c r="M64">
+        <v>3.40972968</v>
+      </c>
+      <c r="N64">
+        <v>-1.98972968</v>
+      </c>
+      <c r="O64">
+        <v>-0.4775351232</v>
+      </c>
+      <c r="P64">
+        <v>-1.5121945568</v>
+      </c>
+      <c r="Q64">
+        <v>-1.3221945568</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2901774826624043</v>
+      </c>
+      <c r="T64">
+        <v>3.148754698305691</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.09994927222500523</v>
+      </c>
+      <c r="W64">
+        <v>0.2149321137926687</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4164553009375218</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2455253539631683</v>
+      </c>
+      <c r="C65">
+        <v>-2.321933077232885</v>
+      </c>
+      <c r="D65">
+        <v>10.49696692276711</v>
+      </c>
+      <c r="E65">
+        <v>14.1789</v>
+      </c>
+      <c r="F65">
+        <v>14.5089</v>
+      </c>
+      <c r="G65">
+        <v>1.69</v>
+      </c>
+      <c r="H65">
+        <v>22.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.61</v>
+      </c>
+      <c r="K65">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L65">
+        <v>1.42</v>
+      </c>
+      <c r="M65">
+        <v>3.46472532</v>
+      </c>
+      <c r="N65">
+        <v>-2.04472532</v>
+      </c>
+      <c r="O65">
+        <v>-0.4907340768</v>
+      </c>
+      <c r="P65">
+        <v>-1.5539912432</v>
+      </c>
+      <c r="Q65">
+        <v>-1.3639912432</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2969714686803072</v>
+      </c>
+      <c r="T65">
+        <v>3.233856176638278</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.09836277584048134</v>
+      </c>
+      <c r="W65">
+        <v>0.2153109691292931</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.409844899335339</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2475253539631683</v>
+      </c>
+      <c r="C66">
+        <v>-2.652814695358868</v>
+      </c>
+      <c r="D66">
+        <v>10.39638530464113</v>
+      </c>
+      <c r="E66">
+        <v>14.4092</v>
+      </c>
+      <c r="F66">
+        <v>14.7392</v>
+      </c>
+      <c r="G66">
+        <v>1.69</v>
+      </c>
+      <c r="H66">
+        <v>22.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.61</v>
+      </c>
+      <c r="K66">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L66">
+        <v>1.42</v>
+      </c>
+      <c r="M66">
+        <v>3.51972096</v>
+      </c>
+      <c r="N66">
+        <v>-2.09972096</v>
+      </c>
+      <c r="O66">
+        <v>-0.5039330303999999</v>
+      </c>
+      <c r="P66">
+        <v>-1.5957879296</v>
+      </c>
+      <c r="Q66">
+        <v>-1.4057879296</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3041428983658713</v>
+      </c>
+      <c r="T66">
+        <v>3.32368551487823</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.09682585746797383</v>
+      </c>
+      <c r="W66">
+        <v>0.2156779852366479</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4034410727832243</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2495253539631683</v>
+      </c>
+      <c r="C67">
+        <v>-2.981787067801132</v>
+      </c>
+      <c r="D67">
+        <v>10.29771293219887</v>
+      </c>
+      <c r="E67">
+        <v>14.6395</v>
+      </c>
+      <c r="F67">
+        <v>14.9695</v>
+      </c>
+      <c r="G67">
+        <v>1.69</v>
+      </c>
+      <c r="H67">
+        <v>22.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.61</v>
+      </c>
+      <c r="K67">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L67">
+        <v>1.42</v>
+      </c>
+      <c r="M67">
+        <v>3.5747166</v>
+      </c>
+      <c r="N67">
+        <v>-2.1547166</v>
+      </c>
+      <c r="O67">
+        <v>-0.5171319839999999</v>
+      </c>
+      <c r="P67">
+        <v>-1.637584616</v>
+      </c>
+      <c r="Q67">
+        <v>-1.447584616</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3117241240334677</v>
+      </c>
+      <c r="T67">
+        <v>3.418647958160466</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.09533622889154345</v>
+      </c>
+      <c r="W67">
+        <v>0.2160337085406994</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3972342870480977</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2515253539631683</v>
+      </c>
+      <c r="C68">
+        <v>-3.308904045564699</v>
+      </c>
+      <c r="D68">
+        <v>10.2008959544353</v>
+      </c>
+      <c r="E68">
+        <v>14.8698</v>
+      </c>
+      <c r="F68">
+        <v>15.1998</v>
+      </c>
+      <c r="G68">
+        <v>1.69</v>
+      </c>
+      <c r="H68">
+        <v>22.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.61</v>
+      </c>
+      <c r="K68">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L68">
+        <v>1.42</v>
+      </c>
+      <c r="M68">
+        <v>3.62971224</v>
+      </c>
+      <c r="N68">
+        <v>-2.20971224</v>
+      </c>
+      <c r="O68">
+        <v>-0.5303309375999999</v>
+      </c>
+      <c r="P68">
+        <v>-1.6793813024</v>
+      </c>
+      <c r="Q68">
+        <v>-1.4893813024</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.319751304152099</v>
+      </c>
+      <c r="T68">
+        <v>3.519196427518126</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.09389174057500492</v>
+      </c>
+      <c r="W68">
+        <v>0.2163786523506888</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3912155857291871</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2535253539631683</v>
+      </c>
+      <c r="C69">
+        <v>-3.634217473333317</v>
+      </c>
+      <c r="D69">
+        <v>10.10588252666668</v>
+      </c>
+      <c r="E69">
+        <v>15.1001</v>
+      </c>
+      <c r="F69">
+        <v>15.4301</v>
+      </c>
+      <c r="G69">
+        <v>1.69</v>
+      </c>
+      <c r="H69">
+        <v>22.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.61</v>
+      </c>
+      <c r="K69">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L69">
+        <v>1.42</v>
+      </c>
+      <c r="M69">
+        <v>3.68470788</v>
+      </c>
+      <c r="N69">
+        <v>-2.26470788</v>
+      </c>
+      <c r="O69">
+        <v>-0.5435298911999999</v>
+      </c>
+      <c r="P69">
+        <v>-1.7211779888</v>
+      </c>
+      <c r="Q69">
+        <v>-1.5311779888</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.328264980035496</v>
+      </c>
+      <c r="T69">
+        <v>3.625838743503525</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.09249037131269142</v>
+      </c>
+      <c r="W69">
+        <v>0.2167132993305293</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3853765471362142</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2555253539631683</v>
+      </c>
+      <c r="C70">
+        <v>-3.957777282043875</v>
+      </c>
+      <c r="D70">
+        <v>10.01262271795613</v>
+      </c>
+      <c r="E70">
+        <v>15.3304</v>
+      </c>
+      <c r="F70">
+        <v>15.6604</v>
+      </c>
+      <c r="G70">
+        <v>1.69</v>
+      </c>
+      <c r="H70">
+        <v>22.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.61</v>
+      </c>
+      <c r="K70">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L70">
+        <v>1.42</v>
+      </c>
+      <c r="M70">
+        <v>3.73970352</v>
+      </c>
+      <c r="N70">
+        <v>-2.31970352</v>
+      </c>
+      <c r="O70">
+        <v>-0.5567288448</v>
+      </c>
+      <c r="P70">
+        <v>-1.7629746752</v>
+      </c>
+      <c r="Q70">
+        <v>-1.5729746752</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3373107606616053</v>
+      </c>
+      <c r="T70">
+        <v>3.73914620423801</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.09113021879338712</v>
+      </c>
+      <c r="W70">
+        <v>0.2170381037521392</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3797092449724464</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2575253539631683</v>
+      </c>
+      <c r="C71">
+        <v>-4.279631576381806</v>
+      </c>
+      <c r="D71">
+        <v>9.921068423618193</v>
+      </c>
+      <c r="E71">
+        <v>15.5607</v>
+      </c>
+      <c r="F71">
+        <v>15.8907</v>
+      </c>
+      <c r="G71">
+        <v>1.69</v>
+      </c>
+      <c r="H71">
+        <v>22.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.61</v>
+      </c>
+      <c r="K71">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L71">
+        <v>1.42</v>
+      </c>
+      <c r="M71">
+        <v>3.79469916</v>
+      </c>
+      <c r="N71">
+        <v>-2.37469916</v>
+      </c>
+      <c r="O71">
+        <v>-0.5699277984</v>
+      </c>
+      <c r="P71">
+        <v>-1.8047713616</v>
+      </c>
+      <c r="Q71">
+        <v>-1.6147713616</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3469401400377861</v>
+      </c>
+      <c r="T71">
+        <v>3.859763823729558</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0898094909847873</v>
+      </c>
+      <c r="W71">
+        <v>0.2173534935528328</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3742062124366138</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2595253539631683</v>
+      </c>
+      <c r="C72">
+        <v>-4.599826717519727</v>
+      </c>
+      <c r="D72">
+        <v>9.831173282480272</v>
+      </c>
+      <c r="E72">
+        <v>15.791</v>
+      </c>
+      <c r="F72">
+        <v>16.121</v>
+      </c>
+      <c r="G72">
+        <v>1.69</v>
+      </c>
+      <c r="H72">
+        <v>22.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.61</v>
+      </c>
+      <c r="K72">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L72">
+        <v>1.42</v>
+      </c>
+      <c r="M72">
+        <v>3.8496948</v>
+      </c>
+      <c r="N72">
+        <v>-2.4296948</v>
+      </c>
+      <c r="O72">
+        <v>-0.583126752</v>
+      </c>
+      <c r="P72">
+        <v>-1.846568048</v>
+      </c>
+      <c r="Q72">
+        <v>-1.656568048</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3572114780390456</v>
+      </c>
+      <c r="T72">
+        <v>3.988422617853877</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0885264982564332</v>
+      </c>
+      <c r="W72">
+        <v>0.2176598722163638</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.368860409401805</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2615253539631683</v>
+      </c>
+      <c r="C73">
+        <v>-4.918407401398275</v>
+      </c>
+      <c r="D73">
+        <v>9.742892598601724</v>
+      </c>
+      <c r="E73">
+        <v>16.0213</v>
+      </c>
+      <c r="F73">
+        <v>16.3513</v>
+      </c>
+      <c r="G73">
+        <v>1.69</v>
+      </c>
+      <c r="H73">
+        <v>22.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.61</v>
+      </c>
+      <c r="K73">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L73">
+        <v>1.42</v>
+      </c>
+      <c r="M73">
+        <v>3.90469044</v>
+      </c>
+      <c r="N73">
+        <v>-2.48469044</v>
+      </c>
+      <c r="O73">
+        <v>-0.5963257056</v>
+      </c>
+      <c r="P73">
+        <v>-1.8883647344</v>
+      </c>
+      <c r="Q73">
+        <v>-1.6983647344</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.368191184178323</v>
+      </c>
+      <c r="T73">
+        <v>4.12595443226263</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.08727964616831442</v>
+      </c>
+      <c r="W73">
+        <v>0.2179576204950065</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3636651923679768</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2635253539631683</v>
+      </c>
+      <c r="C74">
+        <v>-5.235416732826879</v>
+      </c>
+      <c r="D74">
+        <v>9.65618326717312</v>
+      </c>
+      <c r="E74">
+        <v>16.2516</v>
+      </c>
+      <c r="F74">
+        <v>16.5816</v>
+      </c>
+      <c r="G74">
+        <v>1.69</v>
+      </c>
+      <c r="H74">
+        <v>22.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.61</v>
+      </c>
+      <c r="K74">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L74">
+        <v>1.42</v>
+      </c>
+      <c r="M74">
+        <v>3.95968608</v>
+      </c>
+      <c r="N74">
+        <v>-2.53968608</v>
+      </c>
+      <c r="O74">
+        <v>-0.6095246591999999</v>
+      </c>
+      <c r="P74">
+        <v>-1.9301614208</v>
+      </c>
+      <c r="Q74">
+        <v>-1.7401614208</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3799551550418345</v>
+      </c>
+      <c r="T74">
+        <v>4.273309947700581</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.08606742886042118</v>
+      </c>
+      <c r="W74">
+        <v>0.2182470979881314</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3586142869184216</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2655253539631683</v>
+      </c>
+      <c r="C75">
+        <v>-5.550896295662556</v>
+      </c>
+      <c r="D75">
+        <v>9.571003704337443</v>
+      </c>
+      <c r="E75">
+        <v>16.4819</v>
+      </c>
+      <c r="F75">
+        <v>16.8119</v>
+      </c>
+      <c r="G75">
+        <v>1.69</v>
+      </c>
+      <c r="H75">
+        <v>22.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.61</v>
+      </c>
+      <c r="K75">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L75">
+        <v>1.42</v>
+      </c>
+      <c r="M75">
+        <v>4.01468172</v>
+      </c>
+      <c r="N75">
+        <v>-2.59468172</v>
+      </c>
+      <c r="O75">
+        <v>-0.6227236127999999</v>
+      </c>
+      <c r="P75">
+        <v>-1.9719581072</v>
+      </c>
+      <c r="Q75">
+        <v>-1.7819581072</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.392590531154495</v>
+      </c>
+      <c r="T75">
+        <v>4.431580686504306</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0848884229856209</v>
+      </c>
+      <c r="W75">
+        <v>0.2185286445910337</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.353701762440087</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2675253539631683</v>
+      </c>
+      <c r="C76">
+        <v>-5.864886219306776</v>
+      </c>
+      <c r="D76">
+        <v>9.487313780693222</v>
+      </c>
+      <c r="E76">
+        <v>16.7122</v>
+      </c>
+      <c r="F76">
+        <v>17.0422</v>
+      </c>
+      <c r="G76">
+        <v>1.69</v>
+      </c>
+      <c r="H76">
+        <v>22.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.61</v>
+      </c>
+      <c r="K76">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L76">
+        <v>1.42</v>
+      </c>
+      <c r="M76">
+        <v>4.06967736</v>
+      </c>
+      <c r="N76">
+        <v>-2.64967736</v>
+      </c>
+      <c r="O76">
+        <v>-0.6359225664</v>
+      </c>
+      <c r="P76">
+        <v>-2.0137547936</v>
+      </c>
+      <c r="Q76">
+        <v>-1.8237547936</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4061978592758218</v>
+      </c>
+      <c r="T76">
+        <v>4.602026097523703</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.08374128213446384</v>
+      </c>
+      <c r="W76">
+        <v>0.21880258182629</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3489220088935994</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2695253539631683</v>
+      </c>
+      <c r="C77">
+        <v>-6.177425241743883</v>
+      </c>
+      <c r="D77">
+        <v>9.405074758256115</v>
+      </c>
+      <c r="E77">
+        <v>16.9425</v>
+      </c>
+      <c r="F77">
+        <v>17.2725</v>
+      </c>
+      <c r="G77">
+        <v>1.69</v>
+      </c>
+      <c r="H77">
+        <v>22.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.61</v>
+      </c>
+      <c r="K77">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L77">
+        <v>1.42</v>
+      </c>
+      <c r="M77">
+        <v>4.124673</v>
+      </c>
+      <c r="N77">
+        <v>-2.704673</v>
+      </c>
+      <c r="O77">
+        <v>-0.6491215199999999</v>
+      </c>
+      <c r="P77">
+        <v>-2.05555148</v>
+      </c>
+      <c r="Q77">
+        <v>-1.865551479999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4208937736468547</v>
+      </c>
+      <c r="T77">
+        <v>4.786107141424651</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.08262473170600433</v>
+      </c>
+      <c r="W77">
+        <v>0.2190692140686062</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3442697154416847</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2715253539631683</v>
+      </c>
+      <c r="C78">
+        <v>-6.488550769329024</v>
+      </c>
+      <c r="D78">
+        <v>9.324249230670974</v>
+      </c>
+      <c r="E78">
+        <v>17.1728</v>
+      </c>
+      <c r="F78">
+        <v>17.5028</v>
+      </c>
+      <c r="G78">
+        <v>1.69</v>
+      </c>
+      <c r="H78">
+        <v>22.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.61</v>
+      </c>
+      <c r="K78">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L78">
+        <v>1.42</v>
+      </c>
+      <c r="M78">
+        <v>4.179668639999999</v>
+      </c>
+      <c r="N78">
+        <v>-2.759668639999999</v>
+      </c>
+      <c r="O78">
+        <v>-0.6623204735999998</v>
+      </c>
+      <c r="P78">
+        <v>-2.097348166399999</v>
+      </c>
+      <c r="Q78">
+        <v>-1.907348166399999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4368143475488069</v>
+      </c>
+      <c r="T78">
+        <v>4.985528272317345</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.08153756418355691</v>
+      </c>
+      <c r="W78">
+        <v>0.2193288296729666</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3397398507648205</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2735253539631683</v>
+      </c>
+      <c r="C79">
+        <v>-6.79829893351954</v>
+      </c>
+      <c r="D79">
+        <v>9.244801066480461</v>
+      </c>
+      <c r="E79">
+        <v>17.4031</v>
+      </c>
+      <c r="F79">
+        <v>17.7331</v>
+      </c>
+      <c r="G79">
+        <v>1.69</v>
+      </c>
+      <c r="H79">
+        <v>22.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.61</v>
+      </c>
+      <c r="K79">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L79">
+        <v>1.42</v>
+      </c>
+      <c r="M79">
+        <v>4.234664280000001</v>
+      </c>
+      <c r="N79">
+        <v>-2.814664280000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.6755194272000001</v>
+      </c>
+      <c r="P79">
+        <v>-2.1391448528</v>
+      </c>
+      <c r="Q79">
+        <v>-1.9491448528</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4541193191813638</v>
+      </c>
+      <c r="T79">
+        <v>5.202290371113752</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.08047863477857563</v>
+      </c>
+      <c r="W79">
+        <v>0.2195817020148761</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3353276449107319</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2755253539631683</v>
+      </c>
+      <c r="C80">
+        <v>-7.106704644730506</v>
+      </c>
+      <c r="D80">
+        <v>9.166695355269495</v>
+      </c>
+      <c r="E80">
+        <v>17.6334</v>
+      </c>
+      <c r="F80">
+        <v>17.9634</v>
+      </c>
+      <c r="G80">
+        <v>1.69</v>
+      </c>
+      <c r="H80">
+        <v>22.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.61</v>
+      </c>
+      <c r="K80">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L80">
+        <v>1.42</v>
+      </c>
+      <c r="M80">
+        <v>4.28965992</v>
+      </c>
+      <c r="N80">
+        <v>-2.86965992</v>
+      </c>
+      <c r="O80">
+        <v>-0.6887183808</v>
+      </c>
+      <c r="P80">
+        <v>-2.1809415392</v>
+      </c>
+      <c r="Q80">
+        <v>-1.9909415392</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4729974700532441</v>
+      </c>
+      <c r="T80">
+        <v>5.438758115255287</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07944685740961954</v>
+      </c>
+      <c r="W80">
+        <v>0.2198280904505829</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3310285725400814</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2775253539631683</v>
+      </c>
+      <c r="C81">
+        <v>-7.413801643483172</v>
+      </c>
+      <c r="D81">
+        <v>9.089898356516828</v>
+      </c>
+      <c r="E81">
+        <v>17.8637</v>
+      </c>
+      <c r="F81">
+        <v>18.1937</v>
+      </c>
+      <c r="G81">
+        <v>1.69</v>
+      </c>
+      <c r="H81">
+        <v>22.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.61</v>
+      </c>
+      <c r="K81">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L81">
+        <v>1.42</v>
+      </c>
+      <c r="M81">
+        <v>4.344655560000001</v>
+      </c>
+      <c r="N81">
+        <v>-2.924655560000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.7019173344000001</v>
+      </c>
+      <c r="P81">
+        <v>-2.222738225600001</v>
+      </c>
+      <c r="Q81">
+        <v>-2.0327382256</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4936735400557794</v>
+      </c>
+      <c r="T81">
+        <v>5.69774659693411</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.07844120098671295</v>
+      </c>
+      <c r="W81">
+        <v>0.220068241204373</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3268383374446373</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2795253539631683</v>
+      </c>
+      <c r="C82">
+        <v>-7.719622549003638</v>
+      </c>
+      <c r="D82">
+        <v>9.014377450996362</v>
+      </c>
+      <c r="E82">
+        <v>18.094</v>
+      </c>
+      <c r="F82">
+        <v>18.424</v>
+      </c>
+      <c r="G82">
+        <v>1.69</v>
+      </c>
+      <c r="H82">
+        <v>22.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.61</v>
+      </c>
+      <c r="K82">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L82">
+        <v>1.42</v>
+      </c>
+      <c r="M82">
+        <v>4.3996512</v>
+      </c>
+      <c r="N82">
+        <v>-2.9796512</v>
+      </c>
+      <c r="O82">
+        <v>-0.715116288</v>
+      </c>
+      <c r="P82">
+        <v>-2.264534912</v>
+      </c>
+      <c r="Q82">
+        <v>-2.074534912</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5164172170585684</v>
+      </c>
+      <c r="T82">
+        <v>5.982633926780815</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.07746068597437905</v>
+      </c>
+      <c r="W82">
+        <v>0.2203023881893183</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3227528582265794</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2815253539631683</v>
+      </c>
+      <c r="C83">
+        <v>-8.024198905418915</v>
+      </c>
+      <c r="D83">
+        <v>8.940101094581085</v>
+      </c>
+      <c r="E83">
+        <v>18.3243</v>
+      </c>
+      <c r="F83">
+        <v>18.6543</v>
+      </c>
+      <c r="G83">
+        <v>1.69</v>
+      </c>
+      <c r="H83">
+        <v>22.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.61</v>
+      </c>
+      <c r="K83">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L83">
+        <v>1.42</v>
+      </c>
+      <c r="M83">
+        <v>4.45464684</v>
+      </c>
+      <c r="N83">
+        <v>-3.03464684</v>
+      </c>
+      <c r="O83">
+        <v>-0.7283152415999999</v>
+      </c>
+      <c r="P83">
+        <v>-2.3063315984</v>
+      </c>
+      <c r="Q83">
+        <v>-2.1163315984</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5415549653248088</v>
+      </c>
+      <c r="T83">
+        <v>6.297509396611385</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.07650438120926327</v>
+      </c>
+      <c r="W83">
+        <v>0.2205307537672279</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.318768255038597</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2835253539631684</v>
+      </c>
+      <c r="C84">
+        <v>-8.327561225687759</v>
+      </c>
+      <c r="D84">
+        <v>8.86703877431224</v>
+      </c>
+      <c r="E84">
+        <v>18.5546</v>
+      </c>
+      <c r="F84">
+        <v>18.8846</v>
+      </c>
+      <c r="G84">
+        <v>1.69</v>
+      </c>
+      <c r="H84">
+        <v>22.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.61</v>
+      </c>
+      <c r="K84">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L84">
+        <v>1.42</v>
+      </c>
+      <c r="M84">
+        <v>4.50964248</v>
+      </c>
+      <c r="N84">
+        <v>-3.08964248</v>
+      </c>
+      <c r="O84">
+        <v>-0.7415141952000001</v>
+      </c>
+      <c r="P84">
+        <v>-2.3481282848</v>
+      </c>
+      <c r="Q84">
+        <v>-2.1581282848</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5694857967317428</v>
+      </c>
+      <c r="T84">
+        <v>6.647371029756463</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.07557140095061371</v>
+      </c>
+      <c r="W84">
+        <v>0.2207535494529935</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3148808372942238</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2855253539631683</v>
+      </c>
+      <c r="C85">
+        <v>-8.629739033394829</v>
+      </c>
+      <c r="D85">
+        <v>8.79516096660517</v>
+      </c>
+      <c r="E85">
+        <v>18.7849</v>
+      </c>
+      <c r="F85">
+        <v>19.1149</v>
+      </c>
+      <c r="G85">
+        <v>1.69</v>
+      </c>
+      <c r="H85">
+        <v>22.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.61</v>
+      </c>
+      <c r="K85">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L85">
+        <v>1.42</v>
+      </c>
+      <c r="M85">
+        <v>4.56463812</v>
+      </c>
+      <c r="N85">
+        <v>-3.14463812</v>
+      </c>
+      <c r="O85">
+        <v>-0.7547131488</v>
+      </c>
+      <c r="P85">
+        <v>-2.3899249712</v>
+      </c>
+      <c r="Q85">
+        <v>-2.1999249712</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6007026083041982</v>
+      </c>
+      <c r="T85">
+        <v>7.038392855036255</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.07466090214397982</v>
+      </c>
+      <c r="W85">
+        <v>0.2209709765680176</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3110870922665826</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2875253539631683</v>
+      </c>
+      <c r="C86">
+        <v>-8.930760902528505</v>
+      </c>
+      <c r="D86">
+        <v>8.724439097471494</v>
+      </c>
+      <c r="E86">
+        <v>19.0152</v>
+      </c>
+      <c r="F86">
+        <v>19.3452</v>
+      </c>
+      <c r="G86">
+        <v>1.69</v>
+      </c>
+      <c r="H86">
+        <v>22.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.61</v>
+      </c>
+      <c r="K86">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L86">
+        <v>1.42</v>
+      </c>
+      <c r="M86">
+        <v>4.61963376</v>
+      </c>
+      <c r="N86">
+        <v>-3.19963376</v>
+      </c>
+      <c r="O86">
+        <v>-0.7679121024000001</v>
+      </c>
+      <c r="P86">
+        <v>-2.4317216576</v>
+      </c>
+      <c r="Q86">
+        <v>-2.2417216576</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6358215213232103</v>
+      </c>
+      <c r="T86">
+        <v>7.478292408476016</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.073772081880361</v>
+      </c>
+      <c r="W86">
+        <v>0.2211832268469698</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3073836745015042</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2895253539631683</v>
+      </c>
+      <c r="C87">
+        <v>-9.230654495354807</v>
+      </c>
+      <c r="D87">
+        <v>8.654845504645191</v>
+      </c>
+      <c r="E87">
+        <v>19.2455</v>
+      </c>
+      <c r="F87">
+        <v>19.5755</v>
+      </c>
+      <c r="G87">
+        <v>1.69</v>
+      </c>
+      <c r="H87">
+        <v>22.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.61</v>
+      </c>
+      <c r="K87">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L87">
+        <v>1.42</v>
+      </c>
+      <c r="M87">
+        <v>4.6746294</v>
+      </c>
+      <c r="N87">
+        <v>-3.2546294</v>
+      </c>
+      <c r="O87">
+        <v>-0.781111056</v>
+      </c>
+      <c r="P87">
+        <v>-2.473518344</v>
+      </c>
+      <c r="Q87">
+        <v>-2.283518344</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6756229560780911</v>
+      </c>
+      <c r="T87">
+        <v>7.976845235707752</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0729041750347097</v>
+      </c>
+      <c r="W87">
+        <v>0.2213904830017113</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3037673959779571</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2915253539631683</v>
+      </c>
+      <c r="C88">
+        <v>-9.529446598493035</v>
+      </c>
+      <c r="D88">
+        <v>8.586353401506964</v>
+      </c>
+      <c r="E88">
+        <v>19.4758</v>
+      </c>
+      <c r="F88">
+        <v>19.8058</v>
+      </c>
+      <c r="G88">
+        <v>1.69</v>
+      </c>
+      <c r="H88">
+        <v>22.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.61</v>
+      </c>
+      <c r="K88">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L88">
+        <v>1.42</v>
+      </c>
+      <c r="M88">
+        <v>4.72962504</v>
+      </c>
+      <c r="N88">
+        <v>-3.30962504</v>
+      </c>
+      <c r="O88">
+        <v>-0.7943100096</v>
+      </c>
+      <c r="P88">
+        <v>-2.5153150304</v>
+      </c>
+      <c r="Q88">
+        <v>-2.3253150304</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7211103100836691</v>
+      </c>
+      <c r="T88">
+        <v>8.546619895401163</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07205645206918981</v>
+      </c>
+      <c r="W88">
+        <v>0.2215929192458775</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3002352169549576</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2935253539631683</v>
+      </c>
+      <c r="C89">
+        <v>-9.827163157291874</v>
+      </c>
+      <c r="D89">
+        <v>8.518936842708124</v>
+      </c>
+      <c r="E89">
+        <v>19.7061</v>
+      </c>
+      <c r="F89">
+        <v>20.0361</v>
+      </c>
+      <c r="G89">
+        <v>1.69</v>
+      </c>
+      <c r="H89">
+        <v>22.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.61</v>
+      </c>
+      <c r="K89">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L89">
+        <v>1.42</v>
+      </c>
+      <c r="M89">
+        <v>4.78462068</v>
+      </c>
+      <c r="N89">
+        <v>-3.36462068</v>
+      </c>
+      <c r="O89">
+        <v>-0.8075089631999999</v>
+      </c>
+      <c r="P89">
+        <v>-2.5571117168</v>
+      </c>
+      <c r="Q89">
+        <v>-2.367111716799999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7735957185516436</v>
+      </c>
+      <c r="T89">
+        <v>9.204052195047407</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.07122821698793477</v>
+      </c>
+      <c r="W89">
+        <v>0.2217907017832812</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2967842374497281</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2955253539631683</v>
+      </c>
+      <c r="C90">
+        <v>-10.12382930859869</v>
+      </c>
+      <c r="D90">
+        <v>8.452570691401304</v>
+      </c>
+      <c r="E90">
+        <v>19.9364</v>
+      </c>
+      <c r="F90">
+        <v>20.2664</v>
+      </c>
+      <c r="G90">
+        <v>1.69</v>
+      </c>
+      <c r="H90">
+        <v>22.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.61</v>
+      </c>
+      <c r="K90">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L90">
+        <v>1.42</v>
+      </c>
+      <c r="M90">
+        <v>4.839616319999999</v>
+      </c>
+      <c r="N90">
+        <v>-3.419616319999999</v>
+      </c>
+      <c r="O90">
+        <v>-0.8207079167999998</v>
+      </c>
+      <c r="P90">
+        <v>-2.598908403199999</v>
+      </c>
+      <c r="Q90">
+        <v>-2.408908403199999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.834828695097614</v>
+      </c>
+      <c r="T90">
+        <v>9.971056544634692</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0704188054312537</v>
+      </c>
+      <c r="W90">
+        <v>0.2219839892630166</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2934116892968904</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2975253539631683</v>
+      </c>
+      <c r="C91">
+        <v>-10.41946941200893</v>
+      </c>
+      <c r="D91">
+        <v>8.387230587991072</v>
+      </c>
+      <c r="E91">
+        <v>20.1667</v>
+      </c>
+      <c r="F91">
+        <v>20.4967</v>
+      </c>
+      <c r="G91">
+        <v>1.69</v>
+      </c>
+      <c r="H91">
+        <v>22.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.61</v>
+      </c>
+      <c r="K91">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L91">
+        <v>1.42</v>
+      </c>
+      <c r="M91">
+        <v>4.89461196</v>
+      </c>
+      <c r="N91">
+        <v>-3.47461196</v>
+      </c>
+      <c r="O91">
+        <v>-0.8339068703999999</v>
+      </c>
+      <c r="P91">
+        <v>-2.6407050896</v>
+      </c>
+      <c r="Q91">
+        <v>-2.4507050896</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.907194940106488</v>
+      </c>
+      <c r="T91">
+        <v>10.87751623051057</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06962758289831825</v>
+      </c>
+      <c r="W91">
+        <v>0.2221729332038816</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2901149287429927</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2995253539631683</v>
+      </c>
+      <c r="C92">
+        <v>-10.71410707967723</v>
+      </c>
+      <c r="D92">
+        <v>8.32289292032277</v>
+      </c>
+      <c r="E92">
+        <v>20.397</v>
+      </c>
+      <c r="F92">
+        <v>20.727</v>
+      </c>
+      <c r="G92">
+        <v>1.69</v>
+      </c>
+      <c r="H92">
+        <v>22.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.61</v>
+      </c>
+      <c r="K92">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L92">
+        <v>1.42</v>
+      </c>
+      <c r="M92">
+        <v>4.949607599999999</v>
+      </c>
+      <c r="N92">
+        <v>-3.529607599999999</v>
+      </c>
+      <c r="O92">
+        <v>-0.8471058239999998</v>
+      </c>
+      <c r="P92">
+        <v>-2.682501776</v>
+      </c>
+      <c r="Q92">
+        <v>-2.492501775999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9940344341171368</v>
+      </c>
+      <c r="T92">
+        <v>11.96526785356163</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06885394308833695</v>
+      </c>
+      <c r="W92">
+        <v>0.2223576783905052</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2868914295347372</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3015253539631683</v>
+      </c>
+      <c r="C93">
+        <v>-11.00776520476697</v>
+      </c>
+      <c r="D93">
+        <v>8.259534795233026</v>
+      </c>
+      <c r="E93">
+        <v>20.6273</v>
+      </c>
+      <c r="F93">
+        <v>20.9573</v>
+      </c>
+      <c r="G93">
+        <v>1.69</v>
+      </c>
+      <c r="H93">
+        <v>22.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.61</v>
+      </c>
+      <c r="K93">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L93">
+        <v>1.42</v>
+      </c>
+      <c r="M93">
+        <v>5.004603240000001</v>
+      </c>
+      <c r="N93">
+        <v>-3.584603240000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.8603047776000001</v>
+      </c>
+      <c r="P93">
+        <v>-2.724298462400001</v>
+      </c>
+      <c r="Q93">
+        <v>-2.534298462400001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.100171593463485</v>
+      </c>
+      <c r="T93">
+        <v>13.29474205951293</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06809730635110245</v>
+      </c>
+      <c r="W93">
+        <v>0.2225383632433567</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2837387764629269</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3035253539631683</v>
+      </c>
+      <c r="C94">
+        <v>-11.30046598861016</v>
+      </c>
+      <c r="D94">
+        <v>8.197134011389842</v>
+      </c>
+      <c r="E94">
+        <v>20.8576</v>
+      </c>
+      <c r="F94">
+        <v>21.1876</v>
+      </c>
+      <c r="G94">
+        <v>1.69</v>
+      </c>
+      <c r="H94">
+        <v>22.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.61</v>
+      </c>
+      <c r="K94">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L94">
+        <v>1.42</v>
+      </c>
+      <c r="M94">
+        <v>5.05959888</v>
+      </c>
+      <c r="N94">
+        <v>-3.63959888</v>
+      </c>
+      <c r="O94">
+        <v>-0.8735037312</v>
+      </c>
+      <c r="P94">
+        <v>-2.7660951488</v>
+      </c>
+      <c r="Q94">
+        <v>-2.5760951488</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.232843042646421</v>
+      </c>
+      <c r="T94">
+        <v>14.95658481695205</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06735711823859047</v>
+      </c>
+      <c r="W94">
+        <v>0.2227151201646246</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2806546593274604</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3055253539631683</v>
+      </c>
+      <c r="C95">
+        <v>-11.59223096664537</v>
+      </c>
+      <c r="D95">
+        <v>8.135669033354633</v>
+      </c>
+      <c r="E95">
+        <v>21.0879</v>
+      </c>
+      <c r="F95">
+        <v>21.4179</v>
+      </c>
+      <c r="G95">
+        <v>1.69</v>
+      </c>
+      <c r="H95">
+        <v>22.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.61</v>
+      </c>
+      <c r="K95">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L95">
+        <v>1.42</v>
+      </c>
+      <c r="M95">
+        <v>5.11459452</v>
+      </c>
+      <c r="N95">
+        <v>-3.69459452</v>
+      </c>
+      <c r="O95">
+        <v>-0.8867026847999999</v>
+      </c>
+      <c r="P95">
+        <v>-2.8078918352</v>
+      </c>
+      <c r="Q95">
+        <v>-2.6178918352</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.403420620167339</v>
+      </c>
+      <c r="T95">
+        <v>17.09323979080234</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06663284815000348</v>
+      </c>
+      <c r="W95">
+        <v>0.2228880758617792</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2776368672916812</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3075253539631683</v>
+      </c>
+      <c r="C96">
+        <v>-11.88308103319748</v>
+      </c>
+      <c r="D96">
+        <v>8.075118966802522</v>
+      </c>
+      <c r="E96">
+        <v>21.3182</v>
+      </c>
+      <c r="F96">
+        <v>21.6482</v>
+      </c>
+      <c r="G96">
+        <v>1.69</v>
+      </c>
+      <c r="H96">
+        <v>22.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.61</v>
+      </c>
+      <c r="K96">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L96">
+        <v>1.42</v>
+      </c>
+      <c r="M96">
+        <v>5.16959016</v>
+      </c>
+      <c r="N96">
+        <v>-3.74959016</v>
+      </c>
+      <c r="O96">
+        <v>-0.8999016384</v>
+      </c>
+      <c r="P96">
+        <v>-2.8496885216</v>
+      </c>
+      <c r="Q96">
+        <v>-2.6596885216</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.630857390195229</v>
+      </c>
+      <c r="T96">
+        <v>19.9421130892694</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06592398806330131</v>
+      </c>
+      <c r="W96">
+        <v>0.2230573516504837</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2746832835970888</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3095253539631683</v>
+      </c>
+      <c r="C97">
+        <v>-12.17303646515898</v>
+      </c>
+      <c r="D97">
+        <v>8.015463534841015</v>
+      </c>
+      <c r="E97">
+        <v>21.5485</v>
+      </c>
+      <c r="F97">
+        <v>21.8785</v>
+      </c>
+      <c r="G97">
+        <v>1.69</v>
+      </c>
+      <c r="H97">
+        <v>22.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.61</v>
+      </c>
+      <c r="K97">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L97">
+        <v>1.42</v>
+      </c>
+      <c r="M97">
+        <v>5.2245858</v>
+      </c>
+      <c r="N97">
+        <v>-3.8045858</v>
+      </c>
+      <c r="O97">
+        <v>-0.9131005919999999</v>
+      </c>
+      <c r="P97">
+        <v>-2.891485208</v>
+      </c>
+      <c r="Q97">
+        <v>-2.701485207999999</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.949268868234276</v>
+      </c>
+      <c r="T97">
+        <v>23.93053570712329</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.06523005134684552</v>
+      </c>
+      <c r="W97">
+        <v>0.2232230637383733</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2717918806118563</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3115253539631683</v>
+      </c>
+      <c r="C98">
+        <v>-12.46211694462935</v>
+      </c>
+      <c r="D98">
+        <v>7.956683055370641</v>
+      </c>
+      <c r="E98">
+        <v>21.7788</v>
+      </c>
+      <c r="F98">
+        <v>22.1088</v>
+      </c>
+      <c r="G98">
+        <v>1.69</v>
+      </c>
+      <c r="H98">
+        <v>22.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.61</v>
+      </c>
+      <c r="K98">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L98">
+        <v>1.42</v>
+      </c>
+      <c r="M98">
+        <v>5.279581439999999</v>
+      </c>
+      <c r="N98">
+        <v>-3.859581439999999</v>
+      </c>
+      <c r="O98">
+        <v>-0.9262995455999998</v>
+      </c>
+      <c r="P98">
+        <v>-2.933281894399999</v>
+      </c>
+      <c r="Q98">
+        <v>-2.743281894399999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.42688608529284</v>
+      </c>
+      <c r="T98">
+        <v>29.91316963390405</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.06455057164531589</v>
+      </c>
+      <c r="W98">
+        <v>0.2233853234910986</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2689607151888161</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3135253539631683</v>
+      </c>
+      <c r="C99">
+        <v>-12.75034158056549</v>
+      </c>
+      <c r="D99">
+        <v>7.898758419434511</v>
+      </c>
+      <c r="E99">
+        <v>22.0091</v>
+      </c>
+      <c r="F99">
+        <v>22.3391</v>
+      </c>
+      <c r="G99">
+        <v>1.69</v>
+      </c>
+      <c r="H99">
+        <v>22.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.61</v>
+      </c>
+      <c r="K99">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L99">
+        <v>1.42</v>
+      </c>
+      <c r="M99">
+        <v>5.33457708</v>
+      </c>
+      <c r="N99">
+        <v>-3.91457708</v>
+      </c>
+      <c r="O99">
+        <v>-0.9394984991999999</v>
+      </c>
+      <c r="P99">
+        <v>-2.9750785808</v>
+      </c>
+      <c r="Q99">
+        <v>-2.7850785808</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.222914780390453</v>
+      </c>
+      <c r="T99">
+        <v>39.88422617853873</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06388510183453944</v>
+      </c>
+      <c r="W99">
+        <v>0.223544237681912</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2661879243105809</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3155253539631683</v>
+      </c>
+      <c r="C100">
+        <v>-13.0377289294933</v>
+      </c>
+      <c r="D100">
+        <v>7.841671070506695</v>
+      </c>
+      <c r="E100">
+        <v>22.2394</v>
+      </c>
+      <c r="F100">
+        <v>22.5694</v>
+      </c>
+      <c r="G100">
+        <v>1.69</v>
+      </c>
+      <c r="H100">
+        <v>22.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.61</v>
+      </c>
+      <c r="K100">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L100">
+        <v>1.42</v>
+      </c>
+      <c r="M100">
+        <v>5.389572719999999</v>
+      </c>
+      <c r="N100">
+        <v>-3.969572719999999</v>
+      </c>
+      <c r="O100">
+        <v>-0.9526974527999998</v>
+      </c>
+      <c r="P100">
+        <v>-3.0168752672</v>
+      </c>
+      <c r="Q100">
+        <v>-2.826875267199999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.814972170585679</v>
+      </c>
+      <c r="T100">
+        <v>59.82633926780809</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06323321304030945</v>
+      </c>
+      <c r="W100">
+        <v>0.2236999087259741</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2634717210012893</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3175253539631683</v>
+      </c>
+      <c r="C101">
+        <v>-13.32429701532767</v>
+      </c>
+      <c r="D101">
+        <v>7.785402984672328</v>
+      </c>
+      <c r="E101">
+        <v>22.4697</v>
+      </c>
+      <c r="F101">
+        <v>22.7997</v>
+      </c>
+      <c r="G101">
+        <v>1.69</v>
+      </c>
+      <c r="H101">
+        <v>22.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.61</v>
+      </c>
+      <c r="K101">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="L101">
+        <v>1.42</v>
+      </c>
+      <c r="M101">
+        <v>5.44456836</v>
+      </c>
+      <c r="N101">
+        <v>-4.02456836</v>
+      </c>
+      <c r="O101">
+        <v>-0.9658964064</v>
+      </c>
+      <c r="P101">
+        <v>-3.0586719536</v>
+      </c>
+      <c r="Q101">
+        <v>-2.8686719536</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.591144341171359</v>
+      </c>
+      <c r="T101">
+        <v>119.6526785356162</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06259449371666993</v>
+      </c>
+      <c r="W101">
+        <v>0.2238524349004592</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2608103904861248</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_heathcare_information_and_technology.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1154296402642637</v>
+        <v>0.1151868091276295</v>
       </c>
       <c r="C2">
-        <v>18.32756894998072</v>
+        <v>18.20837944665178</v>
       </c>
       <c r="D2">
-        <v>18.32756894998072</v>
+        <v>18.39170944665178</v>
       </c>
       <c r="E2">
-        <v>-0.033</v>
+        <v>0.15033</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.18333</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1564,28 +1564,28 @@
         <v>0.781</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.009221499000000001</v>
       </c>
       <c r="N2">
-        <v>0.781</v>
+        <v>0.771778501</v>
       </c>
       <c r="O2">
-        <v>0.18744</v>
+        <v>0.18522684024</v>
       </c>
       <c r="P2">
-        <v>0.5935600000000001</v>
+        <v>0.58655166076</v>
       </c>
       <c r="Q2">
-        <v>0.7255600000000001</v>
+        <v>0.71855166076</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1154296402642637</v>
+        <v>0.1159641708359894</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.183068719658774</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>84.69338878635675</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1151868091276295</v>
+        <v>0.1149439779909952</v>
       </c>
       <c r="C3">
-        <v>18.20837944665178</v>
+        <v>18.08964046150717</v>
       </c>
       <c r="D3">
-        <v>18.39170944665178</v>
+        <v>18.45630046150717</v>
       </c>
       <c r="E3">
-        <v>0.15033</v>
+        <v>0.3336600000000001</v>
       </c>
       <c r="F3">
-        <v>0.18333</v>
+        <v>0.36666</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1646,28 +1646,28 @@
         <v>0.781</v>
       </c>
       <c r="M3">
-        <v>0.009221499000000001</v>
+        <v>0.018442998</v>
       </c>
       <c r="N3">
-        <v>0.771778501</v>
+        <v>0.762557002</v>
       </c>
       <c r="O3">
-        <v>0.18522684024</v>
+        <v>0.18301368048</v>
       </c>
       <c r="P3">
-        <v>0.58655166076</v>
+        <v>0.57954332152</v>
       </c>
       <c r="Q3">
-        <v>0.71855166076</v>
+        <v>0.71154332152</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1159641708359894</v>
+        <v>0.1165096101948931</v>
       </c>
       <c r="T3">
-        <v>1.183068719658774</v>
+        <v>1.19226561083986</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>84.69338878635675</v>
+        <v>42.34669439317837</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1149439779909952</v>
+        <v>0.114701146854361</v>
       </c>
       <c r="C4">
-        <v>18.08964046150717</v>
+        <v>17.971356757886</v>
       </c>
       <c r="D4">
-        <v>18.45630046150717</v>
+        <v>18.521346757886</v>
       </c>
       <c r="E4">
-        <v>0.3336600000000001</v>
+        <v>0.5169900000000001</v>
       </c>
       <c r="F4">
-        <v>0.36666</v>
+        <v>0.5499900000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1728,28 +1728,28 @@
         <v>0.781</v>
       </c>
       <c r="M4">
-        <v>0.018442998</v>
+        <v>0.027664497</v>
       </c>
       <c r="N4">
-        <v>0.762557002</v>
+        <v>0.7533355030000001</v>
       </c>
       <c r="O4">
-        <v>0.18301368048</v>
+        <v>0.18080052072</v>
       </c>
       <c r="P4">
-        <v>0.57954332152</v>
+        <v>0.5725349822800001</v>
       </c>
       <c r="Q4">
-        <v>0.71154332152</v>
+        <v>0.7045349822800001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1165096101948931</v>
+        <v>0.1170662957261454</v>
       </c>
       <c r="T4">
-        <v>1.19226561083986</v>
+        <v>1.201652128643237</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.34669439317837</v>
+        <v>28.23112959545225</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.114701146854361</v>
+        <v>0.1144583157177268</v>
       </c>
       <c r="C5">
-        <v>17.971356757886</v>
+        <v>17.85353316651544</v>
       </c>
       <c r="D5">
-        <v>18.521346757886</v>
+        <v>18.58685316651544</v>
       </c>
       <c r="E5">
-        <v>0.5169900000000001</v>
+        <v>0.7003200000000001</v>
       </c>
       <c r="F5">
-        <v>0.5499900000000001</v>
+        <v>0.7333200000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1810,28 +1810,28 @@
         <v>0.781</v>
       </c>
       <c r="M5">
-        <v>0.027664497</v>
+        <v>0.036885996</v>
       </c>
       <c r="N5">
-        <v>0.7533355030000001</v>
+        <v>0.7441140040000001</v>
       </c>
       <c r="O5">
-        <v>0.18080052072</v>
+        <v>0.17858736096</v>
       </c>
       <c r="P5">
-        <v>0.5725349822800001</v>
+        <v>0.5655266430400001</v>
       </c>
       <c r="Q5">
-        <v>0.7045349822800001</v>
+        <v>0.6975266430400001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1170662957261454</v>
+        <v>0.1176345788726321</v>
       </c>
       <c r="T5">
-        <v>1.201652128643237</v>
+        <v>1.211234198900851</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.23112959545225</v>
+        <v>21.17334719658919</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1144583157177268</v>
+        <v>0.1142154845810926</v>
       </c>
       <c r="C6">
-        <v>17.85353316651544</v>
+        <v>17.73617458670656</v>
       </c>
       <c r="D6">
-        <v>18.58685316651544</v>
+        <v>18.65282458670656</v>
       </c>
       <c r="E6">
-        <v>0.7003200000000001</v>
+        <v>0.8836500000000002</v>
       </c>
       <c r="F6">
-        <v>0.7333200000000001</v>
+        <v>0.9166500000000002</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1892,28 +1892,28 @@
         <v>0.781</v>
       </c>
       <c r="M6">
-        <v>0.036885996</v>
+        <v>0.04610749500000001</v>
       </c>
       <c r="N6">
-        <v>0.7441140040000001</v>
+        <v>0.734892505</v>
       </c>
       <c r="O6">
-        <v>0.17858736096</v>
+        <v>0.1763742012</v>
       </c>
       <c r="P6">
-        <v>0.5655266430400001</v>
+        <v>0.5585183038</v>
       </c>
       <c r="Q6">
-        <v>0.6975266430400001</v>
+        <v>0.6905183038</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1176345788726321</v>
+        <v>0.1182148258748343</v>
       </c>
       <c r="T6">
-        <v>1.211234198900851</v>
+        <v>1.221017996953362</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.17334719658919</v>
+        <v>16.93867775727135</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1142154845810926</v>
+        <v>0.1139726534444583</v>
       </c>
       <c r="C7">
-        <v>17.73617458670656</v>
+        <v>17.61928598757589</v>
       </c>
       <c r="D7">
-        <v>18.65282458670656</v>
+        <v>18.71926598757588</v>
       </c>
       <c r="E7">
-        <v>0.8836500000000002</v>
+        <v>1.06698</v>
       </c>
       <c r="F7">
-        <v>0.9166500000000002</v>
+        <v>1.09998</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1974,28 +1974,28 @@
         <v>0.781</v>
       </c>
       <c r="M7">
-        <v>0.04610749500000001</v>
+        <v>0.05532899400000001</v>
       </c>
       <c r="N7">
-        <v>0.734892505</v>
+        <v>0.725671006</v>
       </c>
       <c r="O7">
-        <v>0.1763742012</v>
+        <v>0.17416104144</v>
       </c>
       <c r="P7">
-        <v>0.5585183038</v>
+        <v>0.55150996456</v>
       </c>
       <c r="Q7">
-        <v>0.6905183038</v>
+        <v>0.68350996456</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1182148258748343</v>
+        <v>0.1188074185579344</v>
       </c>
       <c r="T7">
-        <v>1.221017996953362</v>
+        <v>1.231009960921883</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.93867775727135</v>
+        <v>14.11556479772612</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1139726534444583</v>
+        <v>0.1138096223078241</v>
       </c>
       <c r="C8">
-        <v>17.61928598757589</v>
+        <v>17.48082939088785</v>
       </c>
       <c r="D8">
-        <v>18.71926598757588</v>
+        <v>18.76413939088785</v>
       </c>
       <c r="E8">
-        <v>1.06698</v>
+        <v>1.25031</v>
       </c>
       <c r="F8">
-        <v>1.09998</v>
+        <v>1.28331</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2056,45 +2056,45 @@
         <v>0.781</v>
       </c>
       <c r="M8">
-        <v>0.05532899400000001</v>
+        <v>0.066475458</v>
       </c>
       <c r="N8">
-        <v>0.725671006</v>
+        <v>0.714524542</v>
       </c>
       <c r="O8">
-        <v>0.17416104144</v>
+        <v>0.17148589008</v>
       </c>
       <c r="P8">
-        <v>0.55150996456</v>
+        <v>0.54303865192</v>
       </c>
       <c r="Q8">
-        <v>0.68350996456</v>
+        <v>0.67503865192</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1188074185579344</v>
+        <v>0.1194127551697033</v>
       </c>
       <c r="T8">
-        <v>1.231009960921883</v>
+        <v>1.241216805835964</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.11556479772612</v>
+        <v>11.74869678972351</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1138096223078241</v>
+        <v>0.1135781911711898</v>
       </c>
       <c r="C9">
-        <v>17.48082939088785</v>
+        <v>17.36157023775108</v>
       </c>
       <c r="D9">
-        <v>18.76413939088785</v>
+        <v>18.82821023775108</v>
       </c>
       <c r="E9">
-        <v>1.25031</v>
+        <v>1.43364</v>
       </c>
       <c r="F9">
-        <v>1.28331</v>
+        <v>1.46664</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2138,28 +2138,28 @@
         <v>0.781</v>
       </c>
       <c r="M9">
-        <v>0.066475458</v>
+        <v>0.07597195200000001</v>
       </c>
       <c r="N9">
-        <v>0.714524542</v>
+        <v>0.705028048</v>
       </c>
       <c r="O9">
-        <v>0.17148589008</v>
+        <v>0.16920673152</v>
       </c>
       <c r="P9">
-        <v>0.54303865192</v>
+        <v>0.53582131648</v>
       </c>
       <c r="Q9">
-        <v>0.67503865192</v>
+        <v>0.66782131648</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1194127551697033</v>
+        <v>0.1200312512730324</v>
       </c>
       <c r="T9">
-        <v>1.241216805835964</v>
+        <v>1.251645538682961</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.74869678972351</v>
+        <v>10.28010969100807</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1135781911711898</v>
+        <v>0.1134630400345556</v>
       </c>
       <c r="C10">
-        <v>17.36157023775108</v>
+        <v>17.21028269118738</v>
       </c>
       <c r="D10">
-        <v>18.82821023775108</v>
+        <v>18.86025269118738</v>
       </c>
       <c r="E10">
-        <v>1.43364</v>
+        <v>1.61697</v>
       </c>
       <c r="F10">
-        <v>1.46664</v>
+        <v>1.64997</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2220,45 +2220,45 @@
         <v>0.781</v>
       </c>
       <c r="M10">
-        <v>0.07597195200000001</v>
+        <v>0.088273395</v>
       </c>
       <c r="N10">
-        <v>0.705028048</v>
+        <v>0.6927266050000001</v>
       </c>
       <c r="O10">
-        <v>0.16920673152</v>
+        <v>0.1662543852</v>
       </c>
       <c r="P10">
-        <v>0.53582131648</v>
+        <v>0.5264722198</v>
       </c>
       <c r="Q10">
-        <v>0.66782131648</v>
+        <v>0.6584722198</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1200312512730324</v>
+        <v>0.1206633406973139</v>
       </c>
       <c r="T10">
-        <v>1.251645538682961</v>
+        <v>1.262303474449671</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.28010969100807</v>
+        <v>8.847512888792824</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1134630400345556</v>
+        <v>0.1132445288979214</v>
       </c>
       <c r="C11">
-        <v>17.21028269118738</v>
+        <v>17.08805735482877</v>
       </c>
       <c r="D11">
-        <v>18.86025269118738</v>
+        <v>18.92135735482877</v>
       </c>
       <c r="E11">
-        <v>1.61697</v>
+        <v>1.8003</v>
       </c>
       <c r="F11">
-        <v>1.64997</v>
+        <v>1.8333</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2302,28 +2302,28 @@
         <v>0.781</v>
       </c>
       <c r="M11">
-        <v>0.088273395</v>
+        <v>0.09808155</v>
       </c>
       <c r="N11">
-        <v>0.6927266050000001</v>
+        <v>0.6829184500000001</v>
       </c>
       <c r="O11">
-        <v>0.1662543852</v>
+        <v>0.163900428</v>
       </c>
       <c r="P11">
-        <v>0.5264722198</v>
+        <v>0.519018022</v>
       </c>
       <c r="Q11">
-        <v>0.6584722198</v>
+        <v>0.651018022</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1206633406973139</v>
+        <v>0.121309476553246</v>
       </c>
       <c r="T11">
-        <v>1.262303474449671</v>
+        <v>1.27319825323342</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.847512888792824</v>
+        <v>7.962761599913541</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1132445288979214</v>
+        <v>0.1130928977612872</v>
       </c>
       <c r="C12">
-        <v>17.08805735482877</v>
+        <v>16.94736286344594</v>
       </c>
       <c r="D12">
-        <v>18.92135735482877</v>
+        <v>18.96399286344593</v>
       </c>
       <c r="E12">
-        <v>1.8003</v>
+        <v>1.98363</v>
       </c>
       <c r="F12">
-        <v>1.8333</v>
+        <v>2.01663</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2384,45 +2384,45 @@
         <v>0.781</v>
       </c>
       <c r="M12">
-        <v>0.09808155000000002</v>
+        <v>0.109503009</v>
       </c>
       <c r="N12">
-        <v>0.6829184500000001</v>
+        <v>0.671496991</v>
       </c>
       <c r="O12">
-        <v>0.163900428</v>
+        <v>0.16115927784</v>
       </c>
       <c r="P12">
-        <v>0.519018022</v>
+        <v>0.51033771316</v>
       </c>
       <c r="Q12">
-        <v>0.651018022</v>
+        <v>0.64233771316</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.121309476553246</v>
+        <v>0.121970132316053</v>
       </c>
       <c r="T12">
-        <v>1.27319825323342</v>
+        <v>1.284337858506691</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.962761599913541</v>
+        <v>7.132224101713954</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1130928977612872</v>
+        <v>0.1128804666246529</v>
       </c>
       <c r="C13">
-        <v>16.94736286344594</v>
+        <v>16.82408823815951</v>
       </c>
       <c r="D13">
-        <v>18.96399286344593</v>
+        <v>19.02404823815952</v>
       </c>
       <c r="E13">
-        <v>1.98363</v>
+        <v>2.16696</v>
       </c>
       <c r="F13">
-        <v>2.01663</v>
+        <v>2.19996</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2466,28 +2466,28 @@
         <v>0.781</v>
       </c>
       <c r="M13">
-        <v>0.109503009</v>
+        <v>0.119457828</v>
       </c>
       <c r="N13">
-        <v>0.671496991</v>
+        <v>0.661542172</v>
       </c>
       <c r="O13">
-        <v>0.16115927784</v>
+        <v>0.15877012128</v>
       </c>
       <c r="P13">
-        <v>0.51033771316</v>
+        <v>0.50277205072</v>
       </c>
       <c r="Q13">
-        <v>0.64233771316</v>
+        <v>0.63477205072</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.121970132316053</v>
+        <v>0.1226458029825601</v>
       </c>
       <c r="T13">
-        <v>1.284337858506691</v>
+        <v>1.295730636627081</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.132224101713954</v>
+        <v>6.53787209323779</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1128804666246529</v>
+        <v>0.1127668354880187</v>
       </c>
       <c r="C14">
-        <v>16.82408823815951</v>
+        <v>16.6730387574484</v>
       </c>
       <c r="D14">
-        <v>19.02404823815952</v>
+        <v>19.0563287574484</v>
       </c>
       <c r="E14">
-        <v>2.16696</v>
+        <v>2.35029</v>
       </c>
       <c r="F14">
-        <v>2.19996</v>
+        <v>2.38329</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2548,45 +2548,45 @@
         <v>0.781</v>
       </c>
       <c r="M14">
-        <v>0.119457828</v>
+        <v>0.131795937</v>
       </c>
       <c r="N14">
-        <v>0.661542172</v>
+        <v>0.649204063</v>
       </c>
       <c r="O14">
-        <v>0.15877012128</v>
+        <v>0.15580897512</v>
       </c>
       <c r="P14">
-        <v>0.50277205072</v>
+        <v>0.49339508788</v>
       </c>
       <c r="Q14">
-        <v>0.63477205072</v>
+        <v>0.62539508788</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1226458029825601</v>
+        <v>0.1233370063080675</v>
       </c>
       <c r="T14">
-        <v>1.295730636627081</v>
+        <v>1.307385317692768</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.53787209323779</v>
+        <v>5.925827592090338</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1127668354880187</v>
+        <v>0.1125620043513845</v>
       </c>
       <c r="C15">
-        <v>16.6730387574484</v>
+        <v>16.54817508897014</v>
       </c>
       <c r="D15">
-        <v>19.0563287574484</v>
+        <v>19.11479508897014</v>
       </c>
       <c r="E15">
-        <v>2.35029</v>
+        <v>2.53362</v>
       </c>
       <c r="F15">
-        <v>2.38329</v>
+        <v>2.56662</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2630,28 +2630,28 @@
         <v>0.781</v>
       </c>
       <c r="M15">
-        <v>0.131795937</v>
+        <v>0.141934086</v>
       </c>
       <c r="N15">
-        <v>0.649204063</v>
+        <v>0.639065914</v>
       </c>
       <c r="O15">
-        <v>0.15580897512</v>
+        <v>0.15337581936</v>
       </c>
       <c r="P15">
-        <v>0.49339508788</v>
+        <v>0.48569009464</v>
       </c>
       <c r="Q15">
-        <v>0.62539508788</v>
+        <v>0.61769009464</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1233370063080675</v>
+        <v>0.1240442841295168</v>
       </c>
       <c r="T15">
-        <v>1.307385317692768</v>
+        <v>1.319311037853006</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.925827592090338</v>
+        <v>5.502554192655314</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1125620043513845</v>
+        <v>0.1123571732147502</v>
       </c>
       <c r="C16">
-        <v>16.54817508897014</v>
+        <v>16.42367128328538</v>
       </c>
       <c r="D16">
-        <v>19.11479508897014</v>
+        <v>19.17362128328538</v>
       </c>
       <c r="E16">
-        <v>2.53362</v>
+        <v>2.716950000000001</v>
       </c>
       <c r="F16">
-        <v>2.56662</v>
+        <v>2.749950000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2712,28 +2712,28 @@
         <v>0.781</v>
       </c>
       <c r="M16">
-        <v>0.141934086</v>
+        <v>0.152072235</v>
       </c>
       <c r="N16">
-        <v>0.639065914</v>
+        <v>0.628927765</v>
       </c>
       <c r="O16">
-        <v>0.15337581936</v>
+        <v>0.1509426636</v>
       </c>
       <c r="P16">
-        <v>0.48569009464</v>
+        <v>0.4779851014000001</v>
       </c>
       <c r="Q16">
-        <v>0.61769009464</v>
+        <v>0.6099851014000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1240442841295168</v>
+        <v>0.1247682037820591</v>
       </c>
       <c r="T16">
-        <v>1.319311037853006</v>
+        <v>1.331517363193485</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.502554192655314</v>
+        <v>5.135717246478293</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1123571732147502</v>
+        <v>0.112152342078116</v>
       </c>
       <c r="C17">
-        <v>16.42367128328539</v>
+        <v>16.29953067310716</v>
       </c>
       <c r="D17">
-        <v>19.17362128328539</v>
+        <v>19.23281067310716</v>
       </c>
       <c r="E17">
-        <v>2.71695</v>
+        <v>2.90028</v>
       </c>
       <c r="F17">
-        <v>2.74995</v>
+        <v>2.93328</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2794,28 +2794,28 @@
         <v>0.781</v>
       </c>
       <c r="M17">
-        <v>0.152072235</v>
+        <v>0.162210384</v>
       </c>
       <c r="N17">
-        <v>0.628927765</v>
+        <v>0.618789616</v>
       </c>
       <c r="O17">
-        <v>0.1509426636</v>
+        <v>0.14850950784</v>
       </c>
       <c r="P17">
-        <v>0.4779851014000001</v>
+        <v>0.47028010816</v>
       </c>
       <c r="Q17">
-        <v>0.6099851014000001</v>
+        <v>0.60228010816</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1247682037820591</v>
+        <v>0.1255093596168048</v>
       </c>
       <c r="T17">
-        <v>1.331517363193485</v>
+        <v>1.344014315327785</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.135717246478294</v>
+        <v>4.8147349185734</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.112152342078116</v>
+        <v>0.1119475109414818</v>
       </c>
       <c r="C18">
-        <v>16.29953067310716</v>
+        <v>16.17575663242857</v>
       </c>
       <c r="D18">
-        <v>19.23281067310716</v>
+        <v>19.29236663242857</v>
       </c>
       <c r="E18">
-        <v>2.90028</v>
+        <v>3.083610000000001</v>
       </c>
       <c r="F18">
-        <v>2.93328</v>
+        <v>3.116610000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2876,28 +2876,28 @@
         <v>0.781</v>
       </c>
       <c r="M18">
-        <v>0.162210384</v>
+        <v>0.172348533</v>
       </c>
       <c r="N18">
-        <v>0.618789616</v>
+        <v>0.6086514670000001</v>
       </c>
       <c r="O18">
-        <v>0.14850950784</v>
+        <v>0.14607635208</v>
       </c>
       <c r="P18">
-        <v>0.47028010816</v>
+        <v>0.46257511492</v>
       </c>
       <c r="Q18">
-        <v>0.60228010816</v>
+        <v>0.59457511492</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1255093596168048</v>
+        <v>0.1262683746282913</v>
       </c>
       <c r="T18">
-        <v>1.344014315327785</v>
+        <v>1.356812398838814</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.8147349185734</v>
+        <v>4.531515217480847</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1119475109414818</v>
+        <v>0.1120846798048475</v>
       </c>
       <c r="C19">
-        <v>16.17575663242857</v>
+        <v>15.95250319898367</v>
       </c>
       <c r="D19">
-        <v>19.29236663242857</v>
+        <v>19.25244319898367</v>
       </c>
       <c r="E19">
-        <v>3.083610000000001</v>
+        <v>3.266940000000001</v>
       </c>
       <c r="F19">
-        <v>3.116610000000001</v>
+        <v>3.299940000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2958,45 +2958,45 @@
         <v>0.781</v>
       </c>
       <c r="M19">
-        <v>0.172348533</v>
+        <v>0.1907365320000001</v>
       </c>
       <c r="N19">
-        <v>0.6086514670000001</v>
+        <v>0.590263468</v>
       </c>
       <c r="O19">
-        <v>0.14607635208</v>
+        <v>0.14166323232</v>
       </c>
       <c r="P19">
-        <v>0.46257511492</v>
+        <v>0.44860023568</v>
       </c>
       <c r="Q19">
-        <v>0.59457511492</v>
+        <v>0.58060023568</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1262683746282913</v>
+        <v>0.1270459022010336</v>
       </c>
       <c r="T19">
-        <v>1.356812398838814</v>
+        <v>1.369922630728162</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.531515217480847</v>
+        <v>4.094653456318477</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1120846798048475</v>
+        <v>0.1124042486682133</v>
       </c>
       <c r="C20">
-        <v>15.95250319898366</v>
+        <v>15.67679949140291</v>
       </c>
       <c r="D20">
-        <v>19.25244319898366</v>
+        <v>19.16006949140291</v>
       </c>
       <c r="E20">
-        <v>3.26694</v>
+        <v>3.450270000000001</v>
       </c>
       <c r="F20">
-        <v>3.29994</v>
+        <v>3.483270000000001</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3040,45 +3040,45 @@
         <v>0.781</v>
       </c>
       <c r="M20">
-        <v>0.190736532</v>
+        <v>0.213524451</v>
       </c>
       <c r="N20">
-        <v>0.590263468</v>
+        <v>0.567475549</v>
       </c>
       <c r="O20">
-        <v>0.14166323232</v>
+        <v>0.13619413176</v>
       </c>
       <c r="P20">
-        <v>0.44860023568</v>
+        <v>0.43128141724</v>
       </c>
       <c r="Q20">
-        <v>0.58060023568</v>
+        <v>0.56328141724</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1270459022010336</v>
+        <v>0.1278426279854485</v>
       </c>
       <c r="T20">
-        <v>1.369922630728162</v>
+        <v>1.383356572046876</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.094653456318477</v>
+        <v>3.657660733196312</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1124042486682133</v>
+        <v>0.1126706175315791</v>
       </c>
       <c r="C21">
-        <v>15.67679949140291</v>
+        <v>15.41714828904489</v>
       </c>
       <c r="D21">
-        <v>19.16006949140291</v>
+        <v>19.08374828904489</v>
       </c>
       <c r="E21">
-        <v>3.450270000000001</v>
+        <v>3.633600000000001</v>
       </c>
       <c r="F21">
-        <v>3.483270000000001</v>
+        <v>3.666600000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3122,45 +3122,45 @@
         <v>0.781</v>
       </c>
       <c r="M21">
-        <v>0.213524451</v>
+        <v>0.2350290600000001</v>
       </c>
       <c r="N21">
-        <v>0.567475549</v>
+        <v>0.5459709399999999</v>
       </c>
       <c r="O21">
-        <v>0.13619413176</v>
+        <v>0.1310330256</v>
       </c>
       <c r="P21">
-        <v>0.43128141724</v>
+        <v>0.4149379143999999</v>
       </c>
       <c r="Q21">
-        <v>0.56328141724</v>
+        <v>0.5469379143999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1278426279854485</v>
+        <v>0.1286592719144738</v>
       </c>
       <c r="T21">
-        <v>1.383356572046876</v>
+        <v>1.397126361898558</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.657660733196312</v>
+        <v>3.322993335377335</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1126706175315791</v>
+        <v>0.1125326663949448</v>
       </c>
       <c r="C22">
-        <v>15.41714828904489</v>
+        <v>15.2732686049087</v>
       </c>
       <c r="D22">
-        <v>19.08374828904489</v>
+        <v>19.1231986049087</v>
       </c>
       <c r="E22">
-        <v>3.633600000000001</v>
+        <v>3.816930000000001</v>
       </c>
       <c r="F22">
-        <v>3.666600000000001</v>
+        <v>3.849930000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3204,28 +3204,28 @@
         <v>0.781</v>
       </c>
       <c r="M22">
-        <v>0.2350290600000001</v>
+        <v>0.2467805130000001</v>
       </c>
       <c r="N22">
-        <v>0.5459709399999999</v>
+        <v>0.5342194869999999</v>
       </c>
       <c r="O22">
-        <v>0.1310330256</v>
+        <v>0.12821267688</v>
       </c>
       <c r="P22">
-        <v>0.4149379143999999</v>
+        <v>0.40600681012</v>
       </c>
       <c r="Q22">
-        <v>0.5469379143999999</v>
+        <v>0.53800681012</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1286592719144738</v>
+        <v>0.1294965903733479</v>
       </c>
       <c r="T22">
-        <v>1.397126361898558</v>
+        <v>1.411244754024966</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.322993335377335</v>
+        <v>3.164755557502223</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1125326663949448</v>
+        <v>0.1123947152583106</v>
       </c>
       <c r="C23">
-        <v>15.2732686049087</v>
+        <v>15.12955236364912</v>
       </c>
       <c r="D23">
-        <v>19.1231986049087</v>
+        <v>19.16281236364912</v>
       </c>
       <c r="E23">
-        <v>3.81693</v>
+        <v>4.00026</v>
       </c>
       <c r="F23">
-        <v>3.84993</v>
+        <v>4.03326</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3286,28 +3286,28 @@
         <v>0.781</v>
       </c>
       <c r="M23">
-        <v>0.246780513</v>
+        <v>0.2585319660000001</v>
       </c>
       <c r="N23">
-        <v>0.534219487</v>
+        <v>0.522468034</v>
       </c>
       <c r="O23">
-        <v>0.12821267688</v>
+        <v>0.12539232816</v>
       </c>
       <c r="P23">
-        <v>0.40600681012</v>
+        <v>0.39707570584</v>
       </c>
       <c r="Q23">
-        <v>0.53800681012</v>
+        <v>0.52907570584</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1294965903733479</v>
+        <v>0.1303553785362956</v>
       </c>
       <c r="T23">
-        <v>1.411244754024966</v>
+        <v>1.425725156205897</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.164755557502224</v>
+        <v>3.020903032161214</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1123947152583106</v>
+        <v>0.1136202041216764</v>
       </c>
       <c r="C24">
-        <v>15.12955236364912</v>
+        <v>14.59995662401366</v>
       </c>
       <c r="D24">
-        <v>19.16281236364912</v>
+        <v>18.81654662401366</v>
       </c>
       <c r="E24">
-        <v>4.00026</v>
+        <v>4.183590000000001</v>
       </c>
       <c r="F24">
-        <v>4.03326</v>
+        <v>4.216590000000001</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3368,45 +3368,45 @@
         <v>0.781</v>
       </c>
       <c r="M24">
-        <v>0.2585319660000001</v>
+        <v>0.3031728210000001</v>
       </c>
       <c r="N24">
-        <v>0.522468034</v>
+        <v>0.4778271789999999</v>
       </c>
       <c r="O24">
-        <v>0.12539232816</v>
+        <v>0.11467852296</v>
       </c>
       <c r="P24">
-        <v>0.39707570584</v>
+        <v>0.36314865604</v>
       </c>
       <c r="Q24">
-        <v>0.52907570584</v>
+        <v>0.49514865604</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1303553785362956</v>
+        <v>0.131236472885294</v>
       </c>
       <c r="T24">
-        <v>1.425725156205897</v>
+        <v>1.440581672729191</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.020903032161214</v>
+        <v>2.576088441648269</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1136202041216764</v>
+        <v>0.1142528929850421</v>
       </c>
       <c r="C25">
-        <v>14.59995662401366</v>
+        <v>14.24271111837363</v>
       </c>
       <c r="D25">
-        <v>18.81654662401366</v>
+        <v>18.64263111837364</v>
       </c>
       <c r="E25">
-        <v>4.183590000000001</v>
+        <v>4.36692</v>
       </c>
       <c r="F25">
-        <v>4.216590000000001</v>
+        <v>4.399920000000001</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3450,45 +3450,45 @@
         <v>0.781</v>
       </c>
       <c r="M25">
-        <v>0.3031728210000001</v>
+        <v>0.3335139360000001</v>
       </c>
       <c r="N25">
-        <v>0.4778271789999999</v>
+        <v>0.447486064</v>
       </c>
       <c r="O25">
-        <v>0.11467852296</v>
+        <v>0.10739665536</v>
       </c>
       <c r="P25">
-        <v>0.36314865604</v>
+        <v>0.34008940864</v>
       </c>
       <c r="Q25">
-        <v>0.49514865604</v>
+        <v>0.47208940864</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.131236472885294</v>
+        <v>0.132140753927687</v>
       </c>
       <c r="T25">
-        <v>1.440581672729191</v>
+        <v>1.455829150213623</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.576088441648269</v>
+        <v>2.341731231285039</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1142528929850421</v>
+        <v>0.1142038618484079</v>
       </c>
       <c r="C26">
-        <v>14.24271111837363</v>
+        <v>14.07274395153666</v>
       </c>
       <c r="D26">
-        <v>18.64263111837364</v>
+        <v>18.65599395153666</v>
       </c>
       <c r="E26">
-        <v>4.36692</v>
+        <v>4.55025</v>
       </c>
       <c r="F26">
-        <v>4.399920000000001</v>
+        <v>4.58325</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3532,28 +3532,28 @@
         <v>0.781</v>
       </c>
       <c r="M26">
-        <v>0.3335139360000001</v>
+        <v>0.3474103500000001</v>
       </c>
       <c r="N26">
-        <v>0.447486064</v>
+        <v>0.4335896499999999</v>
       </c>
       <c r="O26">
-        <v>0.10739665536</v>
+        <v>0.104061516</v>
       </c>
       <c r="P26">
-        <v>0.34008940864</v>
+        <v>0.329528134</v>
       </c>
       <c r="Q26">
-        <v>0.47208940864</v>
+        <v>0.461528134</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.132140753927687</v>
+        <v>0.1330691491312105</v>
       </c>
       <c r="T26">
-        <v>1.455829150213623</v>
+        <v>1.471483227097641</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.341731231285039</v>
+        <v>2.248061982033638</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1142038618484079</v>
+        <v>0.1141548307117737</v>
       </c>
       <c r="C27">
-        <v>14.07274395153666</v>
+        <v>13.9027959551048</v>
       </c>
       <c r="D27">
-        <v>18.65599395153666</v>
+        <v>18.6693759551048</v>
       </c>
       <c r="E27">
-        <v>4.55025</v>
+        <v>4.73358</v>
       </c>
       <c r="F27">
-        <v>4.58325</v>
+        <v>4.76658</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3614,28 +3614,28 @@
         <v>0.781</v>
       </c>
       <c r="M27">
-        <v>0.3474103500000001</v>
+        <v>0.3613067640000001</v>
       </c>
       <c r="N27">
-        <v>0.4335896499999999</v>
+        <v>0.419693236</v>
       </c>
       <c r="O27">
-        <v>0.104061516</v>
+        <v>0.10072637664</v>
       </c>
       <c r="P27">
-        <v>0.329528134</v>
+        <v>0.31896685936</v>
       </c>
       <c r="Q27">
-        <v>0.461528134</v>
+        <v>0.45096685936</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1330691491312105</v>
+        <v>0.1340226360969914</v>
       </c>
       <c r="T27">
-        <v>1.471483227097641</v>
+        <v>1.487560387140686</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.248061982033638</v>
+        <v>2.161598059647729</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1141548307117737</v>
+        <v>0.1141057995751394</v>
       </c>
       <c r="C28">
-        <v>13.9027959551048</v>
+        <v>13.73286717036068</v>
       </c>
       <c r="D28">
-        <v>18.6693759551048</v>
+        <v>18.68277717036068</v>
       </c>
       <c r="E28">
-        <v>4.73358</v>
+        <v>4.916910000000001</v>
       </c>
       <c r="F28">
-        <v>4.76658</v>
+        <v>4.949910000000001</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3696,28 +3696,28 @@
         <v>0.781</v>
       </c>
       <c r="M28">
-        <v>0.3613067640000001</v>
+        <v>0.3752031780000001</v>
       </c>
       <c r="N28">
-        <v>0.419693236</v>
+        <v>0.4057968219999999</v>
       </c>
       <c r="O28">
-        <v>0.10072637664</v>
+        <v>0.09739123727999999</v>
       </c>
       <c r="P28">
-        <v>0.31896685936</v>
+        <v>0.30840558472</v>
       </c>
       <c r="Q28">
-        <v>0.45096685936</v>
+        <v>0.44040558472</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1340226360969914</v>
+        <v>0.1350022459933417</v>
       </c>
       <c r="T28">
-        <v>1.487560387140686</v>
+        <v>1.504078017321896</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.161598059647729</v>
+        <v>2.081538872253368</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1141057995751394</v>
+        <v>0.1140567684385052</v>
       </c>
       <c r="C29">
-        <v>13.73286717036068</v>
+        <v>13.56295763870546</v>
       </c>
       <c r="D29">
-        <v>18.68277717036068</v>
+        <v>18.69619763870546</v>
       </c>
       <c r="E29">
-        <v>4.916910000000001</v>
+        <v>5.10024</v>
       </c>
       <c r="F29">
-        <v>4.949910000000001</v>
+        <v>5.133240000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3778,28 +3778,28 @@
         <v>0.781</v>
       </c>
       <c r="M29">
-        <v>0.3752031780000001</v>
+        <v>0.3890995920000001</v>
       </c>
       <c r="N29">
-        <v>0.4057968219999999</v>
+        <v>0.3919004079999999</v>
       </c>
       <c r="O29">
-        <v>0.09739123727999999</v>
+        <v>0.09405609791999998</v>
       </c>
       <c r="P29">
-        <v>0.30840558472</v>
+        <v>0.29784431008</v>
       </c>
       <c r="Q29">
-        <v>0.44040558472</v>
+        <v>0.42984431008</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1350022459933417</v>
+        <v>0.1360090672757017</v>
       </c>
       <c r="T29">
-        <v>1.504078017321896</v>
+        <v>1.521054470563696</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.081538872253368</v>
+        <v>2.007198198244319</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1140567684385052</v>
+        <v>0.117137417301871</v>
       </c>
       <c r="C30">
-        <v>13.56295763870546</v>
+        <v>12.57224741408624</v>
       </c>
       <c r="D30">
-        <v>18.69619763870546</v>
+        <v>17.88881741408624</v>
       </c>
       <c r="E30">
-        <v>5.10024</v>
+        <v>5.283570000000001</v>
       </c>
       <c r="F30">
-        <v>5.133240000000001</v>
+        <v>5.316570000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3860,45 +3860,45 @@
         <v>0.781</v>
       </c>
       <c r="M30">
-        <v>0.3890995920000001</v>
+        <v>0.4784913000000001</v>
       </c>
       <c r="N30">
-        <v>0.3919004079999999</v>
+        <v>0.3025086999999999</v>
       </c>
       <c r="O30">
-        <v>0.09405609791999998</v>
+        <v>0.07260208799999998</v>
       </c>
       <c r="P30">
-        <v>0.29784431008</v>
+        <v>0.2299066119999999</v>
       </c>
       <c r="Q30">
-        <v>0.42984431008</v>
+        <v>0.361906612</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1360090672757017</v>
+        <v>0.137044249720945</v>
       </c>
       <c r="T30">
-        <v>1.521054470563696</v>
+        <v>1.538509133755969</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.007198198244319</v>
+        <v>1.632213584656607</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.117137417301871</v>
+        <v>0.1171963061652367</v>
       </c>
       <c r="C31">
-        <v>12.57224741408625</v>
+        <v>12.37416241931054</v>
       </c>
       <c r="D31">
-        <v>17.88881741408625</v>
+        <v>17.87406241931054</v>
       </c>
       <c r="E31">
-        <v>5.28357</v>
+        <v>5.4669</v>
       </c>
       <c r="F31">
-        <v>5.31657</v>
+        <v>5.4999</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3942,28 +3942,28 @@
         <v>0.781</v>
       </c>
       <c r="M31">
-        <v>0.4784913</v>
+        <v>0.494991</v>
       </c>
       <c r="N31">
-        <v>0.3025087</v>
+        <v>0.286009</v>
       </c>
       <c r="O31">
-        <v>0.072602088</v>
+        <v>0.06864215999999999</v>
       </c>
       <c r="P31">
-        <v>0.229906612</v>
+        <v>0.21736684</v>
       </c>
       <c r="Q31">
-        <v>0.361906612</v>
+        <v>0.34936684</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.137044249720945</v>
+        <v>0.138109008807481</v>
       </c>
       <c r="T31">
-        <v>1.538509133755969</v>
+        <v>1.556462501610878</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.632213584656607</v>
+        <v>1.577806465168054</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1171963061652367</v>
+        <v>0.1172551950286025</v>
       </c>
       <c r="C32">
-        <v>12.37416241931054</v>
+        <v>12.17610174480631</v>
       </c>
       <c r="D32">
-        <v>17.87406241931054</v>
+        <v>17.85933174480632</v>
       </c>
       <c r="E32">
-        <v>5.4669</v>
+        <v>5.650230000000001</v>
       </c>
       <c r="F32">
-        <v>5.4999</v>
+        <v>5.683230000000001</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4024,28 +4024,28 @@
         <v>0.781</v>
       </c>
       <c r="M32">
-        <v>0.494991</v>
+        <v>0.5114907000000001</v>
       </c>
       <c r="N32">
-        <v>0.286009</v>
+        <v>0.2695093</v>
       </c>
       <c r="O32">
-        <v>0.06864215999999999</v>
+        <v>0.06468223199999999</v>
       </c>
       <c r="P32">
-        <v>0.21736684</v>
+        <v>0.2048270679999999</v>
       </c>
       <c r="Q32">
-        <v>0.34936684</v>
+        <v>0.336827068</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.138109008807481</v>
+        <v>0.1392046304762355</v>
       </c>
       <c r="T32">
-        <v>1.556462501610878</v>
+        <v>1.574936256939843</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.577806465168054</v>
+        <v>1.526909482420697</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1172551950286025</v>
+        <v>0.1326759558290054</v>
       </c>
       <c r="C33">
-        <v>12.17610174480631</v>
+        <v>8.822683079148714</v>
       </c>
       <c r="D33">
-        <v>17.85933174480632</v>
+        <v>14.68924307914872</v>
       </c>
       <c r="E33">
-        <v>5.650230000000001</v>
+        <v>5.83356</v>
       </c>
       <c r="F33">
-        <v>5.683230000000001</v>
+        <v>5.866560000000001</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4106,45 +4106,45 @@
         <v>0.781</v>
       </c>
       <c r="M33">
-        <v>0.5114907000000001</v>
+        <v>0.8612110080000002</v>
       </c>
       <c r="N33">
-        <v>0.2695093</v>
+        <v>-0.08021100800000014</v>
       </c>
       <c r="O33">
-        <v>0.06468223199999999</v>
+        <v>-0.01925064192000003</v>
       </c>
       <c r="P33">
-        <v>0.2048270679999999</v>
+        <v>-0.06096036608000011</v>
       </c>
       <c r="Q33">
-        <v>0.336827068</v>
+        <v>0.0710396339199999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1392046304762355</v>
+        <v>0.1410649142989623</v>
       </c>
       <c r="T33">
-        <v>1.574936256939843</v>
+        <v>1.606303314714955</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.24</v>
+        <v>0.2176470089894624</v>
       </c>
       <c r="W33">
-        <v>0.0684</v>
+        <v>0.1148494190803469</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.526909482420697</v>
+        <v>0.9068625374560934</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1326759558290054</v>
+        <v>0.1336859558290054</v>
       </c>
       <c r="C34">
-        <v>8.822683079148714</v>
+        <v>8.470541858174954</v>
       </c>
       <c r="D34">
-        <v>14.68924307914872</v>
+        <v>14.52043185817496</v>
       </c>
       <c r="E34">
-        <v>5.83356</v>
+        <v>6.016890000000001</v>
       </c>
       <c r="F34">
-        <v>5.866560000000001</v>
+        <v>6.049890000000001</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4188,37 +4188,37 @@
         <v>0.781</v>
       </c>
       <c r="M34">
-        <v>0.8612110080000002</v>
+        <v>0.8881238520000003</v>
       </c>
       <c r="N34">
-        <v>-0.08021100800000014</v>
+        <v>-0.1071238520000003</v>
       </c>
       <c r="O34">
-        <v>-0.01925064192000003</v>
+        <v>-0.02570972448000007</v>
       </c>
       <c r="P34">
-        <v>-0.06096036608000011</v>
+        <v>-0.08141412752000023</v>
       </c>
       <c r="Q34">
-        <v>0.0710396339199999</v>
+        <v>0.05058587247999978</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1410649142989623</v>
+        <v>0.1424867786914841</v>
       </c>
       <c r="T34">
-        <v>1.606303314714955</v>
+        <v>1.630277991053985</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2176470089894624</v>
+        <v>0.2110516450806908</v>
       </c>
       <c r="W34">
-        <v>0.1148494190803469</v>
+        <v>0.1158176185021546</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9068625374560934</v>
+        <v>0.8793818545028782</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1336859558290054</v>
+        <v>0.1346959558290054</v>
       </c>
       <c r="C35">
-        <v>8.470541858174954</v>
+        <v>8.122236567229589</v>
       </c>
       <c r="D35">
-        <v>14.52043185817496</v>
+        <v>14.35545656722959</v>
       </c>
       <c r="E35">
-        <v>6.016890000000001</v>
+        <v>6.200220000000001</v>
       </c>
       <c r="F35">
-        <v>6.049890000000001</v>
+        <v>6.233220000000001</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4270,37 +4270,37 @@
         <v>0.781</v>
       </c>
       <c r="M35">
-        <v>0.8881238520000003</v>
+        <v>0.9150366960000003</v>
       </c>
       <c r="N35">
-        <v>-0.1071238520000003</v>
+        <v>-0.1340366960000002</v>
       </c>
       <c r="O35">
-        <v>-0.02570972448000007</v>
+        <v>-0.03216880704000005</v>
       </c>
       <c r="P35">
-        <v>-0.08141412752000023</v>
+        <v>-0.1018678889600002</v>
       </c>
       <c r="Q35">
-        <v>0.05058587247999978</v>
+        <v>0.03013211103999983</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1424867786914841</v>
+        <v>0.1439517298837794</v>
       </c>
       <c r="T35">
-        <v>1.630277991053985</v>
+        <v>1.654979172736621</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2110516450806908</v>
+        <v>0.2048442437547881</v>
       </c>
       <c r="W35">
-        <v>0.1158176185021546</v>
+        <v>0.1167288650167971</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8793818545028782</v>
+        <v>0.8535176823116172</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1346959558290054</v>
+        <v>0.1357059558290054</v>
       </c>
       <c r="C36">
-        <v>8.122236567229589</v>
+        <v>7.777637928247788</v>
       </c>
       <c r="D36">
-        <v>14.35545656722959</v>
+        <v>14.19418792824779</v>
       </c>
       <c r="E36">
-        <v>6.200220000000001</v>
+        <v>6.383550000000001</v>
       </c>
       <c r="F36">
-        <v>6.233220000000001</v>
+        <v>6.416550000000001</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4352,37 +4352,37 @@
         <v>0.781</v>
       </c>
       <c r="M36">
-        <v>0.9150366960000003</v>
+        <v>0.9419495400000002</v>
       </c>
       <c r="N36">
-        <v>-0.1340366960000002</v>
+        <v>-0.1609495400000002</v>
       </c>
       <c r="O36">
-        <v>-0.03216880704000005</v>
+        <v>-0.03862788960000004</v>
       </c>
       <c r="P36">
-        <v>-0.1018678889600002</v>
+        <v>-0.1223216504000001</v>
       </c>
       <c r="Q36">
-        <v>0.03013211103999983</v>
+        <v>0.009678349599999886</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1439517298837794</v>
+        <v>0.1454617564973759</v>
       </c>
       <c r="T36">
-        <v>1.654979172736621</v>
+        <v>1.680440390778722</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2048442437547881</v>
+        <v>0.1989915510760799</v>
       </c>
       <c r="W36">
-        <v>0.1167288650167971</v>
+        <v>0.1175880403020315</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8535176823116172</v>
+        <v>0.8291314628169996</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1357059558290054</v>
+        <v>0.1367159558290054</v>
       </c>
       <c r="C37">
-        <v>7.777637928247788</v>
+        <v>7.436622407848115</v>
       </c>
       <c r="D37">
-        <v>14.19418792824779</v>
+        <v>14.03650240784812</v>
       </c>
       <c r="E37">
-        <v>6.383550000000001</v>
+        <v>6.566880000000001</v>
       </c>
       <c r="F37">
-        <v>6.416550000000001</v>
+        <v>6.599880000000002</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4434,37 +4434,37 @@
         <v>0.781</v>
       </c>
       <c r="M37">
-        <v>0.9419495400000002</v>
+        <v>0.9688623840000004</v>
       </c>
       <c r="N37">
-        <v>-0.1609495400000002</v>
+        <v>-0.1878623840000003</v>
       </c>
       <c r="O37">
-        <v>-0.03862788960000004</v>
+        <v>-0.04508697216000008</v>
       </c>
       <c r="P37">
-        <v>-0.1223216504000001</v>
+        <v>-0.1427754118400003</v>
       </c>
       <c r="Q37">
-        <v>0.009678349599999886</v>
+        <v>-0.01077541184000025</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1454617564973759</v>
+        <v>0.1470189714426474</v>
       </c>
       <c r="T37">
-        <v>1.680440390778722</v>
+        <v>1.70669727188464</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1989915510760799</v>
+        <v>0.1934640079906332</v>
       </c>
       <c r="W37">
-        <v>0.1175880403020315</v>
+        <v>0.1183994836269751</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8291314628169996</v>
+        <v>0.806100033294305</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1367159558290054</v>
+        <v>0.1590101038430111</v>
       </c>
       <c r="C38">
-        <v>7.436622407848112</v>
+        <v>4.489123383558047</v>
       </c>
       <c r="D38">
-        <v>14.03650240784811</v>
+        <v>11.27233338355805</v>
       </c>
       <c r="E38">
-        <v>6.56688</v>
+        <v>6.75021</v>
       </c>
       <c r="F38">
-        <v>6.599880000000001</v>
+        <v>6.78321</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4516,45 +4516,45 @@
         <v>0.781</v>
       </c>
       <c r="M38">
-        <v>0.9688623840000001</v>
+        <v>1.362068568</v>
       </c>
       <c r="N38">
-        <v>-0.1878623840000001</v>
+        <v>-0.5810685680000002</v>
       </c>
       <c r="O38">
-        <v>-0.04508697216000002</v>
+        <v>-0.13945645632</v>
       </c>
       <c r="P38">
-        <v>-0.1427754118400001</v>
+        <v>-0.4416121116800001</v>
       </c>
       <c r="Q38">
-        <v>-0.01077541184000008</v>
+        <v>-0.3096121116800001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1470189714426474</v>
+        <v>0.1506956979957144</v>
       </c>
       <c r="T38">
-        <v>1.70669727188464</v>
+        <v>1.768692163634165</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1934640079906333</v>
+        <v>0.1376142173776379</v>
       </c>
       <c r="W38">
-        <v>0.1183994836269751</v>
+        <v>0.1731670651505703</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8061000332943052</v>
+        <v>0.5733925724068246</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1590101038430111</v>
+        <v>0.1605601038430111</v>
       </c>
       <c r="C39">
-        <v>4.489123383558047</v>
+        <v>4.153544333936966</v>
       </c>
       <c r="D39">
-        <v>11.27233338355805</v>
+        <v>11.12008433393697</v>
       </c>
       <c r="E39">
-        <v>6.75021</v>
+        <v>6.933540000000001</v>
       </c>
       <c r="F39">
-        <v>6.78321</v>
+        <v>6.966540000000001</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4598,37 +4598,37 @@
         <v>0.781</v>
       </c>
       <c r="M39">
-        <v>1.362068568</v>
+        <v>1.398881232</v>
       </c>
       <c r="N39">
-        <v>-0.5810685680000002</v>
+        <v>-0.6178812320000003</v>
       </c>
       <c r="O39">
-        <v>-0.13945645632</v>
+        <v>-0.1482914956800001</v>
       </c>
       <c r="P39">
-        <v>-0.4416121116800001</v>
+        <v>-0.4695897363200002</v>
       </c>
       <c r="Q39">
-        <v>-0.3096121116800001</v>
+        <v>-0.3375897363200002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1506956979957144</v>
+        <v>0.1523875640924194</v>
       </c>
       <c r="T39">
-        <v>1.768692163634165</v>
+        <v>1.797219456596006</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1376142173776379</v>
+        <v>0.1339927906045422</v>
       </c>
       <c r="W39">
-        <v>0.1731670651505703</v>
+        <v>0.1738942476466079</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5733925724068246</v>
+        <v>0.5583032941855923</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1605601038430111</v>
+        <v>0.1621101038430111</v>
       </c>
       <c r="C40">
-        <v>4.153544333936966</v>
+        <v>3.822023160959707</v>
       </c>
       <c r="D40">
-        <v>11.12008433393697</v>
+        <v>10.97189316095971</v>
       </c>
       <c r="E40">
-        <v>6.933540000000001</v>
+        <v>7.11687</v>
       </c>
       <c r="F40">
-        <v>6.966540000000001</v>
+        <v>7.149870000000001</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4680,37 +4680,37 @@
         <v>0.781</v>
       </c>
       <c r="M40">
-        <v>1.398881232</v>
+        <v>1.435693896</v>
       </c>
       <c r="N40">
-        <v>-0.6178812320000003</v>
+        <v>-0.6546938960000003</v>
       </c>
       <c r="O40">
-        <v>-0.1482914956800001</v>
+        <v>-0.1571265350400001</v>
       </c>
       <c r="P40">
-        <v>-0.4695897363200002</v>
+        <v>-0.4975673609600002</v>
       </c>
       <c r="Q40">
-        <v>-0.3375897363200002</v>
+        <v>-0.3655673609600002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1523875640924194</v>
+        <v>0.1541349012086886</v>
       </c>
       <c r="T40">
-        <v>1.797219456596006</v>
+        <v>1.826682070638564</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1339927906045422</v>
+        <v>0.1305570780249385</v>
       </c>
       <c r="W40">
-        <v>0.1738942476466079</v>
+        <v>0.1745841387325923</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5583032941855923</v>
+        <v>0.5439878251039105</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1621101038430111</v>
+        <v>0.1636601038430111</v>
       </c>
       <c r="C41">
-        <v>3.822023160959707</v>
+        <v>3.49439976697</v>
       </c>
       <c r="D41">
-        <v>10.97189316095971</v>
+        <v>10.82759976697</v>
       </c>
       <c r="E41">
-        <v>7.11687</v>
+        <v>7.300200000000001</v>
       </c>
       <c r="F41">
-        <v>7.149870000000001</v>
+        <v>7.333200000000001</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4762,37 +4762,37 @@
         <v>0.781</v>
       </c>
       <c r="M41">
-        <v>1.435693896</v>
+        <v>1.47250656</v>
       </c>
       <c r="N41">
-        <v>-0.6546938960000003</v>
+        <v>-0.6915065600000002</v>
       </c>
       <c r="O41">
-        <v>-0.1571265350400001</v>
+        <v>-0.1659615744</v>
       </c>
       <c r="P41">
-        <v>-0.4975673609600002</v>
+        <v>-0.5255449856000002</v>
       </c>
       <c r="Q41">
-        <v>-0.3655673609600002</v>
+        <v>-0.3935449856000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1541349012086886</v>
+        <v>0.1559404828955001</v>
       </c>
       <c r="T41">
-        <v>1.826682070638564</v>
+        <v>1.857126771815873</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1305570780249385</v>
+        <v>0.127293151074315</v>
       </c>
       <c r="W41">
-        <v>0.1745841387325923</v>
+        <v>0.1752395352642775</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5439878251039105</v>
+        <v>0.5303881294763128</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1636601038430111</v>
+        <v>0.1652101038430111</v>
       </c>
       <c r="C42">
-        <v>3.49439976697</v>
+        <v>3.170522366886768</v>
       </c>
       <c r="D42">
-        <v>10.82759976697</v>
+        <v>10.68705236688677</v>
       </c>
       <c r="E42">
-        <v>7.300200000000001</v>
+        <v>7.483530000000001</v>
       </c>
       <c r="F42">
-        <v>7.333200000000001</v>
+        <v>7.516530000000001</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4844,37 +4844,37 @@
         <v>0.781</v>
       </c>
       <c r="M42">
-        <v>1.47250656</v>
+        <v>1.509319224</v>
       </c>
       <c r="N42">
-        <v>-0.6915065600000002</v>
+        <v>-0.7283192240000004</v>
       </c>
       <c r="O42">
-        <v>-0.1659615744</v>
+        <v>-0.1747966137600001</v>
       </c>
       <c r="P42">
-        <v>-0.5255449856000002</v>
+        <v>-0.5535226102400003</v>
       </c>
       <c r="Q42">
-        <v>-0.3935449856000002</v>
+        <v>-0.4215226102400003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1559404828955001</v>
+        <v>0.1578072707411866</v>
       </c>
       <c r="T42">
-        <v>1.857126771815873</v>
+        <v>1.888603496761905</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.127293151074315</v>
+        <v>0.1241884400725025</v>
       </c>
       <c r="W42">
-        <v>0.1752395352642775</v>
+        <v>0.1758629612334415</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5303881294763128</v>
+        <v>0.517451833635427</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1652101038430111</v>
+        <v>0.1667601038430111</v>
       </c>
       <c r="C43">
-        <v>3.170522366886768</v>
+        <v>2.850246955611548</v>
       </c>
       <c r="D43">
-        <v>10.68705236688677</v>
+        <v>10.55010695561155</v>
       </c>
       <c r="E43">
-        <v>7.483530000000001</v>
+        <v>7.666860000000002</v>
       </c>
       <c r="F43">
-        <v>7.516530000000001</v>
+        <v>7.699860000000002</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4926,37 +4926,37 @@
         <v>0.781</v>
       </c>
       <c r="M43">
-        <v>1.509319224</v>
+        <v>1.546131888</v>
       </c>
       <c r="N43">
-        <v>-0.7283192240000004</v>
+        <v>-0.7651318880000003</v>
       </c>
       <c r="O43">
-        <v>-0.1747966137600001</v>
+        <v>-0.1836316531200001</v>
       </c>
       <c r="P43">
-        <v>-0.5535226102400003</v>
+        <v>-0.5815002348800002</v>
       </c>
       <c r="Q43">
-        <v>-0.4215226102400003</v>
+        <v>-0.4495002348800002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1578072707411866</v>
+        <v>0.1597384305815518</v>
       </c>
       <c r="T43">
-        <v>1.888603496761905</v>
+        <v>1.92116562601642</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1241884400725025</v>
+        <v>0.1212315724517286</v>
       </c>
       <c r="W43">
-        <v>0.1758629612334415</v>
+        <v>0.1764567002516929</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.517451833635427</v>
+        <v>0.5051315518822026</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1667601038430111</v>
+        <v>0.1838863433190235</v>
       </c>
       <c r="C44">
-        <v>2.850246955611552</v>
+        <v>1.358433771275855</v>
       </c>
       <c r="D44">
-        <v>10.55010695561155</v>
+        <v>9.241623771275856</v>
       </c>
       <c r="E44">
-        <v>7.66686</v>
+        <v>7.85019</v>
       </c>
       <c r="F44">
-        <v>7.69986</v>
+        <v>7.883190000000001</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5008,45 +5008,45 @@
         <v>0.781</v>
       </c>
       <c r="M44">
-        <v>1.546131888</v>
+        <v>1.858856202</v>
       </c>
       <c r="N44">
-        <v>-0.7651318880000001</v>
+        <v>-1.077856202</v>
       </c>
       <c r="O44">
-        <v>-0.18363165312</v>
+        <v>-0.2586854884800001</v>
       </c>
       <c r="P44">
-        <v>-0.58150023488</v>
+        <v>-0.8191707135200004</v>
       </c>
       <c r="Q44">
-        <v>-0.44950023488</v>
+        <v>-0.6871707135200004</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1597384305815518</v>
+        <v>0.1626605775672149</v>
       </c>
       <c r="T44">
-        <v>1.92116562601642</v>
+        <v>1.970437222214203</v>
       </c>
       <c r="U44">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1212315724517287</v>
+        <v>0.1008362022830639</v>
       </c>
       <c r="W44">
-        <v>0.1764567002516929</v>
+        <v>0.2120228235016535</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.5051315518822026</v>
+        <v>0.4201508428460997</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1838863433190235</v>
+        <v>0.1857863433190235</v>
       </c>
       <c r="C45">
-        <v>1.358433771275855</v>
+        <v>1.049669498552495</v>
       </c>
       <c r="D45">
-        <v>9.241623771275856</v>
+        <v>9.116189498552496</v>
       </c>
       <c r="E45">
-        <v>7.85019</v>
+        <v>8.033520000000001</v>
       </c>
       <c r="F45">
-        <v>7.883190000000001</v>
+        <v>8.066520000000001</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5090,37 +5090,37 @@
         <v>0.781</v>
       </c>
       <c r="M45">
-        <v>1.858856202</v>
+        <v>1.902085416</v>
       </c>
       <c r="N45">
-        <v>-1.077856202</v>
+        <v>-1.121085416</v>
       </c>
       <c r="O45">
-        <v>-0.2586854884800001</v>
+        <v>-0.26906049984</v>
       </c>
       <c r="P45">
-        <v>-0.8191707135200004</v>
+        <v>-0.8520249161600001</v>
       </c>
       <c r="Q45">
-        <v>-0.6871707135200004</v>
+        <v>-0.7200249161600001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1626605775672149</v>
+        <v>0.1647473735952009</v>
       </c>
       <c r="T45">
-        <v>1.970437222214203</v>
+        <v>2.005623601182314</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1008362022830639</v>
+        <v>0.0985444704129943</v>
       </c>
       <c r="W45">
-        <v>0.2120228235016535</v>
+        <v>0.2125632138766159</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4201508428460997</v>
+        <v>0.4106019600541431</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1857863433190235</v>
+        <v>0.1876863433190235</v>
       </c>
       <c r="C46">
-        <v>1.049669498552495</v>
+        <v>0.7442646064798684</v>
       </c>
       <c r="D46">
-        <v>9.116189498552496</v>
+        <v>8.994114606479869</v>
       </c>
       <c r="E46">
-        <v>8.033520000000001</v>
+        <v>8.216850000000001</v>
       </c>
       <c r="F46">
-        <v>8.066520000000001</v>
+        <v>8.24985</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5172,37 +5172,37 @@
         <v>0.781</v>
       </c>
       <c r="M46">
-        <v>1.902085416</v>
+        <v>1.94531463</v>
       </c>
       <c r="N46">
-        <v>-1.121085416</v>
+        <v>-1.16431463</v>
       </c>
       <c r="O46">
-        <v>-0.26906049984</v>
+        <v>-0.2794355112</v>
       </c>
       <c r="P46">
-        <v>-0.8520249161600001</v>
+        <v>-0.8848791188000003</v>
       </c>
       <c r="Q46">
-        <v>-0.7200249161600001</v>
+        <v>-0.7528791188000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1647473735952009</v>
+        <v>0.1669100531151136</v>
       </c>
       <c r="T46">
-        <v>2.005623601182314</v>
+        <v>2.042089484840174</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.0985444704129943</v>
+        <v>0.09635459329270556</v>
       </c>
       <c r="W46">
-        <v>0.2125632138766159</v>
+        <v>0.21307958690158</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4106019600541431</v>
+        <v>0.4014774720529397</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1876863433190235</v>
+        <v>0.1895863433190235</v>
       </c>
       <c r="C47">
-        <v>0.7442646064798684</v>
+        <v>0.4420859219813931</v>
       </c>
       <c r="D47">
-        <v>8.994114606479869</v>
+        <v>8.875265921981395</v>
       </c>
       <c r="E47">
-        <v>8.216850000000001</v>
+        <v>8.400180000000002</v>
       </c>
       <c r="F47">
-        <v>8.24985</v>
+        <v>8.433180000000002</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5254,37 +5254,37 @@
         <v>0.781</v>
       </c>
       <c r="M47">
-        <v>1.94531463</v>
+        <v>1.988543844000001</v>
       </c>
       <c r="N47">
-        <v>-1.16431463</v>
+        <v>-1.207543844</v>
       </c>
       <c r="O47">
-        <v>-0.2794355112</v>
+        <v>-0.2898105225600001</v>
       </c>
       <c r="P47">
-        <v>-0.8848791188000003</v>
+        <v>-0.9177333214400003</v>
       </c>
       <c r="Q47">
-        <v>-0.7528791188000002</v>
+        <v>-0.7857333214400003</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1669100531151136</v>
+        <v>0.1691528318765046</v>
       </c>
       <c r="T47">
-        <v>2.042089484840174</v>
+        <v>2.079905956781659</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09635459329270556</v>
+        <v>0.09425992822112497</v>
       </c>
       <c r="W47">
-        <v>0.21307958690158</v>
+        <v>0.2135735089254588</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4014774720529397</v>
+        <v>0.3927497009213542</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1895863433190235</v>
+        <v>0.1914863433190235</v>
       </c>
       <c r="C48">
-        <v>0.4420859219813931</v>
+        <v>0.1430072192025875</v>
       </c>
       <c r="D48">
-        <v>8.875265921981395</v>
+        <v>8.759517219202589</v>
       </c>
       <c r="E48">
-        <v>8.400180000000002</v>
+        <v>8.583510000000002</v>
       </c>
       <c r="F48">
-        <v>8.433180000000002</v>
+        <v>8.616510000000002</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5336,37 +5336,37 @@
         <v>0.781</v>
       </c>
       <c r="M48">
-        <v>1.988543844000001</v>
+        <v>2.031773058000001</v>
       </c>
       <c r="N48">
-        <v>-1.207543844</v>
+        <v>-1.250773058</v>
       </c>
       <c r="O48">
-        <v>-0.2898105225600001</v>
+        <v>-0.3001855339200001</v>
       </c>
       <c r="P48">
-        <v>-0.9177333214400003</v>
+        <v>-0.9505875240800004</v>
       </c>
       <c r="Q48">
-        <v>-0.7857333214400003</v>
+        <v>-0.8185875240800004</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1691528318765046</v>
+        <v>0.1714802437987028</v>
       </c>
       <c r="T48">
-        <v>2.079905956781659</v>
+        <v>2.119149465400181</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09425992822112497</v>
+        <v>0.09225439783344147</v>
       </c>
       <c r="W48">
-        <v>0.2135735089254588</v>
+        <v>0.2140464129908745</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3927497009213542</v>
+        <v>0.3843933243060061</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1914863433190235</v>
+        <v>0.1933863433190235</v>
       </c>
       <c r="C49">
-        <v>0.1430072192025875</v>
+        <v>-0.1530912276753789</v>
       </c>
       <c r="D49">
-        <v>8.759517219202589</v>
+        <v>8.646748772324623</v>
       </c>
       <c r="E49">
-        <v>8.583510000000002</v>
+        <v>8.766840000000002</v>
       </c>
       <c r="F49">
-        <v>8.616510000000002</v>
+        <v>8.799840000000001</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5418,37 +5418,37 @@
         <v>0.781</v>
       </c>
       <c r="M49">
-        <v>2.031773058000001</v>
+        <v>2.075002272</v>
       </c>
       <c r="N49">
-        <v>-1.250773058</v>
+        <v>-1.294002272</v>
       </c>
       <c r="O49">
-        <v>-0.3001855339200001</v>
+        <v>-0.31056054528</v>
       </c>
       <c r="P49">
-        <v>-0.9505875240800004</v>
+        <v>-0.9834417267200002</v>
       </c>
       <c r="Q49">
-        <v>-0.8185875240800004</v>
+        <v>-0.8514417267200002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1714802437987028</v>
+        <v>0.1738971715640625</v>
       </c>
       <c r="T49">
-        <v>2.119149465400181</v>
+        <v>2.1599023397348</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.09225439783344147</v>
+        <v>0.09033243121191145</v>
       </c>
       <c r="W49">
-        <v>0.2140464129908745</v>
+        <v>0.2144996127202313</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3843933243060061</v>
+        <v>0.3763851300496311</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1933863433190235</v>
+        <v>0.1952863433190235</v>
       </c>
       <c r="C50">
-        <v>-0.1530912276753789</v>
+        <v>-0.4463230575191623</v>
       </c>
       <c r="D50">
-        <v>8.646748772324623</v>
+        <v>8.536846942480839</v>
       </c>
       <c r="E50">
-        <v>8.766840000000002</v>
+        <v>8.950170000000002</v>
       </c>
       <c r="F50">
-        <v>8.799840000000001</v>
+        <v>8.983170000000001</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5500,37 +5500,37 @@
         <v>0.781</v>
       </c>
       <c r="M50">
-        <v>2.075002272</v>
+        <v>2.118231486</v>
       </c>
       <c r="N50">
-        <v>-1.294002272</v>
+        <v>-1.337231486</v>
       </c>
       <c r="O50">
-        <v>-0.31056054528</v>
+        <v>-0.3209355566400001</v>
       </c>
       <c r="P50">
-        <v>-0.9834417267200002</v>
+        <v>-1.01629592936</v>
       </c>
       <c r="Q50">
-        <v>-0.8514417267200002</v>
+        <v>-0.8842959293600002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1738971715640625</v>
+        <v>0.1764088808104166</v>
       </c>
       <c r="T50">
-        <v>2.1599023397348</v>
+        <v>2.202253366004109</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.09033243121191145</v>
+        <v>0.08848891220758673</v>
       </c>
       <c r="W50">
-        <v>0.2144996127202313</v>
+        <v>0.2149343145014511</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3763851300496311</v>
+        <v>0.3687038008649447</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1952863433190235</v>
+        <v>0.1971863433190235</v>
       </c>
       <c r="C51">
-        <v>-0.4463230575191623</v>
+        <v>-0.7367962042198695</v>
       </c>
       <c r="D51">
-        <v>8.536846942480839</v>
+        <v>8.429703795780132</v>
       </c>
       <c r="E51">
-        <v>8.950170000000002</v>
+        <v>9.133500000000002</v>
       </c>
       <c r="F51">
-        <v>8.983170000000001</v>
+        <v>9.166500000000001</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5582,37 +5582,37 @@
         <v>0.781</v>
       </c>
       <c r="M51">
-        <v>2.118231486</v>
+        <v>2.1614607</v>
       </c>
       <c r="N51">
-        <v>-1.337231486</v>
+        <v>-1.3804607</v>
       </c>
       <c r="O51">
-        <v>-0.3209355566400001</v>
+        <v>-0.331310568</v>
       </c>
       <c r="P51">
-        <v>-1.01629592936</v>
+        <v>-1.049150132</v>
       </c>
       <c r="Q51">
-        <v>-0.8842959293600002</v>
+        <v>-0.9171501320000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1764088808104166</v>
+        <v>0.179021058426625</v>
       </c>
       <c r="T51">
-        <v>2.202253366004109</v>
+        <v>2.246298433324192</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08848891220758673</v>
+        <v>0.086719133963435</v>
       </c>
       <c r="W51">
-        <v>0.2149343145014511</v>
+        <v>0.215351628211422</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3687038008649447</v>
+        <v>0.3613297248476459</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1971863433190235</v>
+        <v>0.1990863433190235</v>
       </c>
       <c r="C52">
-        <v>-0.7367962042198695</v>
+        <v>-1.024613250261853</v>
       </c>
       <c r="D52">
-        <v>8.429703795780132</v>
+        <v>8.325216749738148</v>
       </c>
       <c r="E52">
-        <v>9.133500000000002</v>
+        <v>9.316830000000001</v>
       </c>
       <c r="F52">
-        <v>9.166500000000001</v>
+        <v>9.349830000000001</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5664,37 +5664,37 @@
         <v>0.781</v>
       </c>
       <c r="M52">
-        <v>2.1614607</v>
+        <v>2.204689914</v>
       </c>
       <c r="N52">
-        <v>-1.3804607</v>
+        <v>-1.423689914</v>
       </c>
       <c r="O52">
-        <v>-0.331310568</v>
+        <v>-0.34168557936</v>
       </c>
       <c r="P52">
-        <v>-1.049150132</v>
+        <v>-1.08200433464</v>
       </c>
       <c r="Q52">
-        <v>-0.9171501320000001</v>
+        <v>-0.9500043346400001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.179021058426625</v>
+        <v>0.1817398555373724</v>
       </c>
       <c r="T52">
-        <v>2.246298433324192</v>
+        <v>2.292141258494073</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.086719133963435</v>
+        <v>0.08501875878768136</v>
       </c>
       <c r="W52">
-        <v>0.215351628211422</v>
+        <v>0.2157525766778647</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3613297248476459</v>
+        <v>0.3542448282820058</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1990863433190235</v>
+        <v>0.2009863433190235</v>
       </c>
       <c r="C53">
-        <v>-1.024613250261853</v>
+        <v>-1.309871754318324</v>
       </c>
       <c r="D53">
-        <v>8.325216749738148</v>
+        <v>8.223288245681676</v>
       </c>
       <c r="E53">
-        <v>9.316830000000001</v>
+        <v>9.500160000000001</v>
       </c>
       <c r="F53">
-        <v>9.349830000000001</v>
+        <v>9.533160000000001</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5746,37 +5746,37 @@
         <v>0.781</v>
       </c>
       <c r="M53">
-        <v>2.204689914</v>
+        <v>2.247919128</v>
       </c>
       <c r="N53">
-        <v>-1.423689914</v>
+        <v>-1.466919128</v>
       </c>
       <c r="O53">
-        <v>-0.34168557936</v>
+        <v>-0.3520605907200001</v>
       </c>
       <c r="P53">
-        <v>-1.08200433464</v>
+        <v>-1.11485853728</v>
       </c>
       <c r="Q53">
-        <v>-0.9500043346400001</v>
+        <v>-0.9828585372800002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1817398555373724</v>
+        <v>0.1845719358610677</v>
       </c>
       <c r="T53">
-        <v>2.292141258494073</v>
+        <v>2.339894201379366</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08501875878768136</v>
+        <v>0.08338378265714902</v>
       </c>
       <c r="W53">
-        <v>0.2157525766778647</v>
+        <v>0.2161381040494443</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3542448282820058</v>
+        <v>0.347432427738121</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2009863433190235</v>
+        <v>0.2028863433190235</v>
       </c>
       <c r="C54">
-        <v>-1.309871754318324</v>
+        <v>-1.592664555072844</v>
       </c>
       <c r="D54">
-        <v>8.223288245681676</v>
+        <v>8.123825444927158</v>
       </c>
       <c r="E54">
-        <v>9.500160000000001</v>
+        <v>9.683490000000003</v>
       </c>
       <c r="F54">
-        <v>9.533160000000001</v>
+        <v>9.716490000000002</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5828,37 +5828,37 @@
         <v>0.781</v>
       </c>
       <c r="M54">
-        <v>2.247919128</v>
+        <v>2.291148342000001</v>
       </c>
       <c r="N54">
-        <v>-1.466919128</v>
+        <v>-1.510148342</v>
       </c>
       <c r="O54">
-        <v>-0.3520605907200001</v>
+        <v>-0.3624356020800001</v>
       </c>
       <c r="P54">
-        <v>-1.11485853728</v>
+        <v>-1.14771273992</v>
       </c>
       <c r="Q54">
-        <v>-0.9828585372800002</v>
+        <v>-1.01571273992</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1845719358610677</v>
+        <v>0.1875245302410904</v>
       </c>
       <c r="T54">
-        <v>2.339894201379366</v>
+        <v>2.389679184387438</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08338378265714902</v>
+        <v>0.0818105037390896</v>
       </c>
       <c r="W54">
-        <v>0.2161381040494443</v>
+        <v>0.2165090832183227</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.347432427738121</v>
+        <v>0.3408770989128734</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2028863433190235</v>
+        <v>0.2047863433190235</v>
       </c>
       <c r="C55">
-        <v>-1.592664555072844</v>
+        <v>-1.873080053255469</v>
       </c>
       <c r="D55">
-        <v>8.123825444927158</v>
+        <v>8.026739946744533</v>
       </c>
       <c r="E55">
-        <v>9.683490000000003</v>
+        <v>9.866820000000002</v>
       </c>
       <c r="F55">
-        <v>9.716490000000002</v>
+        <v>9.899820000000002</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5910,37 +5910,37 @@
         <v>0.781</v>
       </c>
       <c r="M55">
-        <v>2.291148342000001</v>
+        <v>2.334377556000001</v>
       </c>
       <c r="N55">
-        <v>-1.510148342</v>
+        <v>-1.553377556</v>
       </c>
       <c r="O55">
-        <v>-0.3624356020800001</v>
+        <v>-0.3728106134400001</v>
       </c>
       <c r="P55">
-        <v>-1.14771273992</v>
+        <v>-1.18056694256</v>
       </c>
       <c r="Q55">
-        <v>-1.01571273992</v>
+        <v>-1.04856694256</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1875245302410904</v>
+        <v>0.1906054982898097</v>
       </c>
       <c r="T55">
-        <v>2.389679184387438</v>
+        <v>2.441628731874121</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0818105037390896</v>
+        <v>0.08029549441058795</v>
       </c>
       <c r="W55">
-        <v>0.2165090832183227</v>
+        <v>0.2168663224179834</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3408770989128734</v>
+        <v>0.3345645600441165</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2047863433190235</v>
+        <v>0.2066863433190235</v>
       </c>
       <c r="C56">
-        <v>-1.873080053255469</v>
+        <v>-2.151202473694623</v>
       </c>
       <c r="D56">
-        <v>8.026739946744533</v>
+        <v>7.931947526305379</v>
       </c>
       <c r="E56">
-        <v>9.866820000000002</v>
+        <v>10.05015</v>
       </c>
       <c r="F56">
-        <v>9.899820000000002</v>
+        <v>10.08315</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5992,37 +5992,37 @@
         <v>0.781</v>
       </c>
       <c r="M56">
-        <v>2.334377556000001</v>
+        <v>2.37760677</v>
       </c>
       <c r="N56">
-        <v>-1.553377556</v>
+        <v>-1.59660677</v>
       </c>
       <c r="O56">
-        <v>-0.3728106134400001</v>
+        <v>-0.3831856248</v>
       </c>
       <c r="P56">
-        <v>-1.18056694256</v>
+        <v>-1.2134211452</v>
       </c>
       <c r="Q56">
-        <v>-1.04856694256</v>
+        <v>-1.0814211452</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1906054982898097</v>
+        <v>0.1938233982518055</v>
       </c>
       <c r="T56">
-        <v>2.441628731874121</v>
+        <v>2.495887148137991</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.08029549441058795</v>
+        <v>0.07883557633039544</v>
       </c>
       <c r="W56">
-        <v>0.2168663224179834</v>
+        <v>0.2172105711012928</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3345645600441165</v>
+        <v>0.3284815680433144</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2066863433190235</v>
+        <v>0.2085863433190235</v>
       </c>
       <c r="C57">
-        <v>-2.151202473694623</v>
+        <v>-2.427112109017255</v>
       </c>
       <c r="D57">
-        <v>7.931947526305379</v>
+        <v>7.839367890982746</v>
       </c>
       <c r="E57">
-        <v>10.05015</v>
+        <v>10.23348</v>
       </c>
       <c r="F57">
-        <v>10.08315</v>
+        <v>10.26648</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -6074,37 +6074,37 @@
         <v>0.781</v>
       </c>
       <c r="M57">
-        <v>2.37760677</v>
+        <v>2.420835984</v>
       </c>
       <c r="N57">
-        <v>-1.59660677</v>
+        <v>-1.639835984</v>
       </c>
       <c r="O57">
-        <v>-0.3831856248</v>
+        <v>-0.39356063616</v>
       </c>
       <c r="P57">
-        <v>-1.2134211452</v>
+        <v>-1.24627534784</v>
       </c>
       <c r="Q57">
-        <v>-1.0814211452</v>
+        <v>-1.11427534784</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1938233982518055</v>
+        <v>0.197187566393892</v>
       </c>
       <c r="T57">
-        <v>2.495887148137991</v>
+        <v>2.552611856050218</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07883557633039544</v>
+        <v>0.07742779818163839</v>
       </c>
       <c r="W57">
-        <v>0.2172105711012928</v>
+        <v>0.2175425251887697</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3284815680433144</v>
+        <v>0.3226158257568267</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2085863433190235</v>
+        <v>0.2104863433190235</v>
       </c>
       <c r="C58">
-        <v>-2.427112109017255</v>
+        <v>-2.700885546479545</v>
       </c>
       <c r="D58">
-        <v>7.839367890982746</v>
+        <v>7.748924453520458</v>
       </c>
       <c r="E58">
-        <v>10.23348</v>
+        <v>10.41681</v>
       </c>
       <c r="F58">
-        <v>10.26648</v>
+        <v>10.44981</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6156,37 +6156,37 @@
         <v>0.781</v>
       </c>
       <c r="M58">
-        <v>2.420835984</v>
+        <v>2.464065198000001</v>
       </c>
       <c r="N58">
-        <v>-1.639835984</v>
+        <v>-1.683065198000001</v>
       </c>
       <c r="O58">
-        <v>-0.39356063616</v>
+        <v>-0.4039356475200002</v>
       </c>
       <c r="P58">
-        <v>-1.24627534784</v>
+        <v>-1.279129550480001</v>
       </c>
       <c r="Q58">
-        <v>-1.11427534784</v>
+        <v>-1.147129550480001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.197187566393892</v>
+        <v>0.2007082074728198</v>
       </c>
       <c r="T58">
-        <v>2.552611856050218</v>
+        <v>2.611974922469991</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07742779818163839</v>
+        <v>0.0760694157573991</v>
       </c>
       <c r="W58">
-        <v>0.2175425251887697</v>
+        <v>0.2178628317644053</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3226158257568267</v>
+        <v>0.316955898989163</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2104863433190235</v>
+        <v>0.2123863433190235</v>
       </c>
       <c r="C59">
-        <v>-2.700885546479545</v>
+        <v>-2.972595879274853</v>
       </c>
       <c r="D59">
-        <v>7.748924453520458</v>
+        <v>7.66054412072515</v>
       </c>
       <c r="E59">
-        <v>10.41681</v>
+        <v>10.60014</v>
       </c>
       <c r="F59">
-        <v>10.44981</v>
+        <v>10.63314</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6238,37 +6238,37 @@
         <v>0.781</v>
       </c>
       <c r="M59">
-        <v>2.464065198000001</v>
+        <v>2.507294412000001</v>
       </c>
       <c r="N59">
-        <v>-1.683065198000001</v>
+        <v>-1.726294412000001</v>
       </c>
       <c r="O59">
-        <v>-0.4039356475200002</v>
+        <v>-0.4143106588800001</v>
       </c>
       <c r="P59">
-        <v>-1.279129550480001</v>
+        <v>-1.31198375312</v>
       </c>
       <c r="Q59">
-        <v>-1.147129550480001</v>
+        <v>-1.179983753120001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2007082074728198</v>
+        <v>0.2043964981269345</v>
       </c>
       <c r="T59">
-        <v>2.611974922469991</v>
+        <v>2.674164801576419</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0760694157573991</v>
+        <v>0.07475787410640947</v>
       </c>
       <c r="W59">
-        <v>0.2178628317644053</v>
+        <v>0.2181720932857087</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.316955898989163</v>
+        <v>0.3114911421100395</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2123863433190235</v>
+        <v>0.2142863433190235</v>
       </c>
       <c r="C60">
-        <v>-2.972595879274851</v>
+        <v>-3.242312903544337</v>
       </c>
       <c r="D60">
-        <v>7.66054412072515</v>
+        <v>7.574157096455663</v>
       </c>
       <c r="E60">
-        <v>10.60014</v>
+        <v>10.78347</v>
       </c>
       <c r="F60">
-        <v>10.63314</v>
+        <v>10.81647</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6320,37 +6320,37 @@
         <v>0.781</v>
       </c>
       <c r="M60">
-        <v>2.507294412</v>
+        <v>2.550523626</v>
       </c>
       <c r="N60">
-        <v>-1.726294412</v>
+        <v>-1.769523626</v>
       </c>
       <c r="O60">
-        <v>-0.41431065888</v>
+        <v>-0.42468567024</v>
       </c>
       <c r="P60">
-        <v>-1.31198375312</v>
+        <v>-1.34483795576</v>
       </c>
       <c r="Q60">
-        <v>-1.17998375312</v>
+        <v>-1.21283795576</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2043964981269345</v>
+        <v>0.2082647053983231</v>
       </c>
       <c r="T60">
-        <v>2.674164801576419</v>
+        <v>2.739388333322184</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07475787410640948</v>
+        <v>0.07349079149443644</v>
       </c>
       <c r="W60">
-        <v>0.2181720932857087</v>
+        <v>0.2184708713656119</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3114911421100396</v>
+        <v>0.3062116312268185</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2142863433190235</v>
+        <v>0.2161863433190235</v>
       </c>
       <c r="C61">
-        <v>-3.242312903544337</v>
+        <v>-3.510103302206225</v>
       </c>
       <c r="D61">
-        <v>7.574157096455663</v>
+        <v>7.489696697793775</v>
       </c>
       <c r="E61">
-        <v>10.78347</v>
+        <v>10.9668</v>
       </c>
       <c r="F61">
-        <v>10.81647</v>
+        <v>10.9998</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6402,37 +6402,37 @@
         <v>0.781</v>
       </c>
       <c r="M61">
-        <v>2.550523626</v>
+        <v>2.59375284</v>
       </c>
       <c r="N61">
-        <v>-1.769523626</v>
+        <v>-1.81275284</v>
       </c>
       <c r="O61">
-        <v>-0.42468567024</v>
+        <v>-0.4350606815999999</v>
       </c>
       <c r="P61">
-        <v>-1.34483795576</v>
+        <v>-1.3776921584</v>
       </c>
       <c r="Q61">
-        <v>-1.21283795576</v>
+        <v>-1.2456921584</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2082647053983231</v>
+        <v>0.2123263230332812</v>
       </c>
       <c r="T61">
-        <v>2.739388333322184</v>
+        <v>2.807873041655239</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07349079149443644</v>
+        <v>0.07226594496952918</v>
       </c>
       <c r="W61">
-        <v>0.2184708713656119</v>
+        <v>0.218759690176185</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3062116312268185</v>
+        <v>0.3011081040397049</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2161863433190235</v>
+        <v>0.2180863433190235</v>
       </c>
       <c r="C62">
-        <v>-3.510103302206225</v>
+        <v>-3.77603081662127</v>
       </c>
       <c r="D62">
-        <v>7.489696697793775</v>
+        <v>7.407099183378731</v>
       </c>
       <c r="E62">
-        <v>10.9668</v>
+        <v>11.15013</v>
       </c>
       <c r="F62">
-        <v>10.9998</v>
+        <v>11.18313</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6484,37 +6484,37 @@
         <v>0.781</v>
       </c>
       <c r="M62">
-        <v>2.59375284</v>
+        <v>2.636982054</v>
       </c>
       <c r="N62">
-        <v>-1.81275284</v>
+        <v>-1.855982054</v>
       </c>
       <c r="O62">
-        <v>-0.4350606815999999</v>
+        <v>-0.44543569296</v>
       </c>
       <c r="P62">
-        <v>-1.3776921584</v>
+        <v>-1.41054636104</v>
       </c>
       <c r="Q62">
-        <v>-1.2456921584</v>
+        <v>-1.27854636104</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2123263230332812</v>
+        <v>0.2165962287520833</v>
       </c>
       <c r="T62">
-        <v>2.807873041655239</v>
+        <v>2.879869786313066</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07226594496952918</v>
+        <v>0.07108125734707788</v>
       </c>
       <c r="W62">
-        <v>0.218759690176185</v>
+        <v>0.2190390395175591</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3011081040397049</v>
+        <v>0.2961719056128245</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2180863433190235</v>
+        <v>0.2199863433190235</v>
       </c>
       <c r="C63">
-        <v>-3.77603081662127</v>
+        <v>-4.040156407023233</v>
       </c>
       <c r="D63">
-        <v>7.407099183378731</v>
+        <v>7.326303592976768</v>
       </c>
       <c r="E63">
-        <v>11.15013</v>
+        <v>11.33346</v>
       </c>
       <c r="F63">
-        <v>11.18313</v>
+        <v>11.36646</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6566,37 +6566,37 @@
         <v>0.781</v>
       </c>
       <c r="M63">
-        <v>2.636982054</v>
+        <v>2.680211268</v>
       </c>
       <c r="N63">
-        <v>-1.855982054</v>
+        <v>-1.899211268</v>
       </c>
       <c r="O63">
-        <v>-0.44543569296</v>
+        <v>-0.45581070432</v>
       </c>
       <c r="P63">
-        <v>-1.41054636104</v>
+        <v>-1.44340056368</v>
       </c>
       <c r="Q63">
-        <v>-1.27854636104</v>
+        <v>-1.31140056368</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2165962287520833</v>
+        <v>0.2210908663508223</v>
       </c>
       <c r="T63">
-        <v>2.879869786313066</v>
+        <v>2.955655833321305</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07108125734707788</v>
+        <v>0.06993478545438306</v>
       </c>
       <c r="W63">
-        <v>0.2190390395175591</v>
+        <v>0.2193093775898565</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2961719056128245</v>
+        <v>0.2913949393932628</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2199863433190235</v>
+        <v>0.2218863433190235</v>
       </c>
       <c r="C64">
-        <v>-4.040156407023233</v>
+        <v>-4.302538402562925</v>
       </c>
       <c r="D64">
-        <v>7.326303592976768</v>
+        <v>7.247251597437076</v>
       </c>
       <c r="E64">
-        <v>11.33346</v>
+        <v>11.51679</v>
       </c>
       <c r="F64">
-        <v>11.36646</v>
+        <v>11.54979</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6648,37 +6648,37 @@
         <v>0.781</v>
       </c>
       <c r="M64">
-        <v>2.680211268</v>
+        <v>2.723440482</v>
       </c>
       <c r="N64">
-        <v>-1.899211268</v>
+        <v>-1.942440482</v>
       </c>
       <c r="O64">
-        <v>-0.45581070432</v>
+        <v>-0.4661857156800001</v>
       </c>
       <c r="P64">
-        <v>-1.44340056368</v>
+        <v>-1.47625476632</v>
       </c>
       <c r="Q64">
-        <v>-1.31140056368</v>
+        <v>-1.34425476632</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2210908663508223</v>
+        <v>0.225828457333277</v>
       </c>
       <c r="T64">
-        <v>2.955655833321305</v>
+        <v>3.03553842341107</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06993478545438306</v>
+        <v>0.06882470949478968</v>
       </c>
       <c r="W64">
-        <v>0.2193093775898565</v>
+        <v>0.2195711335011286</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2913949393932628</v>
+        <v>0.286769622894957</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2218863433190235</v>
+        <v>0.2237863433190235</v>
       </c>
       <c r="C65">
-        <v>-4.302538402562925</v>
+        <v>-4.563232641741935</v>
       </c>
       <c r="D65">
-        <v>7.247251597437076</v>
+        <v>7.169887358258066</v>
       </c>
       <c r="E65">
-        <v>11.51679</v>
+        <v>11.70012</v>
       </c>
       <c r="F65">
-        <v>11.54979</v>
+        <v>11.73312</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6730,37 +6730,37 @@
         <v>0.781</v>
       </c>
       <c r="M65">
-        <v>2.723440482</v>
+        <v>2.766669696000001</v>
       </c>
       <c r="N65">
-        <v>-1.942440482</v>
+        <v>-1.985669696</v>
       </c>
       <c r="O65">
-        <v>-0.4661857156800001</v>
+        <v>-0.4765607270400001</v>
       </c>
       <c r="P65">
-        <v>-1.47625476632</v>
+        <v>-1.50910896896</v>
       </c>
       <c r="Q65">
-        <v>-1.34425476632</v>
+        <v>-1.37710896896</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.225828457333277</v>
+        <v>0.2308292478147569</v>
       </c>
       <c r="T65">
-        <v>3.03553842341107</v>
+        <v>3.119858935172489</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06882470949478968</v>
+        <v>0.06774932340893358</v>
       </c>
       <c r="W65">
-        <v>0.2195711335011286</v>
+        <v>0.2198247095401735</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.286769622894957</v>
+        <v>0.2822888475372233</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2237863433190235</v>
+        <v>0.2256863433190235</v>
       </c>
       <c r="C66">
-        <v>-4.563232641741935</v>
+        <v>-4.822292603946628</v>
       </c>
       <c r="D66">
-        <v>7.169887358258066</v>
+        <v>7.094157396053373</v>
       </c>
       <c r="E66">
-        <v>11.70012</v>
+        <v>11.88345</v>
       </c>
       <c r="F66">
-        <v>11.73312</v>
+        <v>11.91645</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6812,37 +6812,37 @@
         <v>0.781</v>
       </c>
       <c r="M66">
-        <v>2.766669696000001</v>
+        <v>2.80989891</v>
       </c>
       <c r="N66">
-        <v>-1.985669696</v>
+        <v>-2.02889891</v>
       </c>
       <c r="O66">
-        <v>-0.4765607270400001</v>
+        <v>-0.4869357384</v>
       </c>
       <c r="P66">
-        <v>-1.50910896896</v>
+        <v>-1.5419631716</v>
       </c>
       <c r="Q66">
-        <v>-1.37710896896</v>
+        <v>-1.4099631716</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2308292478147569</v>
+        <v>0.2361157977523214</v>
       </c>
       <c r="T66">
-        <v>3.119858935172489</v>
+        <v>3.208997761891703</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06774932340893358</v>
+        <v>0.06670702612571923</v>
       </c>
       <c r="W66">
-        <v>0.2198247095401735</v>
+        <v>0.2200704832395554</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2822888475372233</v>
+        <v>0.2779459421904968</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2256863433190235</v>
+        <v>0.2275863433190235</v>
       </c>
       <c r="C67">
-        <v>-4.822292603946628</v>
+        <v>-5.079769532733502</v>
       </c>
       <c r="D67">
-        <v>7.094157396053373</v>
+        <v>7.020010467266501</v>
       </c>
       <c r="E67">
-        <v>11.88345</v>
+        <v>12.06678</v>
       </c>
       <c r="F67">
-        <v>11.91645</v>
+        <v>12.09978</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6894,37 +6894,37 @@
         <v>0.781</v>
       </c>
       <c r="M67">
-        <v>2.80989891</v>
+        <v>2.853128124000001</v>
       </c>
       <c r="N67">
-        <v>-2.02889891</v>
+        <v>-2.072128124000001</v>
       </c>
       <c r="O67">
-        <v>-0.4869357384</v>
+        <v>-0.4973107497600002</v>
       </c>
       <c r="P67">
-        <v>-1.5419631716</v>
+        <v>-1.57481737424</v>
       </c>
       <c r="Q67">
-        <v>-1.4099631716</v>
+        <v>-1.442817374240001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2361157977523214</v>
+        <v>0.241713321215625</v>
       </c>
       <c r="T67">
-        <v>3.208997761891703</v>
+        <v>3.303380049006165</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06670702612571923</v>
+        <v>0.06569631360866286</v>
       </c>
       <c r="W67">
-        <v>0.2200704832395554</v>
+        <v>0.2203088092510773</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2779459421904968</v>
+        <v>0.2737346400360953</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2275863433190235</v>
+        <v>0.2294863433190235</v>
       </c>
       <c r="C68">
-        <v>-5.079769532733502</v>
+        <v>-5.335712551463158</v>
       </c>
       <c r="D68">
-        <v>7.020010467266501</v>
+        <v>6.947397448536845</v>
       </c>
       <c r="E68">
-        <v>12.06678</v>
+        <v>12.25011</v>
       </c>
       <c r="F68">
-        <v>12.09978</v>
+        <v>12.28311</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6976,37 +6976,37 @@
         <v>0.781</v>
       </c>
       <c r="M68">
-        <v>2.853128124000001</v>
+        <v>2.896357338000001</v>
       </c>
       <c r="N68">
-        <v>-2.072128124000001</v>
+        <v>-2.115357338</v>
       </c>
       <c r="O68">
-        <v>-0.4973107497600002</v>
+        <v>-0.5076857611200001</v>
       </c>
       <c r="P68">
-        <v>-1.57481737424</v>
+        <v>-1.60767157688</v>
       </c>
       <c r="Q68">
-        <v>-1.442817374240001</v>
+        <v>-1.47567157688</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.241713321215625</v>
+        <v>0.2476500885251894</v>
       </c>
       <c r="T68">
-        <v>3.303380049006165</v>
+        <v>3.403482474733624</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06569631360866286</v>
+        <v>0.06471577161450372</v>
       </c>
       <c r="W68">
-        <v>0.2203088092510773</v>
+        <v>0.2205400210533</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2737346400360953</v>
+        <v>0.2696490483937656</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2294863433190235</v>
+        <v>0.2313863433190235</v>
       </c>
       <c r="C69">
-        <v>-5.335712551463158</v>
+        <v>-5.590168771831265</v>
       </c>
       <c r="D69">
-        <v>6.947397448536845</v>
+        <v>6.876271228168737</v>
       </c>
       <c r="E69">
-        <v>12.25011</v>
+        <v>12.43344</v>
       </c>
       <c r="F69">
-        <v>12.28311</v>
+        <v>12.46644</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -7058,37 +7058,37 @@
         <v>0.781</v>
       </c>
       <c r="M69">
-        <v>2.896357338000001</v>
+        <v>2.939586552000001</v>
       </c>
       <c r="N69">
-        <v>-2.115357338</v>
+        <v>-2.158586552</v>
       </c>
       <c r="O69">
-        <v>-0.5076857611200001</v>
+        <v>-0.5180607724800002</v>
       </c>
       <c r="P69">
-        <v>-1.60767157688</v>
+        <v>-1.64052577952</v>
       </c>
       <c r="Q69">
-        <v>-1.47567157688</v>
+        <v>-1.50852577952</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2476500885251894</v>
+        <v>0.2539579037916015</v>
       </c>
       <c r="T69">
-        <v>3.403482474733624</v>
+        <v>3.50984130206905</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06471577161450372</v>
+        <v>0.06376406909076102</v>
       </c>
       <c r="W69">
-        <v>0.2205400210533</v>
+        <v>0.2207644325083986</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2696490483937656</v>
+        <v>0.2656836212115042</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2313863433190235</v>
+        <v>0.2332863433190235</v>
       </c>
       <c r="C70">
-        <v>-5.590168771831265</v>
+        <v>-5.843183395800326</v>
       </c>
       <c r="D70">
-        <v>6.876271228168737</v>
+        <v>6.806586604199676</v>
       </c>
       <c r="E70">
-        <v>12.43344</v>
+        <v>12.61677</v>
       </c>
       <c r="F70">
-        <v>12.46644</v>
+        <v>12.64977</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7140,37 +7140,37 @@
         <v>0.781</v>
       </c>
       <c r="M70">
-        <v>2.939586552000001</v>
+        <v>2.982815766000001</v>
       </c>
       <c r="N70">
-        <v>-2.158586552</v>
+        <v>-2.201815766000001</v>
       </c>
       <c r="O70">
-        <v>-0.5180607724800002</v>
+        <v>-0.5284357838400001</v>
       </c>
       <c r="P70">
-        <v>-1.64052577952</v>
+        <v>-1.673379982160001</v>
       </c>
       <c r="Q70">
-        <v>-1.50852577952</v>
+        <v>-1.54137998216</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2539579037916015</v>
+        <v>0.2606726748816532</v>
       </c>
       <c r="T70">
-        <v>3.50984130206905</v>
+        <v>3.623061989232568</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06376406909076102</v>
+        <v>0.06283995214741665</v>
       </c>
       <c r="W70">
-        <v>0.2207644325083986</v>
+        <v>0.2209823392836392</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2656836212115042</v>
+        <v>0.2618331339475695</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2332863433190235</v>
+        <v>0.2351863433190235</v>
       </c>
       <c r="C71">
-        <v>-5.843183395800326</v>
+        <v>-6.094799811395744</v>
       </c>
       <c r="D71">
-        <v>6.806586604199676</v>
+        <v>6.738300188604257</v>
       </c>
       <c r="E71">
-        <v>12.61677</v>
+        <v>12.8001</v>
       </c>
       <c r="F71">
-        <v>12.64977</v>
+        <v>12.8331</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7222,37 +7222,37 @@
         <v>0.781</v>
       </c>
       <c r="M71">
-        <v>2.982815766000001</v>
+        <v>3.02604498</v>
       </c>
       <c r="N71">
-        <v>-2.201815766000001</v>
+        <v>-2.24504498</v>
       </c>
       <c r="O71">
-        <v>-0.5284357838400001</v>
+        <v>-0.5388107952000001</v>
       </c>
       <c r="P71">
-        <v>-1.673379982160001</v>
+        <v>-1.7062341848</v>
       </c>
       <c r="Q71">
-        <v>-1.54137998216</v>
+        <v>-1.5742341848</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2606726748816532</v>
+        <v>0.2678350973777083</v>
       </c>
       <c r="T71">
-        <v>3.623061989232568</v>
+        <v>3.743830722206987</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06283995214741665</v>
+        <v>0.06194223854531072</v>
       </c>
       <c r="W71">
-        <v>0.2209823392836392</v>
+        <v>0.2211940201510157</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2618331339475695</v>
+        <v>0.2580926606054613</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2351863433190235</v>
+        <v>0.2370863433190235</v>
       </c>
       <c r="C72">
-        <v>-6.094799811395744</v>
+        <v>-6.345059682792764</v>
       </c>
       <c r="D72">
-        <v>6.738300188604257</v>
+        <v>6.67137031720724</v>
       </c>
       <c r="E72">
-        <v>12.8001</v>
+        <v>12.98343</v>
       </c>
       <c r="F72">
-        <v>12.8331</v>
+        <v>13.01643</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7304,37 +7304,37 @@
         <v>0.781</v>
       </c>
       <c r="M72">
-        <v>3.02604498</v>
+        <v>3.069274194000001</v>
       </c>
       <c r="N72">
-        <v>-2.24504498</v>
+        <v>-2.288274194000001</v>
       </c>
       <c r="O72">
-        <v>-0.5388107952000001</v>
+        <v>-0.5491858065600002</v>
       </c>
       <c r="P72">
-        <v>-1.7062341848</v>
+        <v>-1.739088387440001</v>
       </c>
       <c r="Q72">
-        <v>-1.5742341848</v>
+        <v>-1.607088387440001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2678350973777083</v>
+        <v>0.2754914800459052</v>
       </c>
       <c r="T72">
-        <v>3.743830722206987</v>
+        <v>3.872928333317573</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06194223854531072</v>
+        <v>0.06106981265030632</v>
       </c>
       <c r="W72">
-        <v>0.2211940201510157</v>
+        <v>0.2213997381770578</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2580926606054613</v>
+        <v>0.2544575527096097</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2370863433190235</v>
+        <v>0.2389863433190235</v>
       </c>
       <c r="C73">
-        <v>-6.345059682792762</v>
+        <v>-6.594003035087348</v>
       </c>
       <c r="D73">
-        <v>6.67137031720724</v>
+        <v>6.605756964912653</v>
       </c>
       <c r="E73">
-        <v>12.98343</v>
+        <v>13.16676</v>
       </c>
       <c r="F73">
-        <v>13.01643</v>
+        <v>13.19976</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7386,37 +7386,37 @@
         <v>0.781</v>
       </c>
       <c r="M73">
-        <v>3.069274194000001</v>
+        <v>3.112503408</v>
       </c>
       <c r="N73">
-        <v>-2.288274194</v>
+        <v>-2.331503408</v>
       </c>
       <c r="O73">
-        <v>-0.54918580656</v>
+        <v>-0.55956081792</v>
       </c>
       <c r="P73">
-        <v>-1.73908838744</v>
+        <v>-1.77194259008</v>
       </c>
       <c r="Q73">
-        <v>-1.60708838744</v>
+        <v>-1.63994259008</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2754914800459051</v>
+        <v>0.2836947471904017</v>
       </c>
       <c r="T73">
-        <v>3.872928333317572</v>
+        <v>4.011247202364628</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06106981265030634</v>
+        <v>0.06022162080794097</v>
       </c>
       <c r="W73">
-        <v>0.2213997381770578</v>
+        <v>0.2215997418134875</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2544575527096098</v>
+        <v>0.2509234200330874</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2389863433190235</v>
+        <v>0.2408863433190235</v>
       </c>
       <c r="C74">
-        <v>-6.594003035087348</v>
+        <v>-6.841668334113429</v>
       </c>
       <c r="D74">
-        <v>6.605756964912653</v>
+        <v>6.541421665886572</v>
       </c>
       <c r="E74">
-        <v>13.16676</v>
+        <v>13.35009</v>
       </c>
       <c r="F74">
-        <v>13.19976</v>
+        <v>13.38309</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7468,37 +7468,37 @@
         <v>0.781</v>
       </c>
       <c r="M74">
-        <v>3.112503408</v>
+        <v>3.155732622</v>
       </c>
       <c r="N74">
-        <v>-2.331503408</v>
+        <v>-2.374732622</v>
       </c>
       <c r="O74">
-        <v>-0.55956081792</v>
+        <v>-0.5699358292800001</v>
       </c>
       <c r="P74">
-        <v>-1.77194259008</v>
+        <v>-1.80479679272</v>
       </c>
       <c r="Q74">
-        <v>-1.63994259008</v>
+        <v>-1.67279679272</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2836947471904017</v>
+        <v>0.2925056637530092</v>
       </c>
       <c r="T74">
-        <v>4.011247202364628</v>
+        <v>4.159811913563318</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06022162080794097</v>
+        <v>0.05939666709824315</v>
       </c>
       <c r="W74">
-        <v>0.2215997418134875</v>
+        <v>0.2217942658982343</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2509234200330874</v>
+        <v>0.2474861129093465</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2408863433190235</v>
+        <v>0.2427863433190235</v>
       </c>
       <c r="C75">
-        <v>-6.841668334113429</v>
+        <v>-7.088092561640947</v>
       </c>
       <c r="D75">
-        <v>6.541421665886572</v>
+        <v>6.478327438359054</v>
       </c>
       <c r="E75">
-        <v>13.35009</v>
+        <v>13.53342</v>
       </c>
       <c r="F75">
-        <v>13.38309</v>
+        <v>13.56642</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7550,37 +7550,37 @@
         <v>0.781</v>
       </c>
       <c r="M75">
-        <v>3.155732622</v>
+        <v>3.198961836000001</v>
       </c>
       <c r="N75">
-        <v>-2.374732622</v>
+        <v>-2.417961836</v>
       </c>
       <c r="O75">
-        <v>-0.5699358292800001</v>
+        <v>-0.58031084064</v>
       </c>
       <c r="P75">
-        <v>-1.80479679272</v>
+        <v>-1.83765099536</v>
       </c>
       <c r="Q75">
-        <v>-1.67279679272</v>
+        <v>-1.70565099536</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2925056637530092</v>
+        <v>0.3019943431281249</v>
       </c>
       <c r="T75">
-        <v>4.159811913563318</v>
+        <v>4.319804679469599</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05939666709824315</v>
+        <v>0.05859400943475337</v>
       </c>
       <c r="W75">
-        <v>0.2217942658982343</v>
+        <v>0.2219835325752852</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2474861129093465</v>
+        <v>0.2441417059781391</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2427863433190235</v>
+        <v>0.2446863433190235</v>
       </c>
       <c r="C76">
-        <v>-7.088092561640947</v>
+        <v>-7.333311286263624</v>
       </c>
       <c r="D76">
-        <v>6.478327438359054</v>
+        <v>6.416438713736378</v>
       </c>
       <c r="E76">
-        <v>13.53342</v>
+        <v>13.71675</v>
       </c>
       <c r="F76">
-        <v>13.56642</v>
+        <v>13.74975</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7632,37 +7632,37 @@
         <v>0.781</v>
       </c>
       <c r="M76">
-        <v>3.198961836000001</v>
+        <v>3.242191050000001</v>
       </c>
       <c r="N76">
-        <v>-2.417961836</v>
+        <v>-2.46119105</v>
       </c>
       <c r="O76">
-        <v>-0.58031084064</v>
+        <v>-0.5906858520000001</v>
       </c>
       <c r="P76">
-        <v>-1.83765099536</v>
+        <v>-1.870505198</v>
       </c>
       <c r="Q76">
-        <v>-1.70565099536</v>
+        <v>-1.738505198</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3019943431281249</v>
+        <v>0.3122421168532499</v>
       </c>
       <c r="T76">
-        <v>4.319804679469599</v>
+        <v>4.492596866648383</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05859400943475337</v>
+        <v>0.05781275597562333</v>
       </c>
       <c r="W76">
-        <v>0.2219835325752852</v>
+        <v>0.222167752140948</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2441417059781391</v>
+        <v>0.2408864832317639</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2446863433190235</v>
+        <v>0.2465863433190235</v>
       </c>
       <c r="C77">
-        <v>-7.333311286263624</v>
+        <v>-7.57735873026194</v>
       </c>
       <c r="D77">
-        <v>6.416438713736378</v>
+        <v>6.355721269738062</v>
       </c>
       <c r="E77">
-        <v>13.71675</v>
+        <v>13.90008</v>
       </c>
       <c r="F77">
-        <v>13.74975</v>
+        <v>13.93308</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7714,37 +7714,37 @@
         <v>0.781</v>
       </c>
       <c r="M77">
-        <v>3.242191050000001</v>
+        <v>3.285420264000001</v>
       </c>
       <c r="N77">
-        <v>-2.46119105</v>
+        <v>-2.504420264000001</v>
       </c>
       <c r="O77">
-        <v>-0.5906858520000001</v>
+        <v>-0.6010608633600001</v>
       </c>
       <c r="P77">
-        <v>-1.870505198</v>
+        <v>-1.903359400640001</v>
       </c>
       <c r="Q77">
-        <v>-1.738505198</v>
+        <v>-1.771359400640001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3122421168532499</v>
+        <v>0.3233438717221354</v>
       </c>
       <c r="T77">
-        <v>4.492596866648383</v>
+        <v>4.679788402758733</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05781275597562333</v>
+        <v>0.05705206181804933</v>
       </c>
       <c r="W77">
-        <v>0.222167752140948</v>
+        <v>0.222347123823304</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2408864832317639</v>
+        <v>0.2377169242418723</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2465863433190235</v>
+        <v>0.2484863433190235</v>
       </c>
       <c r="C78">
-        <v>-7.57735873026194</v>
+        <v>-7.820267832705437</v>
       </c>
       <c r="D78">
-        <v>6.355721269738062</v>
+        <v>6.296142167294565</v>
       </c>
       <c r="E78">
-        <v>13.90008</v>
+        <v>14.08341</v>
       </c>
       <c r="F78">
-        <v>13.93308</v>
+        <v>14.11641</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7796,37 +7796,37 @@
         <v>0.781</v>
       </c>
       <c r="M78">
-        <v>3.285420264000001</v>
+        <v>3.328649478</v>
       </c>
       <c r="N78">
-        <v>-2.504420264000001</v>
+        <v>-2.547649478</v>
       </c>
       <c r="O78">
-        <v>-0.6010608633600001</v>
+        <v>-0.61143587472</v>
       </c>
       <c r="P78">
-        <v>-1.903359400640001</v>
+        <v>-1.93621360328</v>
       </c>
       <c r="Q78">
-        <v>-1.771359400640001</v>
+        <v>-1.80421360328</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3233438717221354</v>
+        <v>0.3354109965796195</v>
       </c>
       <c r="T78">
-        <v>4.679788402758733</v>
+        <v>4.883257463748243</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05705206181804933</v>
+        <v>0.05631112595028246</v>
       </c>
       <c r="W78">
-        <v>0.222347123823304</v>
+        <v>0.2225218365009234</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2377169242418723</v>
+        <v>0.2346296914595103</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2484863433190235</v>
+        <v>0.2503863433190235</v>
       </c>
       <c r="C79">
-        <v>-7.820267832705437</v>
+        <v>-8.062070309038841</v>
       </c>
       <c r="D79">
-        <v>6.296142167294565</v>
+        <v>6.23766969096116</v>
       </c>
       <c r="E79">
-        <v>14.08341</v>
+        <v>14.26674</v>
       </c>
       <c r="F79">
-        <v>14.11641</v>
+        <v>14.29974</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7878,37 +7878,37 @@
         <v>0.781</v>
       </c>
       <c r="M79">
-        <v>3.328649478</v>
+        <v>3.371878692000001</v>
       </c>
       <c r="N79">
-        <v>-2.547649478</v>
+        <v>-2.590878692</v>
       </c>
       <c r="O79">
-        <v>-0.61143587472</v>
+        <v>-0.6218108860800001</v>
       </c>
       <c r="P79">
-        <v>-1.93621360328</v>
+        <v>-1.96906780592</v>
       </c>
       <c r="Q79">
-        <v>-1.80421360328</v>
+        <v>-1.83706780592</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3354109965796195</v>
+        <v>0.348575132787784</v>
       </c>
       <c r="T79">
-        <v>4.883257463748243</v>
+        <v>5.105223712100436</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05631112595028246</v>
+        <v>0.05558918843809935</v>
       </c>
       <c r="W79">
-        <v>0.2225218365009234</v>
+        <v>0.2226920693662962</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2346296914595103</v>
+        <v>0.2316216184920806</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2503863433190235</v>
+        <v>0.2522863433190235</v>
       </c>
       <c r="C80">
-        <v>-8.062070309038841</v>
+        <v>-8.302796707378443</v>
       </c>
       <c r="D80">
-        <v>6.23766969096116</v>
+        <v>6.180273292621559</v>
       </c>
       <c r="E80">
-        <v>14.26674</v>
+        <v>14.45007</v>
       </c>
       <c r="F80">
-        <v>14.29974</v>
+        <v>14.48307</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7960,37 +7960,37 @@
         <v>0.781</v>
       </c>
       <c r="M80">
-        <v>3.371878692000001</v>
+        <v>3.415107906000001</v>
       </c>
       <c r="N80">
-        <v>-2.590878692</v>
+        <v>-2.634107906000001</v>
       </c>
       <c r="O80">
-        <v>-0.6218108860800001</v>
+        <v>-0.6321858974400001</v>
       </c>
       <c r="P80">
-        <v>-1.96906780592</v>
+        <v>-2.00192200856</v>
       </c>
       <c r="Q80">
-        <v>-1.83706780592</v>
+        <v>-1.86992200856</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.348575132787784</v>
+        <v>0.362992996253869</v>
       </c>
       <c r="T80">
-        <v>5.105223712100436</v>
+        <v>5.348329603152838</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05558918843809935</v>
+        <v>0.05488552782495885</v>
       </c>
       <c r="W80">
-        <v>0.2226920693662962</v>
+        <v>0.2228579925388747</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2316216184920806</v>
+        <v>0.228689699270662</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2522863433190235</v>
+        <v>0.2541863433190236</v>
       </c>
       <c r="C81">
-        <v>-8.302796707378443</v>
+        <v>-8.542476461728731</v>
       </c>
       <c r="D81">
-        <v>6.180273292621559</v>
+        <v>6.123923538271272</v>
       </c>
       <c r="E81">
-        <v>14.45007</v>
+        <v>14.6334</v>
       </c>
       <c r="F81">
-        <v>14.48307</v>
+        <v>14.6664</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -8042,37 +8042,37 @@
         <v>0.781</v>
       </c>
       <c r="M81">
-        <v>3.415107906000001</v>
+        <v>3.458337120000001</v>
       </c>
       <c r="N81">
-        <v>-2.634107906000001</v>
+        <v>-2.677337120000001</v>
       </c>
       <c r="O81">
-        <v>-0.6321858974400001</v>
+        <v>-0.6425609088000002</v>
       </c>
       <c r="P81">
-        <v>-2.00192200856</v>
+        <v>-2.034776211200001</v>
       </c>
       <c r="Q81">
-        <v>-1.86992200856</v>
+        <v>-1.9027762112</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.362992996253869</v>
+        <v>0.3788526460665625</v>
       </c>
       <c r="T81">
-        <v>5.348329603152838</v>
+        <v>5.615746083310481</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05488552782495885</v>
+        <v>0.05419945872714686</v>
       </c>
       <c r="W81">
-        <v>0.2228579925388747</v>
+        <v>0.2230197676321388</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.228689699270662</v>
+        <v>0.2258310780297786</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2541863433190236</v>
+        <v>0.2560863433190235</v>
       </c>
       <c r="C82">
-        <v>-8.542476461728731</v>
+        <v>-8.781137942314055</v>
       </c>
       <c r="D82">
-        <v>6.123923538271272</v>
+        <v>6.068592057685947</v>
       </c>
       <c r="E82">
-        <v>14.6334</v>
+        <v>14.81673</v>
       </c>
       <c r="F82">
-        <v>14.6664</v>
+        <v>14.84973</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8124,37 +8124,37 @@
         <v>0.781</v>
       </c>
       <c r="M82">
-        <v>3.458337120000001</v>
+        <v>3.501566334000001</v>
       </c>
       <c r="N82">
-        <v>-2.677337120000001</v>
+        <v>-2.720566334000001</v>
       </c>
       <c r="O82">
-        <v>-0.6425609088000002</v>
+        <v>-0.6529359201600001</v>
       </c>
       <c r="P82">
-        <v>-2.034776211200001</v>
+        <v>-2.067630413840001</v>
       </c>
       <c r="Q82">
-        <v>-1.9027762112</v>
+        <v>-1.935630413840001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3788526460665625</v>
+        <v>0.3963817327016447</v>
       </c>
       <c r="T82">
-        <v>5.615746083310481</v>
+        <v>5.911311666642612</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05419945872714686</v>
+        <v>0.05353032960705863</v>
       </c>
       <c r="W82">
-        <v>0.2230197676321388</v>
+        <v>0.2231775482786556</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2258310780297786</v>
+        <v>0.223043040029411</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2560863433190235</v>
+        <v>0.2579863433190235</v>
       </c>
       <c r="C83">
-        <v>-8.781137942314055</v>
+        <v>-9.01880850320617</v>
       </c>
       <c r="D83">
-        <v>6.068592057685947</v>
+        <v>6.014251496793832</v>
       </c>
       <c r="E83">
-        <v>14.81673</v>
+        <v>15.00006</v>
       </c>
       <c r="F83">
-        <v>14.84973</v>
+        <v>15.03306</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8206,37 +8206,37 @@
         <v>0.781</v>
       </c>
       <c r="M83">
-        <v>3.501566334000001</v>
+        <v>3.544795548000001</v>
       </c>
       <c r="N83">
-        <v>-2.720566334000001</v>
+        <v>-2.763795548</v>
       </c>
       <c r="O83">
-        <v>-0.6529359201600001</v>
+        <v>-0.6633109315200001</v>
       </c>
       <c r="P83">
-        <v>-2.067630413840001</v>
+        <v>-2.10048461648</v>
       </c>
       <c r="Q83">
-        <v>-1.935630413840001</v>
+        <v>-1.96848461648</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3963817327016447</v>
+        <v>0.4158584956295139</v>
       </c>
       <c r="T83">
-        <v>5.911311666642612</v>
+        <v>6.239717870344979</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05353032960705863</v>
+        <v>0.05287752070941158</v>
       </c>
       <c r="W83">
-        <v>0.2231775482786556</v>
+        <v>0.2233314806167208</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.223043040029411</v>
+        <v>0.2203230029558816</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2579863433190235</v>
+        <v>0.2598863433190235</v>
       </c>
       <c r="C84">
-        <v>-9.01880850320617</v>
+        <v>-9.255514527415617</v>
       </c>
       <c r="D84">
-        <v>6.014251496793832</v>
+        <v>5.960875472584385</v>
       </c>
       <c r="E84">
-        <v>15.00006</v>
+        <v>15.18339</v>
       </c>
       <c r="F84">
-        <v>15.03306</v>
+        <v>15.21639</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8288,37 +8288,37 @@
         <v>0.781</v>
       </c>
       <c r="M84">
-        <v>3.544795548000001</v>
+        <v>3.588024762000001</v>
       </c>
       <c r="N84">
-        <v>-2.763795548</v>
+        <v>-2.807024762000001</v>
       </c>
       <c r="O84">
-        <v>-0.6633109315200001</v>
+        <v>-0.6736859428800002</v>
       </c>
       <c r="P84">
-        <v>-2.10048461648</v>
+        <v>-2.13333881912</v>
       </c>
       <c r="Q84">
-        <v>-1.96848461648</v>
+        <v>-2.00133881912</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4158584956295139</v>
+        <v>0.43762664243125</v>
       </c>
       <c r="T84">
-        <v>6.239717870344979</v>
+        <v>6.606760098012331</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05287752070941158</v>
+        <v>0.05224044214664758</v>
       </c>
       <c r="W84">
-        <v>0.2233314806167208</v>
+        <v>0.2234817037418205</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2203230029558816</v>
+        <v>0.217668508944365</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2598863433190235</v>
+        <v>0.2617863433190235</v>
       </c>
       <c r="C85">
-        <v>-9.255514527415617</v>
+        <v>-9.491281469603125</v>
       </c>
       <c r="D85">
-        <v>5.960875472584385</v>
+        <v>5.908438530396879</v>
       </c>
       <c r="E85">
-        <v>15.18339</v>
+        <v>15.36672</v>
       </c>
       <c r="F85">
-        <v>15.21639</v>
+        <v>15.39972</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8370,37 +8370,37 @@
         <v>0.781</v>
       </c>
       <c r="M85">
-        <v>3.588024762000001</v>
+        <v>3.631253976000001</v>
       </c>
       <c r="N85">
-        <v>-2.807024762000001</v>
+        <v>-2.850253976000001</v>
       </c>
       <c r="O85">
-        <v>-0.6736859428800002</v>
+        <v>-0.6840609542400001</v>
       </c>
       <c r="P85">
-        <v>-2.13333881912</v>
+        <v>-2.166193021760001</v>
       </c>
       <c r="Q85">
-        <v>-2.00133881912</v>
+        <v>-2.034193021760001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.43762664243125</v>
+        <v>0.4621158075832032</v>
       </c>
       <c r="T85">
-        <v>6.606760098012331</v>
+        <v>7.019682604138103</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05224044214664758</v>
+        <v>0.05161853212109225</v>
       </c>
       <c r="W85">
-        <v>0.2234817037418205</v>
+        <v>0.2236283501258464</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.217668508944365</v>
+        <v>0.2150772171712177</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2617863433190235</v>
+        <v>0.2636863433190235</v>
       </c>
       <c r="C86">
-        <v>-9.491281469603122</v>
+        <v>-9.726133896556323</v>
       </c>
       <c r="D86">
-        <v>5.908438530396879</v>
+        <v>5.856916103443679</v>
       </c>
       <c r="E86">
-        <v>15.36672</v>
+        <v>15.55005</v>
       </c>
       <c r="F86">
-        <v>15.39972</v>
+        <v>15.58305</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8452,37 +8452,37 @@
         <v>0.781</v>
       </c>
       <c r="M86">
-        <v>3.631253976</v>
+        <v>3.674483190000001</v>
       </c>
       <c r="N86">
-        <v>-2.850253976</v>
+        <v>-2.89348319</v>
       </c>
       <c r="O86">
-        <v>-0.68406095424</v>
+        <v>-0.6944359656000001</v>
       </c>
       <c r="P86">
-        <v>-2.16619302176</v>
+        <v>-2.1990472244</v>
       </c>
       <c r="Q86">
-        <v>-2.03419302176</v>
+        <v>-2.0670472244</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.462115807583203</v>
+        <v>0.4898701947554164</v>
       </c>
       <c r="T86">
-        <v>7.019682604138099</v>
+        <v>7.487661444413971</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05161853212109226</v>
+        <v>0.05101125527260882</v>
       </c>
       <c r="W86">
-        <v>0.2236283501258464</v>
+        <v>0.2237715460067188</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2150772171712177</v>
+        <v>0.2125468969692035</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2636863433190235</v>
+        <v>0.2655863433190235</v>
       </c>
       <c r="C87">
-        <v>-9.726133896556323</v>
+        <v>-9.960095525567004</v>
       </c>
       <c r="D87">
-        <v>5.856916103443679</v>
+        <v>5.806284474432998</v>
       </c>
       <c r="E87">
-        <v>15.55005</v>
+        <v>15.73338</v>
       </c>
       <c r="F87">
-        <v>15.58305</v>
+        <v>15.76638</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8534,37 +8534,37 @@
         <v>0.781</v>
       </c>
       <c r="M87">
-        <v>3.674483190000001</v>
+        <v>3.717712404000001</v>
       </c>
       <c r="N87">
-        <v>-2.89348319</v>
+        <v>-2.936712404000001</v>
       </c>
       <c r="O87">
-        <v>-0.6944359656000001</v>
+        <v>-0.7048109769600001</v>
       </c>
       <c r="P87">
-        <v>-2.1990472244</v>
+        <v>-2.23190142704</v>
       </c>
       <c r="Q87">
-        <v>-2.0670472244</v>
+        <v>-2.09990142704</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4898701947554164</v>
+        <v>0.5215894943808033</v>
       </c>
       <c r="T87">
-        <v>7.487661444413971</v>
+        <v>8.022494404729255</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05101125527260882</v>
+        <v>0.05041810114153197</v>
       </c>
       <c r="W87">
-        <v>0.2237715460067188</v>
+        <v>0.2239114117508268</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2125468969692035</v>
+        <v>0.2100754214230499</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2655863433190235</v>
+        <v>0.2674863433190235</v>
       </c>
       <c r="C88">
-        <v>-9.960095525567004</v>
+        <v>-10.19318926083484</v>
       </c>
       <c r="D88">
-        <v>5.806284474432998</v>
+        <v>5.75652073916516</v>
       </c>
       <c r="E88">
-        <v>15.73338</v>
+        <v>15.91671</v>
       </c>
       <c r="F88">
-        <v>15.76638</v>
+        <v>15.94971</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8616,37 +8616,37 @@
         <v>0.781</v>
       </c>
       <c r="M88">
-        <v>3.717712404000001</v>
+        <v>3.760941618</v>
       </c>
       <c r="N88">
-        <v>-2.936712404000001</v>
+        <v>-2.979941618</v>
       </c>
       <c r="O88">
-        <v>-0.7048109769600001</v>
+        <v>-0.71518598832</v>
       </c>
       <c r="P88">
-        <v>-2.23190142704</v>
+        <v>-2.26475562968</v>
       </c>
       <c r="Q88">
-        <v>-2.09990142704</v>
+        <v>-2.13275562968</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5215894943808033</v>
+        <v>0.5581886862562497</v>
       </c>
       <c r="T88">
-        <v>8.022494404729255</v>
+        <v>8.639609358939198</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05041810114153197</v>
+        <v>0.04983858273760632</v>
       </c>
       <c r="W88">
-        <v>0.2239114117508268</v>
+        <v>0.2240480621904724</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2100754214230499</v>
+        <v>0.207660761406693</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2674863433190235</v>
+        <v>0.2693863433190235</v>
       </c>
       <c r="C89">
-        <v>-10.19318926083484</v>
+        <v>-10.42543722801501</v>
       </c>
       <c r="D89">
-        <v>5.75652073916516</v>
+        <v>5.707602771984993</v>
       </c>
       <c r="E89">
-        <v>15.91671</v>
+        <v>16.10004</v>
       </c>
       <c r="F89">
-        <v>15.94971</v>
+        <v>16.13304</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8698,37 +8698,37 @@
         <v>0.781</v>
       </c>
       <c r="M89">
-        <v>3.760941618</v>
+        <v>3.804170832000001</v>
       </c>
       <c r="N89">
-        <v>-2.979941618</v>
+        <v>-3.023170832</v>
       </c>
       <c r="O89">
-        <v>-0.71518598832</v>
+        <v>-0.7255609996800001</v>
       </c>
       <c r="P89">
-        <v>-2.26475562968</v>
+        <v>-2.29760983232</v>
       </c>
       <c r="Q89">
-        <v>-2.13275562968</v>
+        <v>-2.16560983232</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5581886862562497</v>
+        <v>0.6008877434442706</v>
       </c>
       <c r="T89">
-        <v>8.639609358939198</v>
+        <v>9.359576805517467</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04983858273760632</v>
+        <v>0.04927223520649715</v>
       </c>
       <c r="W89">
-        <v>0.2240480621904724</v>
+        <v>0.224181606938308</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.207660761406693</v>
+        <v>0.2053009800270715</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2693863433190235</v>
+        <v>0.2712863433190235</v>
       </c>
       <c r="C90">
-        <v>-10.42543722801501</v>
+        <v>-10.65686080701916</v>
       </c>
       <c r="D90">
-        <v>5.707602771984993</v>
+        <v>5.659509192980837</v>
       </c>
       <c r="E90">
-        <v>16.10004</v>
+        <v>16.28337</v>
       </c>
       <c r="F90">
-        <v>16.13304</v>
+        <v>16.31637</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8780,37 +8780,37 @@
         <v>0.781</v>
       </c>
       <c r="M90">
-        <v>3.804170832000001</v>
+        <v>3.847400046000001</v>
       </c>
       <c r="N90">
-        <v>-3.023170832</v>
+        <v>-3.066400046</v>
       </c>
       <c r="O90">
-        <v>-0.7255609996800001</v>
+        <v>-0.7359360110400001</v>
       </c>
       <c r="P90">
-        <v>-2.29760983232</v>
+        <v>-2.33046403496</v>
       </c>
       <c r="Q90">
-        <v>-2.16560983232</v>
+        <v>-2.19846403496</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6008877434442706</v>
+        <v>0.651350265575568</v>
       </c>
       <c r="T90">
-        <v>9.359576805517467</v>
+        <v>10.21044742420087</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04927223520649715</v>
+        <v>0.04871861458619944</v>
       </c>
       <c r="W90">
-        <v>0.224181606938308</v>
+        <v>0.2243121506805742</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2053009800270715</v>
+        <v>0.2029942274424976</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2712863433190235</v>
+        <v>0.2731863433190235</v>
       </c>
       <c r="C91">
-        <v>-10.65686080701916</v>
+        <v>-10.88748066317195</v>
       </c>
       <c r="D91">
-        <v>5.659509192980837</v>
+        <v>5.612219336828056</v>
       </c>
       <c r="E91">
-        <v>16.28337</v>
+        <v>16.4667</v>
       </c>
       <c r="F91">
-        <v>16.31637</v>
+        <v>16.4997</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8862,37 +8862,37 @@
         <v>0.781</v>
       </c>
       <c r="M91">
-        <v>3.847400046000001</v>
+        <v>3.89062926</v>
       </c>
       <c r="N91">
-        <v>-3.066400046</v>
+        <v>-3.10962926</v>
       </c>
       <c r="O91">
-        <v>-0.7359360110400001</v>
+        <v>-0.7463110224</v>
       </c>
       <c r="P91">
-        <v>-2.33046403496</v>
+        <v>-2.3633182376</v>
       </c>
       <c r="Q91">
-        <v>-2.19846403496</v>
+        <v>-2.2313182376</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.651350265575568</v>
+        <v>0.7119052921331249</v>
       </c>
       <c r="T91">
-        <v>10.21044742420087</v>
+        <v>11.23149216662096</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04871861458619944</v>
+        <v>0.04817729664635278</v>
       </c>
       <c r="W91">
-        <v>0.2243121506805742</v>
+        <v>0.22443979345079</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2029942274424976</v>
+        <v>0.20073873602647</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2731863433190235</v>
+        <v>0.2750863433190235</v>
       </c>
       <c r="C92">
-        <v>-10.88748066317195</v>
+        <v>-11.1173167768184</v>
       </c>
       <c r="D92">
-        <v>5.612219336828056</v>
+        <v>5.565713223181606</v>
       </c>
       <c r="E92">
-        <v>16.4667</v>
+        <v>16.65003</v>
       </c>
       <c r="F92">
-        <v>16.4997</v>
+        <v>16.68303</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8944,37 +8944,37 @@
         <v>0.781</v>
       </c>
       <c r="M92">
-        <v>3.89062926</v>
+        <v>3.933858474000001</v>
       </c>
       <c r="N92">
-        <v>-3.10962926</v>
+        <v>-3.152858474000001</v>
       </c>
       <c r="O92">
-        <v>-0.7463110224</v>
+        <v>-0.7566860337600001</v>
       </c>
       <c r="P92">
-        <v>-2.3633182376</v>
+        <v>-2.396172440240001</v>
       </c>
       <c r="Q92">
-        <v>-2.2313182376</v>
+        <v>-2.264172440240001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7119052921331249</v>
+        <v>0.7859169912590277</v>
       </c>
       <c r="T92">
-        <v>11.23149216662096</v>
+        <v>12.47943574068996</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04817729664635278</v>
+        <v>0.04764787580408515</v>
       </c>
       <c r="W92">
-        <v>0.22443979345079</v>
+        <v>0.2245646308853967</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.20073873602647</v>
+        <v>0.1985328158503549</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2750863433190235</v>
+        <v>0.2769863433190235</v>
       </c>
       <c r="C93">
-        <v>-11.1173167768184</v>
+        <v>-11.34638847147141</v>
       </c>
       <c r="D93">
-        <v>5.565713223181606</v>
+        <v>5.519971528528596</v>
       </c>
       <c r="E93">
-        <v>16.65003</v>
+        <v>16.83336</v>
       </c>
       <c r="F93">
-        <v>16.68303</v>
+        <v>16.86636</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -9026,37 +9026,37 @@
         <v>0.781</v>
       </c>
       <c r="M93">
-        <v>3.933858474000001</v>
+        <v>3.977087688000001</v>
       </c>
       <c r="N93">
-        <v>-3.152858474000001</v>
+        <v>-3.196087688000001</v>
       </c>
       <c r="O93">
-        <v>-0.7566860337600001</v>
+        <v>-0.7670610451200002</v>
       </c>
       <c r="P93">
-        <v>-2.396172440240001</v>
+        <v>-2.429026642880001</v>
       </c>
       <c r="Q93">
-        <v>-2.264172440240001</v>
+        <v>-2.297026642880001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7859169912590277</v>
+        <v>0.8784316151664063</v>
       </c>
       <c r="T93">
-        <v>12.47943574068996</v>
+        <v>14.03936520827621</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04764787580408515</v>
+        <v>0.04712996411056249</v>
       </c>
       <c r="W93">
-        <v>0.2245646308853967</v>
+        <v>0.2246867544627294</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1985328158503549</v>
+        <v>0.196374850460677</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2769863433190235</v>
+        <v>0.2788863433190235</v>
       </c>
       <c r="C94">
-        <v>-11.34638847147141</v>
+        <v>-11.57471444058252</v>
       </c>
       <c r="D94">
-        <v>5.519971528528596</v>
+        <v>5.474975559417485</v>
       </c>
       <c r="E94">
-        <v>16.83336</v>
+        <v>17.01669</v>
       </c>
       <c r="F94">
-        <v>16.86636</v>
+        <v>17.04969</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -9108,37 +9108,37 @@
         <v>0.781</v>
       </c>
       <c r="M94">
-        <v>3.977087688000001</v>
+        <v>4.020316902</v>
       </c>
       <c r="N94">
-        <v>-3.196087688000001</v>
+        <v>-3.239316902</v>
       </c>
       <c r="O94">
-        <v>-0.7670610451200002</v>
+        <v>-0.77743605648</v>
       </c>
       <c r="P94">
-        <v>-2.429026642880001</v>
+        <v>-2.46188084552</v>
       </c>
       <c r="Q94">
-        <v>-2.297026642880001</v>
+        <v>-2.32988084552</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8784316151664063</v>
+        <v>0.9973789887616075</v>
       </c>
       <c r="T94">
-        <v>14.03936520827621</v>
+        <v>16.04498880945852</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04712996411056249</v>
+        <v>0.04662319030292204</v>
       </c>
       <c r="W94">
-        <v>0.2246867544627294</v>
+        <v>0.224806251726571</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.196374850460677</v>
+        <v>0.1942632929288419</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2788863433190235</v>
+        <v>0.2807863433190235</v>
       </c>
       <c r="C95">
-        <v>-11.57471444058252</v>
+        <v>-11.80231277301395</v>
       </c>
       <c r="D95">
-        <v>5.474975559417485</v>
+        <v>5.430707226986051</v>
       </c>
       <c r="E95">
-        <v>17.01669</v>
+        <v>17.20002</v>
       </c>
       <c r="F95">
-        <v>17.04969</v>
+        <v>17.23302</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9190,37 +9190,37 @@
         <v>0.781</v>
       </c>
       <c r="M95">
-        <v>4.020316902</v>
+        <v>4.063546116000001</v>
       </c>
       <c r="N95">
-        <v>-3.239316902</v>
+        <v>-3.282546116000001</v>
       </c>
       <c r="O95">
-        <v>-0.77743605648</v>
+        <v>-0.7878110678400002</v>
       </c>
       <c r="P95">
-        <v>-2.46188084552</v>
+        <v>-2.494735048160001</v>
       </c>
       <c r="Q95">
-        <v>-2.32988084552</v>
+        <v>-2.362735048160001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9973789887616075</v>
+        <v>1.155975486888543</v>
       </c>
       <c r="T95">
-        <v>16.04498880945852</v>
+        <v>18.71915361103495</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04662319030292204</v>
+        <v>0.04612719891672074</v>
       </c>
       <c r="W95">
-        <v>0.224806251726571</v>
+        <v>0.2249232064954373</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1942632929288419</v>
+        <v>0.1921966621530031</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2807863433190235</v>
+        <v>0.2826863433190235</v>
       </c>
       <c r="C96">
-        <v>-11.80231277301395</v>
+        <v>-12.02920097728484</v>
       </c>
       <c r="D96">
-        <v>5.430707226986051</v>
+        <v>5.387149022715165</v>
       </c>
       <c r="E96">
-        <v>17.20002</v>
+        <v>17.38335</v>
       </c>
       <c r="F96">
-        <v>17.23302</v>
+        <v>17.41635</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9272,37 +9272,37 @@
         <v>0.781</v>
       </c>
       <c r="M96">
-        <v>4.063546116000001</v>
+        <v>4.106775330000001</v>
       </c>
       <c r="N96">
-        <v>-3.282546116000001</v>
+        <v>-3.32577533</v>
       </c>
       <c r="O96">
-        <v>-0.7878110678400002</v>
+        <v>-0.7981860792000001</v>
       </c>
       <c r="P96">
-        <v>-2.494735048160001</v>
+        <v>-2.5275892508</v>
       </c>
       <c r="Q96">
-        <v>-2.362735048160001</v>
+        <v>-2.3955892508</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.155975486888543</v>
+        <v>1.378010584266252</v>
       </c>
       <c r="T96">
-        <v>18.71915361103495</v>
+        <v>22.46298433324195</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04612719891672074</v>
+        <v>0.04564164945443947</v>
       </c>
       <c r="W96">
-        <v>0.2249232064954373</v>
+        <v>0.2250376990586432</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1921966621530031</v>
+        <v>0.1901735393934978</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2826863433190235</v>
+        <v>0.2845863433190235</v>
       </c>
       <c r="C97">
-        <v>-12.02920097728484</v>
+        <v>-12.25539600465989</v>
       </c>
       <c r="D97">
-        <v>5.387149022715165</v>
+        <v>5.344283995340112</v>
       </c>
       <c r="E97">
-        <v>17.38335</v>
+        <v>17.56668</v>
       </c>
       <c r="F97">
-        <v>17.41635</v>
+        <v>17.59968</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9354,37 +9354,37 @@
         <v>0.781</v>
       </c>
       <c r="M97">
-        <v>4.106775330000001</v>
+        <v>4.150004544000001</v>
       </c>
       <c r="N97">
-        <v>-3.32577533</v>
+        <v>-3.369004544</v>
       </c>
       <c r="O97">
-        <v>-0.7981860792000001</v>
+        <v>-0.8085610905600001</v>
       </c>
       <c r="P97">
-        <v>-2.5275892508</v>
+        <v>-2.56044345344</v>
       </c>
       <c r="Q97">
-        <v>-2.3955892508</v>
+        <v>-2.42844345344</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.378010584266252</v>
+        <v>1.711063230332815</v>
       </c>
       <c r="T97">
-        <v>22.46298433324195</v>
+        <v>28.07873041655245</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04564164945443947</v>
+        <v>0.04516621560595573</v>
       </c>
       <c r="W97">
-        <v>0.2250376990586432</v>
+        <v>0.2251498063601157</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1901735393934978</v>
+        <v>0.1881925650248155</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2845863433190235</v>
+        <v>0.2864863433190235</v>
       </c>
       <c r="C98">
-        <v>-12.25539600465989</v>
+        <v>-12.48091427114449</v>
       </c>
       <c r="D98">
-        <v>5.344283995340112</v>
+        <v>5.302095728855514</v>
       </c>
       <c r="E98">
-        <v>17.56668</v>
+        <v>17.75001</v>
       </c>
       <c r="F98">
-        <v>17.59968</v>
+        <v>17.78301</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9436,37 +9436,37 @@
         <v>0.781</v>
       </c>
       <c r="M98">
-        <v>4.150004544000001</v>
+        <v>4.193233758000001</v>
       </c>
       <c r="N98">
-        <v>-3.369004544</v>
+        <v>-3.412233758000001</v>
       </c>
       <c r="O98">
-        <v>-0.8085610905600001</v>
+        <v>-0.8189361019200001</v>
       </c>
       <c r="P98">
-        <v>-2.56044345344</v>
+        <v>-2.593297656080001</v>
       </c>
       <c r="Q98">
-        <v>-2.42844345344</v>
+        <v>-2.461297656080001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.711063230332811</v>
+        <v>2.266150973777081</v>
       </c>
       <c r="T98">
-        <v>28.07873041655238</v>
+        <v>37.43830722206983</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04516621560595573</v>
+        <v>0.04470058451723453</v>
       </c>
       <c r="W98">
-        <v>0.2251498063601157</v>
+        <v>0.2252596021708361</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1881925650248155</v>
+        <v>0.1862524354884773</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2864863433190235</v>
+        <v>0.2883863433190235</v>
       </c>
       <c r="C99">
-        <v>-12.48091427114449</v>
+        <v>-12.70577167844613</v>
       </c>
       <c r="D99">
-        <v>5.302095728855514</v>
+        <v>5.260568321553872</v>
       </c>
       <c r="E99">
-        <v>17.75001</v>
+        <v>17.93334</v>
       </c>
       <c r="F99">
-        <v>17.78301</v>
+        <v>17.96634</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9518,37 +9518,37 @@
         <v>0.781</v>
       </c>
       <c r="M99">
-        <v>4.193233758000001</v>
+        <v>4.236462972000001</v>
       </c>
       <c r="N99">
-        <v>-3.412233758000001</v>
+        <v>-3.455462972000001</v>
       </c>
       <c r="O99">
-        <v>-0.8189361019200001</v>
+        <v>-0.8293111132800002</v>
       </c>
       <c r="P99">
-        <v>-2.593297656080001</v>
+        <v>-2.626151858720001</v>
       </c>
       <c r="Q99">
-        <v>-2.461297656080001</v>
+        <v>-2.49415185872</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.266150973777081</v>
+        <v>3.376326460665621</v>
       </c>
       <c r="T99">
-        <v>37.43830722206983</v>
+        <v>56.15746083310475</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04470058451723453</v>
+        <v>0.04424445610379336</v>
       </c>
       <c r="W99">
-        <v>0.2252596021708361</v>
+        <v>0.2253671572507255</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1862524354884773</v>
+        <v>0.1843519004324724</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2883863433190235</v>
+        <v>0.2902863433190235</v>
       </c>
       <c r="C100">
-        <v>-12.70577167844613</v>
+        <v>-12.92998363395851</v>
       </c>
       <c r="D100">
-        <v>5.260568321553872</v>
+        <v>5.219686366041494</v>
       </c>
       <c r="E100">
-        <v>17.93334</v>
+        <v>18.11667</v>
       </c>
       <c r="F100">
-        <v>17.96634</v>
+        <v>18.14967</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9600,37 +9600,37 @@
         <v>0.781</v>
       </c>
       <c r="M100">
-        <v>4.236462972000001</v>
+        <v>4.279692186</v>
       </c>
       <c r="N100">
-        <v>-3.455462972000001</v>
+        <v>-3.498692186</v>
       </c>
       <c r="O100">
-        <v>-0.8293111132800002</v>
+        <v>-0.8396861246399999</v>
       </c>
       <c r="P100">
-        <v>-2.626151858720001</v>
+        <v>-2.65900606136</v>
       </c>
       <c r="Q100">
-        <v>-2.49415185872</v>
+        <v>-2.52700606136</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.376326460665621</v>
+        <v>6.706852921331243</v>
       </c>
       <c r="T100">
-        <v>56.15746083310475</v>
+        <v>112.3149216662095</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04424445610379336</v>
+        <v>0.04379754240577526</v>
       </c>
       <c r="W100">
-        <v>0.2253671572507255</v>
+        <v>0.2254725395007182</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1843519004324724</v>
+        <v>0.1824897600240636</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2902863433190235</v>
-      </c>
-      <c r="C101">
-        <v>-12.92998363395851</v>
-      </c>
-      <c r="D101">
-        <v>5.219686366041494</v>
-      </c>
-      <c r="E101">
-        <v>18.11667</v>
-      </c>
-      <c r="F101">
-        <v>18.14967</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>18.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.913</v>
-      </c>
-      <c r="K101">
-        <v>0.132</v>
-      </c>
-      <c r="L101">
-        <v>0.781</v>
-      </c>
-      <c r="M101">
-        <v>4.279692186</v>
-      </c>
-      <c r="N101">
-        <v>-3.498692186</v>
-      </c>
-      <c r="O101">
-        <v>-0.8396861246399999</v>
-      </c>
-      <c r="P101">
-        <v>-2.65900606136</v>
-      </c>
-      <c r="Q101">
-        <v>-2.52700606136</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.706852921331243</v>
-      </c>
-      <c r="T101">
-        <v>112.3149216662095</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04379754240577526</v>
-      </c>
-      <c r="W101">
-        <v>0.2254725395007182</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1824897600240636</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
